--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
@@ -204,7 +204,7 @@
     <t>Public Funding</t>
   </si>
   <si>
-    <t>Grants &amp; Contributions</t>
+    <t>Philanthropy</t>
   </si>
   <si>
     <t>Other Revenue</t>
@@ -225,7 +225,7 @@
     <t>Total Public Funding</t>
   </si>
   <si>
-    <t>GRANTS &amp; CONTRIBUTIONS</t>
+    <t>PHILANTHROPY</t>
   </si>
   <si>
     <t>CSP Startup Grant</t>
@@ -234,7 +234,7 @@
     <t>Annual Fundraising</t>
   </si>
   <si>
-    <t>Total Grants &amp; Contributions</t>
+    <t>Total Philanthropy</t>
   </si>
   <si>
     <t>OTHER REVENUE</t>
@@ -786,7 +786,7 @@
     <t>Charter School  |  OH  |  Est. 2026</t>
   </si>
   <si>
-    <t>Prepared March 16, 2026</t>
+    <t>Prepared March 17, 2026</t>
   </si>
   <si>
     <t>Cash Balance</t>
@@ -813,7 +813,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>March 16, 2026</t>
+    <t>March 17, 2026</t>
   </si>
   <si>
     <t>UNDERWRITING HIGHLIGHTS</t>
@@ -883,7 +883,7 @@
     <numFmt numFmtId="169" formatCode="0.00x"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -900,7 +900,7 @@
     <font>
       <i/>
       <color rgb="FF6B7280"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -949,19 +949,13 @@
     </font>
     <font>
       <color rgb="FF6B7280"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <i/>
       <color rgb="FF9CA3AF"/>
-      <sz val="9"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FF9CA3AF"/>
-      <sz val="8"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -978,7 +972,7 @@
     </font>
     <font>
       <color rgb="FF94A3B8"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1098,7 +1092,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1149,14 +1143,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -3107,14 +3100,14 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="42" t="s">
+      <c r="A18" s="41" t="s">
         <v>246</v>
       </c>
-      <c r="B18" s="42"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3150,43 +3143,43 @@
     <row r="1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" ht="10" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" ht="40" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="42" t="s">
         <v>247</v>
       </c>
-      <c r="C3" s="43"/>
+      <c r="C3" s="42"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="43" t="s">
         <v>248</v>
       </c>
-      <c r="C4" s="44"/>
+      <c r="C4" s="43"/>
     </row>
     <row r="6" ht="4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="46" t="s">
+      <c r="B8" s="45" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="47" t="s">
+      <c r="B9" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="47"/>
+      <c r="C9" s="46"/>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="48" t="s">
+      <c r="B10" s="47" t="s">
         <v>250</v>
       </c>
-      <c r="C10" s="48"/>
+      <c r="C10" s="47"/>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="46" t="s">
+      <c r="B12" s="45" t="s">
         <v>251</v>
       </c>
-      <c r="C12" s="49" t="s">
+      <c r="C12" s="48" t="s">
         <v>252</v>
       </c>
     </row>
@@ -3225,7 +3218,7 @@
       <c r="B19" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="C19" s="50" t="s">
+      <c r="C19" s="49" t="s">
         <v>256</v>
       </c>
     </row>
@@ -3237,88 +3230,88 @@
       <c r="C22" s="3"/>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="51" t="s">
+      <c r="B23" s="50" t="s">
         <v>258</v>
       </c>
-      <c r="C23" s="52"/>
+      <c r="C23" s="51"/>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="51" t="s">
+      <c r="B24" s="50" t="s">
         <v>259</v>
       </c>
-      <c r="C24" s="52"/>
+      <c r="C24" s="51"/>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="51" t="s">
+      <c r="B25" s="50" t="s">
         <v>260</v>
       </c>
-      <c r="C25" s="52"/>
+      <c r="C25" s="51"/>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="51" t="s">
+      <c r="B26" s="50" t="s">
         <v>261</v>
       </c>
-      <c r="C26" s="52"/>
+      <c r="C26" s="51"/>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="51" t="s">
+      <c r="B27" s="50" t="s">
         <v>167</v>
       </c>
-      <c r="C27" s="52"/>
+      <c r="C27" s="51"/>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="51" t="s">
+      <c r="B28" s="50" t="s">
         <v>262</v>
       </c>
-      <c r="C28" s="52"/>
+      <c r="C28" s="51"/>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="51" t="s">
+      <c r="B29" s="50" t="s">
         <v>263</v>
       </c>
-      <c r="C29" s="52"/>
+      <c r="C29" s="51"/>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="51" t="s">
+      <c r="B30" s="50" t="s">
         <v>264</v>
       </c>
-      <c r="C30" s="52"/>
+      <c r="C30" s="51"/>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="51" t="s">
+      <c r="B31" s="50" t="s">
         <v>265</v>
       </c>
-      <c r="C31" s="52"/>
+      <c r="C31" s="51"/>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="51" t="s">
+      <c r="B32" s="50" t="s">
         <v>266</v>
       </c>
-      <c r="C32" s="52"/>
+      <c r="C32" s="51"/>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="51" t="s">
+      <c r="B33" s="50" t="s">
         <v>267</v>
       </c>
-      <c r="C33" s="52"/>
+      <c r="C33" s="51"/>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="51" t="s">
+      <c r="B34" s="50" t="s">
         <v>268</v>
       </c>
-      <c r="C34" s="52"/>
+      <c r="C34" s="51"/>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="51" t="s">
+      <c r="B35" s="50" t="s">
         <v>269</v>
       </c>
-      <c r="C35" s="52"/>
+      <c r="C35" s="51"/>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B36" s="51" t="s">
+      <c r="B36" s="50" t="s">
         <v>270</v>
       </c>
-      <c r="C36" s="52"/>
+      <c r="C36" s="51"/>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" s="41" t="s">

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
@@ -57,7 +57,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="271">
   <si>
-    <t>SchoolStack — Assumptions &amp; Drivers</t>
+    <t>SchoolStack - Assumptions &amp; Drivers</t>
   </si>
   <si>
     <t>Edit the highlighted cells below to update the entire model</t>
@@ -177,7 +177,7 @@
     <t>Enrollment Growth %</t>
   </si>
   <si>
-    <t>—</t>
+    <t>-</t>
   </si>
   <si>
     <t>Capacity Utilization %</t>
@@ -249,7 +249,7 @@
     <t>TOTAL NET REVENUE</t>
   </si>
   <si>
-    <t>SchoolStack — Staffing Plan</t>
+    <t>SchoolStack - Staffing Plan</t>
   </si>
   <si>
     <t>Role</t>
@@ -426,7 +426,7 @@
     <t>% of Revenue</t>
   </si>
   <si>
-    <t>SchoolStack — Capital Stack (2026-27)</t>
+    <t>SchoolStack - Capital Stack (2026-27)</t>
   </si>
   <si>
     <t>SOURCES OF CAPITAL</t>
@@ -471,10 +471,10 @@
     <t>CAPITAL SURPLUS / (GAP)</t>
   </si>
   <si>
-    <t>⚠ Funding gap — additional capital needed</t>
-  </si>
-  <si>
-    <t>SchoolStack — Debt Schedule</t>
+    <t>⚠ Funding gap - additional capital needed</t>
+  </si>
+  <si>
+    <t>SchoolStack - Debt Schedule</t>
   </si>
   <si>
     <t>Loan / Facility</t>
@@ -684,7 +684,7 @@
     <t>Enrollment ≥ 70% Capacity</t>
   </si>
   <si>
-    <t>SchoolStack — Underwriting Snapshot</t>
+    <t>SchoolStack - Underwriting Snapshot</t>
   </si>
   <si>
     <t>Civic Scholars Charter | Charter School | OH</t>
@@ -3408,19 +3408,19 @@
         <v>40</v>
       </c>
       <c r="C3" s="12">
-        <f>IF(B2=0,"—",(C2-B2)/B2)</f>
+        <f>IF(B2=0,"-",(C2-B2)/B2)</f>
         <v>0.67</v>
       </c>
       <c r="D3" s="12">
-        <f>IF(C2=0,"—",(D2-C2)/C2)</f>
+        <f>IF(C2=0,"-",(D2-C2)/C2)</f>
         <v>0.5</v>
       </c>
       <c r="E3" s="12">
-        <f>IF(D2=0,"—",(E2-D2)/D2)</f>
+        <f>IF(D2=0,"-",(E2-D2)/D2)</f>
         <v>0.25</v>
       </c>
       <c r="F3" s="12">
-        <f>IF(E2=0,"—",(F2-E2)/E2)</f>
+        <f>IF(E2=0,"-",(F2-E2)/E2)</f>
         <v>0.07</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
@@ -786,7 +786,7 @@
     <t>Charter School  |  OH  |  Est. 2026</t>
   </si>
   <si>
-    <t>Prepared March 17, 2026</t>
+    <t>Prepared March 18, 2026</t>
   </si>
   <si>
     <t>Cash Balance</t>
@@ -813,7 +813,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>March 17, 2026</t>
+    <t>March 18, 2026</t>
   </si>
   <si>
     <t>UNDERWRITING HIGHLIGHTS</t>

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
@@ -786,7 +786,7 @@
     <t>Charter School  |  OH  |  Est. 2026</t>
   </si>
   <si>
-    <t>Prepared March 18, 2026</t>
+    <t>Prepared March 26, 2026</t>
   </si>
   <si>
     <t>Cash Balance</t>
@@ -813,7 +813,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>March 18, 2026</t>
+    <t>March 26, 2026</t>
   </si>
   <si>
     <t>UNDERWRITING HIGHLIGHTS</t>

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
@@ -883,7 +883,7 @@
     <numFmt numFmtId="169" formatCode="0.00x"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -921,6 +921,11 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF1E3A5F"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -1012,7 +1017,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFDE8"/>
+        <fgColor rgb="FFDBEAFE"/>
       </patternFill>
     </fill>
     <fill>
@@ -1050,17 +1055,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFD0D0D0"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD0D0D0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD0D0D0"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFD97706"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF93C5FD"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1102,9 +1101,9 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1119,7 +1118,7 @@
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1134,22 +1133,22 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
@@ -55,12 +55,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="272">
   <si>
     <t>SchoolStack - Assumptions &amp; Drivers</t>
   </si>
   <si>
-    <t>Edit the highlighted cells below to update the entire model</t>
+    <t/>
+  </si>
+  <si>
+    <t>Editable assumption — change this value</t>
+  </si>
+  <si>
+    <t>Calculated — driven by formula</t>
   </si>
   <si>
     <t>SCHOOL INFORMATION</t>
@@ -97,9 +103,6 @@
   </si>
   <si>
     <t>Planned Opening Year</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Max Student Capacity</t>
@@ -899,7 +902,7 @@
     </font>
     <font>
       <i/>
-      <color rgb="FF6B7280"/>
+      <color rgb="FF666666"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -998,12 +1001,22 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBEAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1017,11 +1030,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDBEAFE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFCE4EC"/>
       </patternFill>
     </fill>
@@ -1031,12 +1039,30 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF93C5FD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1051,15 +1077,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD0D0D0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF93C5FD"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1091,65 +1108,66 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1509,202 +1527,205 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="B2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
+      <c r="A3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>4</v>
+      <c r="A4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>6</v>
+      <c r="A5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>8</v>
+      <c r="A6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="5" t="s">
+      <c r="A7" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="7">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="5">
+    <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+    </row>
+    <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="9">
+        <v>120</v>
+      </c>
+      <c r="C17" s="9">
+        <v>200</v>
+      </c>
+      <c r="D17" s="9">
+        <v>300</v>
+      </c>
+      <c r="E17" s="9">
+        <v>375</v>
+      </c>
+      <c r="F17" s="9">
         <v>400</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-    </row>
-    <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="7">
-        <v>120</v>
-      </c>
-      <c r="C17" s="7">
-        <v>200</v>
-      </c>
-      <c r="D17" s="7">
-        <v>300</v>
-      </c>
-      <c r="E17" s="7">
-        <v>375</v>
-      </c>
-      <c r="F17" s="7">
-        <v>400</v>
-      </c>
-    </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
+      <c r="A19" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="8">
+      <c r="A20" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" s="8">
+      <c r="A21" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="9">
+      <c r="A22" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="11">
         <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" s="5" t="s">
+      <c r="A23" s="6" t="s">
         <v>33</v>
       </c>
+      <c r="B23" s="7" t="s">
+        <v>34</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
@@ -1728,216 +1749,216 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="A1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="E1" s="8" t="s">
         <v>38</v>
       </c>
+      <c r="F1" s="8" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="B2" s="26">
+      <c r="A2" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="B2" s="27">
         <f>'Tuition &amp; Funding Detail'!B16</f>
         <v>1288333</v>
       </c>
-      <c r="C2" s="26">
+      <c r="C2" s="27">
         <f>'Tuition &amp; Funding Detail'!C16</f>
         <v>2522800</v>
       </c>
-      <c r="D2" s="26">
+      <c r="D2" s="27">
         <f>'Tuition &amp; Funding Detail'!D16</f>
         <v>3784600</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="27">
         <f>'Tuition &amp; Funding Detail'!E16</f>
         <v>4759125</v>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="27">
         <f>'Tuition &amp; Funding Detail'!F16</f>
         <v>5184400</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="B3" s="13">
+      <c r="A3" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B3" s="15">
         <f>'Staffing Plan'!B28</f>
         <v>1026431</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="15">
         <f>'Staffing Plan'!C28</f>
         <v>1231718</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="15">
         <f>'Staffing Plan'!D28</f>
         <v>1231718</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="15">
         <f>'Staffing Plan'!E28</f>
         <v>1231718</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="15">
         <f>'Staffing Plan'!F28</f>
         <v>1231718</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B4" s="13">
+      <c r="A4" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" s="15">
         <f>'Operating Expenses'!B16+'Facilities &amp; Occupancy'!B7</f>
         <v>545000</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="15">
         <f>'Operating Expenses'!C16+'Facilities &amp; Occupancy'!C7</f>
         <v>887860</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="15">
         <f>'Operating Expenses'!D16+'Facilities &amp; Occupancy'!D7</f>
         <v>1190521</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="15">
         <f>'Operating Expenses'!E16+'Facilities &amp; Occupancy'!E7</f>
         <v>1439089</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="15">
         <f>'Operating Expenses'!F16+'Facilities &amp; Occupancy'!F7</f>
         <v>1554924</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="B5" s="13">
+      <c r="A5" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B5" s="15">
         <v>164825</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="15">
         <v>89825</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="15">
         <v>89825</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="15">
         <v>74825</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="15">
         <v>69825</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="B6" s="27">
+      <c r="A6" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B6" s="28">
         <f>SUM(B3:B5)</f>
         <v>1736256</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="28">
         <f>SUM(C3:C5)</f>
         <v>2209403</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="28">
         <f>SUM(D3:D5)</f>
         <v>2512064</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="28">
         <f>SUM(E3:E5)</f>
         <v>2745632</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="28">
         <f>SUM(F3:F5)</f>
         <v>2856467</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="B7" s="28">
+      <c r="A7" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="B7" s="29">
         <f>B2-B6</f>
         <v>-447923</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <f>C2-C6</f>
         <v>313398</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <f>D2-D6</f>
         <v>1272536</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <f>E2-E6</f>
         <v>2013494</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <f>F2-F6</f>
         <v>2327934</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="B8" s="12">
+      <c r="A8" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B8" s="14">
         <f>IF(B2=0,0,B7/B2)</f>
         <v>-0.35</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="14">
         <f>IF(C2=0,0,C7/C2)</f>
         <v>0.12</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="14">
         <f>IF(D2=0,0,D7/D2)</f>
         <v>0.34</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="14">
         <f>IF(E2=0,0,E7/E2)</f>
         <v>0.42</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="14">
         <f>IF(F2=0,0,F7/F2)</f>
         <v>0.45</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="B9" s="26">
+      <c r="A9" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="B9" s="27">
         <f>B7</f>
         <v>-447923</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="27">
         <f>B9+C7</f>
         <v>-134525</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="27">
         <f>C9+D7</f>
         <v>1138011</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="27">
         <f>D9+E7</f>
         <v>3151505</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="27">
         <f>E9+F7</f>
         <v>5479439</v>
       </c>
@@ -1965,271 +1986,271 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="A1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="E1" s="8" t="s">
         <v>38</v>
       </c>
+      <c r="F1" s="8" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="A2" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="B3" s="13">
+      <c r="A3" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="B3" s="15">
         <v>52077</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="15">
         <v>365475</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="15">
         <v>1638011</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="15">
         <v>3651505</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="15">
         <v>5979439</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="B4" s="13">
+      <c r="A4" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B4" s="15">
         <v>0</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="15">
         <v>0</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="15">
         <v>0</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="15">
         <v>0</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="B5" s="14">
+      <c r="A5" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B5" s="16">
         <f>SUM(B3:B4)</f>
         <v>52077</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="16">
         <f>SUM(C3:C4)</f>
         <v>365475</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="16">
         <f>SUM(D3:D4)</f>
         <v>1638011</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="16">
         <f>SUM(E3:E4)</f>
         <v>3651505</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="16">
         <f>SUM(F3:F4)</f>
         <v>5979439</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+      <c r="A7" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="B8" s="13">
+      <c r="A8" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B8" s="15">
         <v>478925</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="15">
         <v>456639</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="15">
         <v>433071</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="15">
         <v>408148</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="15">
         <v>381792</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="B9" s="13">
+      <c r="A9" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="B9" s="15">
         <v>0</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="15">
         <v>0</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="15">
         <v>0</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="15">
         <v>0</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="B10" s="14">
+      <c r="A10" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B10" s="16">
         <f>SUM(B8:B9)</f>
         <v>478925</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="16">
         <f>SUM(C8:C9)</f>
         <v>456639</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="16">
         <f>SUM(D8:D9)</f>
         <v>433071</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="16">
         <f>SUM(E8:E9)</f>
         <v>408148</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="16">
         <f>SUM(F8:F9)</f>
         <v>381792</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
+      <c r="A12" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B13" s="13">
+      <c r="A13" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="B13" s="15">
         <v>0</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="15">
         <v>-426848</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="15">
         <v>-91164</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="15">
         <v>1204940</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="15">
         <v>3243357</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B14" s="13">
+      <c r="A14" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="B14" s="15">
         <v>-426848</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="15">
         <v>335684</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="15">
         <v>1296104</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="15">
         <v>2038417</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="15">
         <v>2354290</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B15" s="14">
+      <c r="A15" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B15" s="16">
         <f>B5-B10</f>
         <v>-426848</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="16">
         <f>C5-C10</f>
         <v>-91164</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="16">
         <f>D5-D10</f>
         <v>1204940</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="16">
         <f>E5-E10</f>
         <v>3243357</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="16">
         <f>F5-F10</f>
         <v>5597647</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="B17" s="26" t="str">
+      <c r="A17" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="B17" s="27" t="str">
         <f>B5-B10-B15</f>
         <v>0</v>
       </c>
-      <c r="C17" s="26" t="str">
+      <c r="C17" s="27" t="str">
         <f>C5-C10-C15</f>
         <v>0</v>
       </c>
-      <c r="D17" s="26" t="str">
+      <c r="D17" s="27" t="str">
         <f>D5-D10-D15</f>
         <v>0</v>
       </c>
-      <c r="E17" s="26" t="str">
+      <c r="E17" s="27" t="str">
         <f>E5-E10-E15</f>
         <v>0</v>
       </c>
-      <c r="F17" s="26" t="str">
+      <c r="F17" s="27" t="str">
         <f>F5-F10-F15</f>
         <v>0</v>
       </c>
@@ -2257,293 +2278,293 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="A1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="E1" s="8" t="s">
         <v>38</v>
       </c>
+      <c r="F1" s="8" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="A2" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="B3" s="13">
+      <c r="A3" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" s="15">
         <v>-283098</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="15">
         <v>403222</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="15">
         <v>1362361</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="15">
         <v>2088318</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="15">
         <v>2397758</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="B4" s="13">
+      <c r="A4" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B4" s="15">
         <v>49825</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="15">
         <v>49825</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="15">
         <v>49825</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="15">
         <v>49825</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="15">
         <v>49825</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="B5" s="30">
+      <c r="A5" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="B5" s="31">
         <f>IF(B4=0,"N/A",B3/B4)</f>
         <v>-5.68</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <f>IF(C4=0,"N/A",C3/C4)</f>
         <v>8.09</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <f>IF(D4=0,"N/A",D3/D4)</f>
         <v>27.34</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <f>IF(E4=0,"N/A",E3/E4)</f>
         <v>41.91</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <f>IF(F4=0,"N/A",F3/F4)</f>
         <v>48.12</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+      <c r="A7" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="B8" s="13">
+      <c r="A8" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="B8" s="15">
         <v>52077</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="15">
         <v>365475</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="15">
         <v>1638011</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="15">
         <v>3651505</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="15">
         <v>5979439</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="B9" s="13">
+      <c r="A9" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B9" s="15">
         <v>130953</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="15">
         <v>176632</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="15">
         <v>201853</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="15">
         <v>222567</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="15">
         <v>232220</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="B10" s="31">
+      <c r="A10" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="B10" s="32">
         <f>IF(B9=0,0,B8/B9)</f>
         <v>0.4</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="32">
         <f>IF(C9=0,0,C8/C9)</f>
         <v>2.07</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="32">
         <f>IF(D9=0,0,D8/D9)</f>
         <v>8.11</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="32">
         <f>IF(E9=0,0,E8/E9)</f>
         <v>16.41</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="32">
         <f>IF(F9=0,0,F8/F9)</f>
         <v>25.75</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="B11" s="32">
+      <c r="A11" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B11" s="33">
         <v>12</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="33">
         <v>63</v>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="33">
         <v>247</v>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="33">
         <v>499</v>
       </c>
-      <c r="F11" s="32">
+      <c r="F11" s="33">
         <v>783</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
+      <c r="A13" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="B14" s="33" t="str">
+      <c r="A14" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="B14" s="34" t="str">
         <f>IF(B5&gt;=1.2,"PASS","FAIL")</f>
         <v>FAIL</v>
       </c>
-      <c r="C14" s="34" t="str">
+      <c r="C14" s="35" t="str">
         <f>IF(C5&gt;=1.2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="D14" s="34" t="str">
+      <c r="D14" s="35" t="str">
         <f>IF(D5&gt;=1.2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="E14" s="34" t="str">
+      <c r="E14" s="35" t="str">
         <f>IF(E5&gt;=1.2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="F14" s="34" t="str">
+      <c r="F14" s="35" t="str">
         <f>IF(F5&gt;=1.2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="B15" s="33" t="str">
+      <c r="A15" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="B15" s="34" t="str">
         <f>IF(B10&gt;=2,"PASS","FAIL")</f>
         <v>FAIL</v>
       </c>
-      <c r="C15" s="34" t="str">
+      <c r="C15" s="35" t="str">
         <f>IF(C10&gt;=2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="D15" s="34" t="str">
+      <c r="D15" s="35" t="str">
         <f>IF(D10&gt;=2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="E15" s="34" t="str">
+      <c r="E15" s="35" t="str">
         <f>IF(E10&gt;=2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="F15" s="34" t="str">
+      <c r="F15" s="35" t="str">
         <f>IF(F10&gt;=2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="B16" s="33" t="s">
+      <c r="A16" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="B16" s="34" t="s">
         <v>207</v>
       </c>
-      <c r="D16" s="34" t="s">
+      <c r="C16" s="35" t="s">
+        <v>208</v>
+      </c>
+      <c r="D16" s="35" t="s">
+        <v>208</v>
+      </c>
+      <c r="E16" s="35" t="s">
+        <v>208</v>
+      </c>
+      <c r="F16" s="35" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="B17" s="34" t="s">
         <v>207</v>
       </c>
-      <c r="E16" s="34" t="s">
+      <c r="C17" s="34" t="s">
         <v>207</v>
       </c>
-      <c r="F16" s="34" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="D17" s="35" t="s">
         <v>208</v>
       </c>
-      <c r="B17" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="C17" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="D17" s="34" t="s">
-        <v>207</v>
-      </c>
-      <c r="E17" s="34" t="s">
-        <v>207</v>
-      </c>
-      <c r="F17" s="34" t="s">
-        <v>207</v>
+      <c r="E17" s="35" t="s">
+        <v>208</v>
+      </c>
+      <c r="F17" s="35" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -2570,213 +2591,213 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
-        <v>209</v>
-      </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
+      <c r="A1" s="36" t="s">
+        <v>210</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="36" t="s">
-        <v>210</v>
-      </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
+      <c r="A2" s="37" t="s">
+        <v>211</v>
+      </c>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
+      <c r="A4" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="B5" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="A5" s="6" t="s">
         <v>213</v>
       </c>
+      <c r="B5" s="34" t="s">
+        <v>207</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="B6" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="A6" s="6" t="s">
         <v>215</v>
       </c>
+      <c r="B6" s="34" t="s">
+        <v>207</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="B7" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="C7" s="4" t="s">
+      <c r="A7" s="6" t="s">
         <v>217</v>
       </c>
+      <c r="B7" s="34" t="s">
+        <v>207</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="B8" s="34" t="s">
+      <c r="A8" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>208</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="B9" s="34" t="s">
         <v>207</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="B9" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>220</v>
+      <c r="C9" s="6" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="B10" s="34" t="s">
-        <v>207</v>
-      </c>
-      <c r="C10" s="4" t="s">
+      <c r="A10" s="6" t="s">
         <v>222</v>
       </c>
+      <c r="B10" s="35" t="s">
+        <v>208</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
+      <c r="A12" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="B13" s="5" t="s">
+      <c r="A13" s="6" t="s">
         <v>225</v>
       </c>
+      <c r="B13" s="7" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="B14" s="37" t="s">
+      <c r="A14" s="6" t="s">
         <v>227</v>
       </c>
+      <c r="B14" s="38" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
+      <c r="A16" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>229</v>
+      <c r="A17" s="6" t="s">
+        <v>230</v>
       </c>
       <c r="B17" s="18">
         <v>1288333</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>230</v>
+      <c r="A18" s="6" t="s">
+        <v>231</v>
       </c>
       <c r="B18" s="18">
         <v>1736256</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>231</v>
+      <c r="A19" s="6" t="s">
+        <v>232</v>
       </c>
       <c r="B19" s="18">
         <v>-447923</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="B20" s="38">
+      <c r="A20" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="B20" s="39">
         <v>-0.34767641595767557</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>173</v>
+      <c r="A21" s="6" t="s">
+        <v>174</v>
       </c>
       <c r="B21" s="18">
         <v>500000</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>233</v>
+      <c r="A22" s="6" t="s">
+        <v>234</v>
       </c>
       <c r="B22" s="18">
         <v>52077</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>234</v>
+      <c r="A23" s="6" t="s">
+        <v>235</v>
       </c>
       <c r="B23" s="18">
         <v>500000</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>213</v>
+      <c r="A24" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="B25" s="5" t="s">
+      <c r="A25" s="6" t="s">
         <v>237</v>
       </c>
+      <c r="B25" s="7" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>35</v>
+      <c r="A26" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>239</v>
+      <c r="A27" s="6" t="s">
+        <v>240</v>
       </c>
       <c r="B27" s="18">
         <v>10736</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>240</v>
+      <c r="A28" s="6" t="s">
+        <v>241</v>
       </c>
       <c r="B28" s="18">
         <v>14469</v>
@@ -2809,304 +2830,304 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
+      <c r="A1" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="39" t="s">
-        <v>241</v>
-      </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
+      <c r="A2" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="40" t="s">
-        <v>242</v>
-      </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
+      <c r="A3" s="41" t="s">
+        <v>243</v>
+      </c>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
     </row>
     <row r="4" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="41" t="s">
-        <v>243</v>
-      </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
+      <c r="A4" s="42" t="s">
+        <v>244</v>
+      </c>
+      <c r="B4" s="42"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="6" t="s">
+      <c r="A6" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="C6" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="D6" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="E6" s="8" t="s">
         <v>38</v>
       </c>
+      <c r="F6" s="8" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="32">
+      <c r="A7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="33">
         <f>Assumptions!$B$17</f>
         <v>120</v>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="33">
         <f>Assumptions!$C$17</f>
         <v>200</v>
       </c>
-      <c r="D7" s="32">
+      <c r="D7" s="33">
         <f>Assumptions!$D$17</f>
         <v>300</v>
       </c>
-      <c r="E7" s="32">
+      <c r="E7" s="33">
         <f>Assumptions!$E$17</f>
         <v>375</v>
       </c>
-      <c r="F7" s="32">
+      <c r="F7" s="33">
         <f>Assumptions!$F$17</f>
         <v>400</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="B8" s="26">
+      <c r="A8" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="B8" s="27">
         <f>'5-Year P&amp;L'!B2</f>
         <v>1288333</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="27">
         <f>'5-Year P&amp;L'!C2</f>
         <v>2522800</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="27">
         <f>'5-Year P&amp;L'!D2</f>
         <v>3784600</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="27">
         <f>'5-Year P&amp;L'!E2</f>
         <v>4759125</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="27">
         <f>'5-Year P&amp;L'!F2</f>
         <v>5184400</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B9" s="13">
+      <c r="A9" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B9" s="15">
         <f>'5-Year P&amp;L'!B6</f>
         <v>1736256</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="15">
         <f>'5-Year P&amp;L'!C6</f>
         <v>2209403</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="15">
         <f>'5-Year P&amp;L'!D6</f>
         <v>2512064</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="15">
         <f>'5-Year P&amp;L'!E6</f>
         <v>2745632</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="15">
         <f>'5-Year P&amp;L'!F6</f>
         <v>2856467</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B10" s="22">
+      <c r="A10" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B10" s="23">
         <f>'5-Year P&amp;L'!B7</f>
         <v>-447923</v>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="23">
         <f>'5-Year P&amp;L'!C7</f>
         <v>313398</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="23">
         <f>'5-Year P&amp;L'!D7</f>
         <v>1272536</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="23">
         <f>'5-Year P&amp;L'!E7</f>
         <v>2013494</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="23">
         <f>'5-Year P&amp;L'!F7</f>
         <v>2327934</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="B11" s="12">
+      <c r="A11" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B11" s="14">
         <f>IF(B8=0,0,B10/B8)</f>
         <v>-0.35</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="14">
         <f>IF(C8=0,0,C10/C8)</f>
         <v>0.12</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="14">
         <f>IF(D8=0,0,D10/D8)</f>
         <v>0.34</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="14">
         <f>IF(E8=0,0,E10/E8)</f>
         <v>0.42</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="14">
         <f>IF(F8=0,0,F10/F8)</f>
         <v>0.45</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="B12" s="26">
+      <c r="A12" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="B12" s="27">
         <f>B10</f>
         <v>-447923</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="27">
         <f>B12+C10</f>
         <v>-134525</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="27">
         <f>C12+D10</f>
         <v>1138011</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="27">
         <f>D12+E10</f>
         <v>3151505</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="27">
         <f>E12+F10</f>
         <v>5479439</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="B13" s="26">
+      <c r="A13" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="B13" s="27">
         <v>52077</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="27">
         <v>365475</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="27">
         <v>1638011</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="27">
         <v>3651505</v>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="27">
         <v>5979439</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="B14" s="13">
+      <c r="A14" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="B14" s="15">
         <v>10736</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="15">
         <v>12614</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="15">
         <v>12615</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="15">
         <v>12691</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="15">
         <v>12961</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B15" s="13">
+      <c r="A15" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B15" s="15">
         <v>14469</v>
       </c>
-      <c r="C15" s="13">
+      <c r="C15" s="15">
         <v>11047</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="15">
         <v>8374</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="15">
         <v>7322</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="15">
         <v>7141</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="B16" s="30">
+      <c r="A16" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="B16" s="31">
         <v>-5.68</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="31">
         <v>8.09</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="31">
         <v>27.34</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <v>41.91</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <v>48.12</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="B18" s="41"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
+      <c r="A18" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3142,181 +3163,181 @@
     <row r="1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" ht="10" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" ht="40" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="43" t="s">
+        <v>248</v>
+      </c>
+      <c r="C3" s="43"/>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="44" t="s">
+        <v>249</v>
+      </c>
+      <c r="C4" s="44"/>
+    </row>
+    <row r="6" ht="4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8" s="46" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="47" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="47"/>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="48" t="s">
+        <v>251</v>
+      </c>
+      <c r="C10" s="48"/>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="46" t="s">
+        <v>252</v>
+      </c>
+      <c r="C12" s="49" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="C15" s="5"/>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="C16" s="27">
+        <v>5184400</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="C17" s="27">
+        <v>2327934</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="C18" s="27">
+        <v>5479439</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="C19" s="50" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C22" s="5"/>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="51" t="s">
+        <v>259</v>
+      </c>
+      <c r="C23" s="52"/>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="51" t="s">
+        <v>260</v>
+      </c>
+      <c r="C24" s="52"/>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="51" t="s">
+        <v>261</v>
+      </c>
+      <c r="C25" s="52"/>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="51" t="s">
+        <v>262</v>
+      </c>
+      <c r="C26" s="52"/>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="51" t="s">
+        <v>168</v>
+      </c>
+      <c r="C27" s="52"/>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" s="51" t="s">
+        <v>263</v>
+      </c>
+      <c r="C28" s="52"/>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="51" t="s">
+        <v>264</v>
+      </c>
+      <c r="C29" s="52"/>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="51" t="s">
+        <v>265</v>
+      </c>
+      <c r="C30" s="52"/>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="51" t="s">
+        <v>266</v>
+      </c>
+      <c r="C31" s="52"/>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="51" t="s">
+        <v>267</v>
+      </c>
+      <c r="C32" s="52"/>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="51" t="s">
+        <v>268</v>
+      </c>
+      <c r="C33" s="52"/>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B34" s="51" t="s">
+        <v>269</v>
+      </c>
+      <c r="C34" s="52"/>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B35" s="51" t="s">
+        <v>270</v>
+      </c>
+      <c r="C35" s="52"/>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B36" s="51" t="s">
+        <v>271</v>
+      </c>
+      <c r="C36" s="52"/>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="42" t="s">
         <v>247</v>
       </c>
-      <c r="C3" s="42"/>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="43" t="s">
-        <v>248</v>
-      </c>
-      <c r="C4" s="43"/>
-    </row>
-    <row r="6" ht="4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-    </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="45" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="46" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="46"/>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="47" t="s">
-        <v>250</v>
-      </c>
-      <c r="C10" s="47"/>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="45" t="s">
-        <v>251</v>
-      </c>
-      <c r="C12" s="48" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C15" s="3"/>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="C16" s="26">
-        <v>5184400</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="C17" s="26">
-        <v>2327934</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="C18" s="26">
-        <v>5479439</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="C19" s="49" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="C22" s="3"/>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="50" t="s">
-        <v>258</v>
-      </c>
-      <c r="C23" s="51"/>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="50" t="s">
-        <v>259</v>
-      </c>
-      <c r="C24" s="51"/>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="50" t="s">
-        <v>260</v>
-      </c>
-      <c r="C25" s="51"/>
-    </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="50" t="s">
-        <v>261</v>
-      </c>
-      <c r="C26" s="51"/>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="50" t="s">
-        <v>167</v>
-      </c>
-      <c r="C27" s="51"/>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="50" t="s">
-        <v>262</v>
-      </c>
-      <c r="C28" s="51"/>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="50" t="s">
-        <v>263</v>
-      </c>
-      <c r="C29" s="51"/>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="50" t="s">
-        <v>264</v>
-      </c>
-      <c r="C30" s="51"/>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="50" t="s">
-        <v>265</v>
-      </c>
-      <c r="C31" s="51"/>
-    </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="50" t="s">
-        <v>266</v>
-      </c>
-      <c r="C32" s="51"/>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="50" t="s">
-        <v>267</v>
-      </c>
-      <c r="C33" s="51"/>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="50" t="s">
-        <v>268</v>
-      </c>
-      <c r="C34" s="51"/>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="50" t="s">
-        <v>269</v>
-      </c>
-      <c r="C35" s="51"/>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B36" s="50" t="s">
-        <v>270</v>
-      </c>
-      <c r="C36" s="51"/>
-    </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B39" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="C39" s="41"/>
+      <c r="C39" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3360,246 +3381,246 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="A1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="E1" s="8" t="s">
         <v>38</v>
       </c>
+      <c r="F1" s="8" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="10">
+      <c r="A2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="12">
         <v>120</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="12">
         <v>200</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="12">
         <v>300</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="12">
         <v>375</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="12">
         <v>400</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="11" t="s">
+      <c r="A3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="12">
+      <c r="B3" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="14">
         <f>IF(B2=0,"-",(C2-B2)/B2)</f>
         <v>0.67</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="14">
         <f>IF(C2=0,"-",(D2-C2)/C2)</f>
         <v>0.5</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="14">
         <f>IF(D2=0,"-",(E2-D2)/D2)</f>
         <v>0.25</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="14">
         <f>IF(E2=0,"-",(F2-E2)/E2)</f>
         <v>0.07</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="12">
+      <c r="A4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="14">
         <v>0.3</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="14">
         <v>0.5</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="14">
         <v>0.75</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="14">
         <v>0.9375</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+      <c r="A6" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="13">
+      <c r="A7" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="15">
         <v>9500</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="15">
         <v>9690</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="15">
         <v>9884</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="15">
         <v>10081</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="15">
         <v>10283</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="13">
+      <c r="A8" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="15">
         <v>800</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="15">
         <v>816</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="15">
         <v>832</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="15">
         <v>849</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="15">
         <v>866</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="13">
+      <c r="A9" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="15">
         <v>1200</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="15">
         <v>1224</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="15">
         <v>1248</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="15">
         <v>1273</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="15">
         <v>1299</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="13">
+      <c r="A10" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="15">
         <v>300</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="15">
         <v>309</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="15">
         <v>318</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="15">
         <v>328</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="15">
         <v>338</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
+      <c r="A12" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="13">
+      <c r="A13" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="15">
         <v>1380000</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="15">
         <v>2346000</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="15">
         <v>3589200</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="15">
         <v>4576125</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="15">
         <v>4979200</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="13">
+      <c r="A14" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="15">
         <v>130000</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="15">
         <v>115000</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="15">
         <v>100000</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="15">
         <v>60000</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="15">
         <v>70000</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="13">
+      <c r="A15" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" s="15">
         <v>36000</v>
       </c>
-      <c r="C15" s="13">
+      <c r="C15" s="15">
         <v>61800</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="15">
         <v>95400</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="15">
         <v>123000</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="15">
         <v>135200</v>
       </c>
     </row>
@@ -3626,316 +3647,316 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="A1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="E1" s="8" t="s">
         <v>38</v>
       </c>
+      <c r="F1" s="8" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="10">
+      <c r="A2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="12">
         <f>Assumptions!$B$17</f>
         <v>120</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="12">
         <f>Assumptions!$C$17</f>
         <v>200</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="12">
         <f>Assumptions!$D$17</f>
         <v>300</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="12">
         <f>Assumptions!$E$17</f>
         <v>375</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="12">
         <f>Assumptions!$F$17</f>
         <v>400</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
+      <c r="A3" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="13">
+      <c r="A4" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="15">
         <f>ROUND(Assumptions!$B$17*9500,0)</f>
         <v>1140000</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="15">
         <f>ROUND(Assumptions!$C$17*9690,0)</f>
         <v>1938000</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="15">
         <f>ROUND(Assumptions!$D$17*9884,0)</f>
         <v>2965200</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="15">
         <f>ROUND(Assumptions!$E$17*10081,0)</f>
         <v>3780375</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="15">
         <f>ROUND(Assumptions!$F$17*10283,0)</f>
         <v>4113200</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="13">
+      <c r="A5" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="15">
         <f>ROUND(Assumptions!$B$17*800,0)</f>
         <v>96000</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="15">
         <f>ROUND(Assumptions!$C$17*816,0)</f>
         <v>163200</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="15">
         <f>ROUND(Assumptions!$D$17*832,0)</f>
         <v>249600</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="15">
         <f>ROUND(Assumptions!$E$17*849,0)</f>
         <v>318375</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="15">
         <f>ROUND(Assumptions!$F$17*866,0)</f>
         <v>346400</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B6" s="13">
+      <c r="A6" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="15">
         <f>ROUND(Assumptions!$B$17*1200,0)</f>
         <v>144000</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="15">
         <f>ROUND(Assumptions!$C$17*1224,0)</f>
         <v>244800</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="15">
         <f>ROUND(Assumptions!$D$17*1248,0)</f>
         <v>374400</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="15">
         <f>ROUND(Assumptions!$E$17*1273,0)</f>
         <v>477375</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="15">
         <f>ROUND(Assumptions!$F$17*1299,0)</f>
         <v>519600</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B7" s="14">
+      <c r="A7" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="16">
         <f>SUM(B4:B6)</f>
         <v>1380000</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="16">
         <f>SUM(C4:C6)</f>
         <v>2346000</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="16">
         <f>SUM(D4:D6)</f>
         <v>3589200</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="16">
         <f>SUM(E4:E6)</f>
         <v>4576125</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="16">
         <f>SUM(F4:F6)</f>
         <v>4979200</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+      <c r="A8" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9" s="13">
+      <c r="A9" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="15">
         <v>100000</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="15">
         <v>75000</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="15">
         <v>50000</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="15">
         <v>0</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B10" s="13">
+      <c r="A10" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="15">
         <v>30000</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="15">
         <v>40000</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="15">
         <v>50000</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="15">
         <v>60000</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="15">
         <v>70000</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B11" s="14">
+      <c r="A11" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="16">
         <f>SUM(B9:B10)</f>
         <v>130000</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="16">
         <f>SUM(C9:C10)</f>
         <v>115000</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="16">
         <f>SUM(D9:D10)</f>
         <v>100000</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="16">
         <f>SUM(E9:E10)</f>
         <v>60000</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="16">
         <f>SUM(F9:F10)</f>
         <v>70000</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
+      <c r="A12" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B13" s="13">
+      <c r="A13" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="15">
         <f>ROUND(Assumptions!$B$17*300,0)</f>
         <v>36000</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="15">
         <f>ROUND(Assumptions!$C$17*309,0)</f>
         <v>61800</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="15">
         <f>ROUND(Assumptions!$D$17*318,0)</f>
         <v>95400</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="15">
         <f>ROUND(Assumptions!$E$17*328,0)</f>
         <v>123000</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="15">
         <f>ROUND(Assumptions!$F$17*338,0)</f>
         <v>135200</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B14" s="14">
+      <c r="A14" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="16">
         <f>SUM(B13:B13)</f>
         <v>36000</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="16">
         <f>SUM(C13:C13)</f>
         <v>61800</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="16">
         <f>SUM(D13:D13)</f>
         <v>95400</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="16">
         <f>SUM(E13:E13)</f>
         <v>123000</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="16">
         <f>SUM(F13:F13)</f>
         <v>135200</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B16" s="14">
+      <c r="A16" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="16">
         <f>B7+B11+B14</f>
         <v>1546000</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="16">
         <f>C7+C11+C14</f>
         <v>2522800</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="16">
         <f>D7+D11+D14</f>
         <v>3784600</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="16">
         <f>E7+E11+E14</f>
         <v>4759125</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="16">
         <f>F7+F11+F14</f>
         <v>5184400</v>
       </c>
@@ -3964,7 +3985,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3975,51 +3996,51 @@
       <c r="H1" s="1"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="A3" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="C3" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="D3" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="E3" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="F3" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="G3" s="8" t="s">
         <v>72</v>
       </c>
+      <c r="H3" s="8" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="B4" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="15">
+      <c r="C4" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="11">
         <v>1</v>
       </c>
-      <c r="E4" s="16">
+      <c r="E4" s="17">
         <v>110000</v>
       </c>
-      <c r="F4" s="17">
+      <c r="F4" s="10">
         <v>0.28</v>
       </c>
-      <c r="G4" s="17">
+      <c r="G4" s="10">
         <v>0.0765</v>
       </c>
       <c r="H4" s="18">
@@ -4027,25 +4048,25 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D5" s="15">
+      <c r="D5" s="11">
         <v>1</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="17">
         <v>90000</v>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="10">
         <v>0.28</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="10">
         <v>0.0765</v>
       </c>
       <c r="H5" s="18">
@@ -4053,25 +4074,25 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="A6" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D6" s="15">
+      <c r="C6" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="11">
         <v>1</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="17">
         <v>72000</v>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="10">
         <v>0.28</v>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="10">
         <v>0.0765</v>
       </c>
       <c r="H6" s="18">
@@ -4079,25 +4100,25 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" s="4" t="s">
+      <c r="A7" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D7" s="15">
+      <c r="B7" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="11">
         <v>6</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="17">
         <v>52000</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="10">
         <v>0.28</v>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="10">
         <v>0.0765</v>
       </c>
       <c r="H7" s="18">
@@ -4105,25 +4126,25 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D8" s="15">
+      <c r="C8" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="11">
         <v>1</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="17">
         <v>55000</v>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="10">
         <v>0.28</v>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="10">
         <v>0.0765</v>
       </c>
       <c r="H8" s="18">
@@ -4131,25 +4152,25 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" s="15">
+      <c r="A9" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" s="11">
         <v>3</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="17">
         <v>30000</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="10">
         <v>0.2</v>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="10">
         <v>0.0765</v>
       </c>
       <c r="H9" s="18">
@@ -4157,25 +4178,25 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B10" s="4" t="s">
+      <c r="A10" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D10" s="15">
+      <c r="B10" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" s="11">
         <v>1</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="17">
         <v>55000</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="10">
         <v>0.28</v>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="10">
         <v>0.0765</v>
       </c>
       <c r="H10" s="18">
@@ -4183,25 +4204,25 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B11" s="4" t="s">
+      <c r="A11" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D11" s="15">
+      <c r="B11" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" s="11">
         <v>1</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="17">
         <v>55000</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="10">
         <v>0.28</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="10">
         <v>0.0765</v>
       </c>
       <c r="H11" s="18">
@@ -4209,25 +4230,25 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B12" s="4" t="s">
+      <c r="A12" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D12" s="15">
+      <c r="B12" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="11">
         <v>2</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="17">
         <v>38000</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="10">
         <v>0.25</v>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="10">
         <v>0.0765</v>
       </c>
       <c r="H12" s="18">
@@ -4235,126 +4256,126 @@
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
+      <c r="A14" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B15" s="5">
+      <c r="A15" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" s="7">
         <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B16" s="5">
+      <c r="A16" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" s="7">
         <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>91</v>
+      <c r="A17" s="6" t="s">
+        <v>92</v>
       </c>
       <c r="B17" s="19">
         <v>915000</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>92</v>
+      <c r="A18" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="B18" s="19">
         <v>246720</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>93</v>
+      <c r="A19" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="B19" s="19">
         <v>69998</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>94</v>
+      <c r="A20" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="B20" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>95</v>
+      <c r="A21" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="B21" s="18">
         <v>1231718</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
+      <c r="A23" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
     </row>
     <row r="24" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" s="6" t="s">
+      <c r="A24" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="C24" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="D24" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="E24" s="8" t="s">
         <v>38</v>
       </c>
+      <c r="F24" s="8" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B25" s="13">
+      <c r="A25" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B25" s="15">
         <v>1231718</v>
       </c>
-      <c r="C25" s="13">
+      <c r="C25" s="15">
         <v>1231718</v>
       </c>
-      <c r="D25" s="13">
+      <c r="D25" s="15">
         <v>1231718</v>
       </c>
-      <c r="E25" s="13">
+      <c r="E25" s="15">
         <v>1231718</v>
       </c>
-      <c r="F25" s="13">
+      <c r="F25" s="15">
         <v>1231718</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>98</v>
+      <c r="A26" s="6" t="s">
+        <v>99</v>
       </c>
       <c r="B26" s="20">
         <f>(1+Assumptions!$B$20)^0</f>
@@ -4378,8 +4399,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>99</v>
+      <c r="A27" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="B27" s="21">
         <f>Assumptions!$B$22</f>
@@ -4399,26 +4420,26 @@
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B28" s="14">
+      <c r="A28" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B28" s="16">
         <f>B25*B26*B27</f>
         <v>1026431</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="16">
         <f>C25*C26*C27</f>
         <v>1231718</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="16">
         <f>D25*D26*D27</f>
         <v>1231718</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E28" s="16">
         <f>E25*E26*E27</f>
         <v>1231718</v>
       </c>
-      <c r="F28" s="14">
+      <c r="F28" s="16">
         <f>F25*F26*F27</f>
         <v>1231718</v>
       </c>
@@ -4449,311 +4470,311 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="A1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="E1" s="8" t="s">
         <v>38</v>
       </c>
+      <c r="F1" s="8" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="A2" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" s="13">
+      <c r="A3" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" s="15">
         <f>ROUND(Assumptions!$B$17*700,0)</f>
         <v>84000</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="15">
         <f>ROUND(Assumptions!$C$17*721,0)</f>
         <v>144200</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="15">
         <f>ROUND(Assumptions!$D$17*743,0)</f>
         <v>222900</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="15">
         <f>ROUND(Assumptions!$E$17*765,0)</f>
         <v>286875</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="15">
         <f>ROUND(Assumptions!$F$17*788,0)</f>
         <v>315200</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B4" s="14">
+      <c r="A4" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" s="16">
         <f>SUM(B3:B3)</f>
         <v>84000</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="16">
         <f>SUM(C3:C3)</f>
         <v>144200</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="16">
         <f>SUM(D3:D3)</f>
         <v>222900</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="16">
         <f>SUM(E3:E3)</f>
         <v>286875</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="16">
         <f>SUM(F3:F3)</f>
         <v>315200</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+      <c r="A5" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B6" s="13">
+      <c r="A6" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" s="15">
         <f>ROUND(Assumptions!$B$17*500,0)</f>
         <v>60000</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="15">
         <f>ROUND(Assumptions!$C$17*515,0)</f>
         <v>103000</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="15">
         <f>ROUND(Assumptions!$D$17*530,0)</f>
         <v>159000</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="15">
         <f>ROUND(Assumptions!$E$17*546,0)</f>
         <v>204750</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="15">
         <f>ROUND(Assumptions!$F$17*562,0)</f>
         <v>224800</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B7" s="14">
+      <c r="A7" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="16">
         <f>SUM(B6:B6)</f>
         <v>60000</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="16">
         <f>SUM(C6:C6)</f>
         <v>103000</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="16">
         <f>SUM(D6:D6)</f>
         <v>159000</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="16">
         <f>SUM(E6:E6)</f>
         <v>204750</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="16">
         <f>SUM(F6:F6)</f>
         <v>224800</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+      <c r="A8" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B9" s="13">
+      <c r="A9" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B9" s="15">
         <v>25000</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="15">
         <v>25750</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="15">
         <v>26523</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="15">
         <v>27318</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="15">
         <v>28138</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B10" s="13">
+      <c r="A10" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B10" s="15">
         <v>15000</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="15">
         <v>15450</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="15">
         <v>15914</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="15">
         <v>16391</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="15">
         <v>16883</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B11" s="13">
+      <c r="A11" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B11" s="15">
         <v>20000</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="15">
         <v>20600</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="15">
         <v>21218</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="15">
         <v>21855</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="15">
         <v>22510</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B12" s="13">
+      <c r="A12" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B12" s="15">
         <f>ROUND(Assumptions!$B$17*800,0)</f>
         <v>96000</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="15">
         <f>ROUND(Assumptions!$C$17*824,0)</f>
         <v>164800</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="15">
         <f>ROUND(Assumptions!$D$17*849,0)</f>
         <v>254700</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="15">
         <f>ROUND(Assumptions!$E$17*874,0)</f>
         <v>327750</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="15">
         <f>ROUND(Assumptions!$F$17*900,0)</f>
         <v>360000</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B13" s="13">
+      <c r="A13" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B13" s="15">
         <f>ROUND(Assumptions!$B$17*600,0)</f>
         <v>72000</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="15">
         <f>ROUND(Assumptions!$C$17*618,0)</f>
         <v>123600</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="15">
         <f>ROUND(Assumptions!$D$17*637,0)</f>
         <v>191100</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="15">
         <f>ROUND(Assumptions!$E$17*656,0)</f>
         <v>246000</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="15">
         <f>ROUND(Assumptions!$F$17*675,0)</f>
         <v>270000</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B14" s="14">
+      <c r="A14" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" s="16">
         <f>SUM(B9:B13)</f>
         <v>228000</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="16">
         <f>SUM(C9:C13)</f>
         <v>350200</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="16">
         <f>SUM(D9:D13)</f>
         <v>509455</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="16">
         <f>SUM(E9:E13)</f>
         <v>639314</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="16">
         <f>SUM(F9:F13)</f>
         <v>697531</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B16" s="14">
+      <c r="A16" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" s="16">
         <f>B4+B7+B14</f>
         <v>372000</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="16">
         <f>C4+C7+C14</f>
         <v>597400</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="16">
         <f>D4+D7+D14</f>
         <v>891355</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="16">
         <f>E4+E7+E14</f>
         <v>1130939</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="16">
         <f>F4+F7+F14</f>
         <v>1237531</v>
       </c>
@@ -4781,177 +4802,177 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="A1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="E1" s="8" t="s">
         <v>38</v>
       </c>
+      <c r="F1" s="8" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="A2" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B3" s="13">
+      <c r="A3" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B3" s="15">
         <v>216000</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="15">
         <v>222480</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="15">
         <v>229154</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="15">
         <v>236029</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="15">
         <v>243110</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B4" s="13">
+      <c r="A4" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B4" s="15">
         <v>30000</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="15">
         <v>30900</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="15">
         <v>31824</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="15">
         <v>32784</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="15">
         <v>33768</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B5" s="13">
+      <c r="A5" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B5" s="15">
         <v>18000</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="15">
         <v>18540</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="15">
         <v>19096</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="15">
         <v>19669</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="15">
         <v>20259</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B6" s="13">
+      <c r="A6" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B6" s="15">
         <v>18000</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="15">
         <v>18540</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="15">
         <v>19092</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="15">
         <v>19668</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="15">
         <v>20256</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="B7" s="14">
+      <c r="A7" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="16">
         <f>SUM(B3:B6)</f>
         <v>282000</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="16">
         <f>SUM(C3:C6)</f>
         <v>290460</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="16">
         <f>SUM(D3:D6)</f>
         <v>299166</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="16">
         <f>SUM(E3:E6)</f>
         <v>308150</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="16">
         <f>SUM(F3:F6)</f>
         <v>317393</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B9" s="13">
+      <c r="A9" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B9" s="15">
         <v>2350</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="15">
         <v>1452</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="15">
         <v>997</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="15">
         <v>822</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="15">
         <v>793</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B10" s="12">
+      <c r="A10" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" s="14">
         <v>0.21888750812095942</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="14">
         <v>0.1151339781195497</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="14">
         <v>0.07904835385509698</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="14">
         <v>0.06474930412628371</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="14">
         <v>0.06122075900007716</v>
       </c>
     </row>
@@ -4979,124 +5000,124 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B3" s="3"/>
+      <c r="A3" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B3" s="5"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B4" s="16">
+      <c r="A4" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B5" s="16">
+      <c r="A5" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5" s="22">
         <v>500000</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B6" s="22">
+      <c r="A6" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" s="23">
         <f>SUM(B4:B5)</f>
         <v>500000</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B8" s="3"/>
+      <c r="A8" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" s="5"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="B9" s="16">
+      <c r="A9" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B9" s="22">
         <v>47000</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B10" s="16">
+      <c r="A10" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B10" s="22">
         <v>30000</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B11" s="16">
+      <c r="A11" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B11" s="22">
         <v>84000</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="B12" s="16">
+      <c r="A12" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B12" s="22">
         <v>75000</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B13" s="16">
+      <c r="A13" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B13" s="22">
         <v>40000</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B14" s="16">
+      <c r="A14" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B14" s="22">
         <v>261905</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B15" s="16">
+      <c r="A15" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B15" s="22">
         <v>26895</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="B16" s="22">
+      <c r="A16" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B16" s="23">
         <f>SUM(B9:B15)</f>
         <v>564800</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="B18" s="23">
+      <c r="A18" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="B18" s="24">
         <f>B6-B16</f>
         <v>-64800</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="24" t="s">
-        <v>138</v>
+      <c r="A19" s="25" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -5128,7 +5149,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5138,134 +5159,134 @@
       <c r="G1" s="1"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" s="6" t="s">
+      <c r="A3" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="B3" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="D3" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="E3" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="F3" s="8" t="s">
         <v>145</v>
       </c>
+      <c r="G3" s="8" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B4" s="13">
+      <c r="A4" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B4" s="17">
         <v>500000</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="10">
         <v>0.0575</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="26">
         <v>15</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="15">
         <v>49825</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="15">
         <v>4152</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="15">
         <v>247369</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+      <c r="A6" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>148</v>
+      <c r="A7" s="7" t="s">
+        <v>149</v>
       </c>
       <c r="B7" s="18">
         <v>49825</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>149</v>
+      <c r="A8" s="6" t="s">
+        <v>150</v>
       </c>
       <c r="B8" s="19">
         <v>4152</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
+      <c r="A10" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B11" s="6" t="s">
+      <c r="A11" s="8" t="s">
         <v>152</v>
       </c>
+      <c r="B11" s="8" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="13">
+      <c r="A12" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="15">
         <v>478925</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="13">
+      <c r="A13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="15">
         <v>456639</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="13">
+      <c r="A14" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="15">
         <v>433071</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="13">
+      <c r="A15" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="15">
         <v>408148</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" s="13">
+      <c r="A16" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="15">
         <v>381792</v>
       </c>
     </row>
@@ -5296,429 +5317,429 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="D1" s="6" t="s">
+      <c r="A1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="E1" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="F1" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="G1" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="H1" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="I1" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="J1" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="K1" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="L1" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="M1" s="8" t="s">
         <v>164</v>
       </c>
+      <c r="N1" s="8" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="B2" s="13">
+      <c r="A2" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="B2" s="15">
         <v>154600</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="15">
         <v>154600</v>
       </c>
-      <c r="D2" s="13">
+      <c r="D2" s="15">
         <v>154600</v>
       </c>
-      <c r="E2" s="13">
+      <c r="E2" s="15">
         <v>154600</v>
       </c>
-      <c r="F2" s="13">
+      <c r="F2" s="15">
         <v>154600</v>
       </c>
-      <c r="G2" s="13">
+      <c r="G2" s="15">
         <v>154600</v>
       </c>
-      <c r="H2" s="13">
+      <c r="H2" s="15">
         <v>154600</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="15">
         <v>154600</v>
       </c>
-      <c r="J2" s="13">
+      <c r="J2" s="15">
         <v>154600</v>
       </c>
-      <c r="K2" s="13">
+      <c r="K2" s="15">
         <v>-103067</v>
       </c>
-      <c r="L2" s="13">
+      <c r="L2" s="15">
         <v>0</v>
       </c>
-      <c r="M2" s="13">
+      <c r="M2" s="15">
         <v>0</v>
       </c>
-      <c r="N2" s="26">
+      <c r="N2" s="27">
         <f>SUM(B2:M2)</f>
         <v>1288333</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="B3" s="13">
+      <c r="A3" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B3" s="15">
         <v>102643</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="15">
         <v>102643</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="15">
         <v>102643</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="15">
         <v>102643</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="15">
         <v>102643</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="15">
         <v>102643</v>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="15">
         <v>102643</v>
       </c>
-      <c r="I3" s="13">
+      <c r="I3" s="15">
         <v>102643</v>
       </c>
-      <c r="J3" s="13">
+      <c r="J3" s="15">
         <v>102643</v>
       </c>
-      <c r="K3" s="13">
+      <c r="K3" s="15">
         <v>102644</v>
       </c>
-      <c r="L3" s="13">
+      <c r="L3" s="15">
         <v>0</v>
       </c>
-      <c r="M3" s="13">
+      <c r="M3" s="15">
         <v>0</v>
       </c>
-      <c r="N3" s="13">
+      <c r="N3" s="15">
         <f>SUM(B3:M3)</f>
         <v>1026431</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B4" s="13">
+      <c r="A4" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" s="15">
         <v>54500</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="15">
         <v>54500</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="15">
         <v>54500</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="15">
         <v>54500</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="15">
         <v>54500</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="15">
         <v>54500</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="15">
         <v>54500</v>
       </c>
-      <c r="I4" s="13">
+      <c r="I4" s="15">
         <v>54500</v>
       </c>
-      <c r="J4" s="13">
+      <c r="J4" s="15">
         <v>54500</v>
       </c>
-      <c r="K4" s="13">
+      <c r="K4" s="15">
         <v>54500</v>
       </c>
-      <c r="L4" s="13">
+      <c r="L4" s="15">
         <v>0</v>
       </c>
-      <c r="M4" s="13">
+      <c r="M4" s="15">
         <v>0</v>
       </c>
-      <c r="N4" s="13">
+      <c r="N4" s="15">
         <f>SUM(B4:M4)</f>
         <v>545000</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="B5" s="13">
+      <c r="A5" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="B5" s="15">
         <v>13735</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="15">
         <v>13735</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="15">
         <v>13735</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="15">
         <v>13735</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="15">
         <v>13735</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="15">
         <v>13735</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="15">
         <v>13735</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="15">
         <v>13735</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="15">
         <v>13735</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="15">
         <v>13735</v>
       </c>
-      <c r="L5" s="13">
+      <c r="L5" s="15">
         <v>13735</v>
       </c>
-      <c r="M5" s="13">
+      <c r="M5" s="15">
         <v>13740</v>
       </c>
-      <c r="N5" s="13">
+      <c r="N5" s="15">
         <f>SUM(B5:M5)</f>
         <v>164825</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="B6" s="22">
+      <c r="A6" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B6" s="23">
         <f>SUM(B3:B5)</f>
         <v>170878</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="23">
         <f>SUM(C3:C5)</f>
         <v>170878</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="23">
         <f>SUM(D3:D5)</f>
         <v>170878</v>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="23">
         <f>SUM(E3:E5)</f>
         <v>170878</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="23">
         <f>SUM(F3:F5)</f>
         <v>170878</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="23">
         <f>SUM(G3:G5)</f>
         <v>170878</v>
       </c>
-      <c r="H6" s="22">
+      <c r="H6" s="23">
         <f>SUM(H3:H5)</f>
         <v>170878</v>
       </c>
-      <c r="I6" s="22">
+      <c r="I6" s="23">
         <f>SUM(I3:I5)</f>
         <v>170878</v>
       </c>
-      <c r="J6" s="22">
+      <c r="J6" s="23">
         <f>SUM(J3:J5)</f>
         <v>170878</v>
       </c>
-      <c r="K6" s="22">
+      <c r="K6" s="23">
         <f>SUM(K3:K5)</f>
         <v>170879</v>
       </c>
-      <c r="L6" s="22">
+      <c r="L6" s="23">
         <f>SUM(L3:L5)</f>
         <v>13735</v>
       </c>
-      <c r="M6" s="22">
+      <c r="M6" s="23">
         <f>SUM(M3:M5)</f>
         <v>13740</v>
       </c>
-      <c r="N6" s="22">
+      <c r="N6" s="23">
         <f>SUM(B6:M6)</f>
         <v>1736256</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="B7" s="26">
+      <c r="A7" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="B7" s="27">
         <f>B2-B6</f>
         <v>-16278</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="27">
         <f>C2-C6</f>
         <v>-16278</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="27">
         <f>D2-D6</f>
         <v>-16278</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="27">
         <f>E2-E6</f>
         <v>-16278</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="27">
         <f>F2-F6</f>
         <v>-16278</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="27">
         <f>G2-G6</f>
         <v>-16278</v>
       </c>
-      <c r="H7" s="26">
+      <c r="H7" s="27">
         <f>H2-H6</f>
         <v>-16278</v>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="27">
         <f>I2-I6</f>
         <v>-16278</v>
       </c>
-      <c r="J7" s="26">
+      <c r="J7" s="27">
         <f>J2-J6</f>
         <v>-16278</v>
       </c>
-      <c r="K7" s="26">
+      <c r="K7" s="27">
         <f>K2-K6</f>
         <v>-273946</v>
       </c>
-      <c r="L7" s="26">
+      <c r="L7" s="27">
         <f>L2-L6</f>
         <v>-13735</v>
       </c>
-      <c r="M7" s="26">
+      <c r="M7" s="27">
         <f>M2-M6</f>
         <v>-13740</v>
       </c>
-      <c r="N7" s="26">
+      <c r="N7" s="27">
         <f>SUM(B7:M7)</f>
         <v>-447923</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="B8" s="26">
+      <c r="A8" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B8" s="27">
         <f>500000+B7</f>
         <v>483722</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="27">
         <f>B8+C7</f>
         <v>467444</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="27">
         <f>C8+D7</f>
         <v>451166</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="27">
         <f>D8+E7</f>
         <v>434888</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="27">
         <f>E8+F7</f>
         <v>418610</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="27">
         <f>F8+G7</f>
         <v>402332</v>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="27">
         <f>G8+H7</f>
         <v>386054</v>
       </c>
-      <c r="I8" s="26">
+      <c r="I8" s="27">
         <f>H8+I7</f>
         <v>369776</v>
       </c>
-      <c r="J8" s="26">
+      <c r="J8" s="27">
         <f>I8+J7</f>
         <v>353498</v>
       </c>
-      <c r="K8" s="26">
+      <c r="K8" s="27">
         <f>J8+K7</f>
         <v>79552</v>
       </c>
-      <c r="L8" s="26">
+      <c r="L8" s="27">
         <f>K8+L7</f>
         <v>65817</v>
       </c>
-      <c r="M8" s="26">
+      <c r="M8" s="27">
         <f>L8+M7</f>
         <v>52077</v>
       </c>
-      <c r="N8" s="26">
+      <c r="N8" s="27">
         <f>M8</f>
         <v>52077</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
+      <c r="A10" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>173</v>
+      <c r="A11" s="6" t="s">
+        <v>174</v>
       </c>
       <c r="B11" s="19">
         <v>500000</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>174</v>
+      <c r="A12" s="6" t="s">
+        <v>175</v>
       </c>
       <c r="B12" s="18">
         <f>M8</f>
@@ -5726,8 +5747,8 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>175</v>
+      <c r="A13" s="6" t="s">
+        <v>176</v>
       </c>
       <c r="B13" s="19">
         <f>MIN(B8:M8)</f>

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
@@ -19,6 +19,7 @@
     <sheet sheetId="13" name="Underwriting Snapshot" state="visible" r:id="rId16"/>
     <sheet sheetId="14" name="Summary" state="visible" r:id="rId17"/>
     <sheet sheetId="15" name="Cover" state="visible" r:id="rId18"/>
+    <sheet sheetId="16" name="Financial Health" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Assumptions'!$A1:$F23</definedName>
@@ -49,13 +50,15 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'Underwriting Snapshot'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'Summary'!$A1:$F18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="13">'Summary'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'Financial Health'!$A1:$H35</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="15">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="323">
   <si>
     <t>SchoolStack - Assumptions &amp; Drivers</t>
   </si>
@@ -871,6 +874,159 @@
   </si>
   <si>
     <t>Summary</t>
+  </si>
+  <si>
+    <t>Civic Scholars Charter — Financial Health Dashboard</t>
+  </si>
+  <si>
+    <t>Generated March 26, 2026</t>
+  </si>
+  <si>
+    <t>● Green = healthy</t>
+  </si>
+  <si>
+    <t>◐ Yellow = monitor</t>
+  </si>
+  <si>
+    <t>○ Red = action needed</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Benchmark</t>
+  </si>
+  <si>
+    <t>Enrollment</t>
+  </si>
+  <si>
+    <t>Ending Cash</t>
+  </si>
+  <si>
+    <t>Net Margin</t>
+  </si>
+  <si>
+    <t>≥ $10,000</t>
+  </si>
+  <si>
+    <t>Payroll %</t>
+  </si>
+  <si>
+    <t>≤ 55%</t>
+  </si>
+  <si>
+    <t>Facility %</t>
+  </si>
+  <si>
+    <t>≤ 15%</t>
+  </si>
+  <si>
+    <t>Operating Margin</t>
+  </si>
+  <si>
+    <t>≥ 10%</t>
+  </si>
+  <si>
+    <t>Revenue Sources</t>
+  </si>
+  <si>
+    <t>≥ 3 sources</t>
+  </si>
+  <si>
+    <t>≥ 1.25x</t>
+  </si>
+  <si>
+    <t>Break-even Year</t>
+  </si>
+  <si>
+    <t>Cash Runway</t>
+  </si>
+  <si>
+    <t>60+ months</t>
+  </si>
+  <si>
+    <t>FINANCIAL HEALTH SIGNALS</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Assessment</t>
+  </si>
+  <si>
+    <t>Watch Item</t>
+  </si>
+  <si>
+    <t>Viability</t>
+  </si>
+  <si>
+    <t>● Healthy</t>
+  </si>
+  <si>
+    <t>The model reaches net income early and sustains strong margins through Year 5.</t>
+  </si>
+  <si>
+    <t>Monitor enrollment actuals vs. projections in Year 1.</t>
+  </si>
+  <si>
+    <t>Liquidity</t>
+  </si>
+  <si>
+    <t>Cash stays positive throughout the projection and reserves exceed 3 months of expenses.</t>
+  </si>
+  <si>
+    <t>Maintain reserves as a buffer against seasonal revenue dips.</t>
+  </si>
+  <si>
+    <t>Staffing Burden</t>
+  </si>
+  <si>
+    <t>Staffing at 24% of revenue leaves room for facilities, programs, and reserves.</t>
+  </si>
+  <si>
+    <t>As you add staff, ensure staffing stays below 60% of revenue.</t>
+  </si>
+  <si>
+    <t>Facility Burden</t>
+  </si>
+  <si>
+    <t>Facility costs at 9% of revenue are well-managed and leave budget for programs.</t>
+  </si>
+  <si>
+    <t>Watch for rent escalation clauses that could push this higher over time.</t>
+  </si>
+  <si>
+    <t>Debt Affordability</t>
+  </si>
+  <si>
+    <t>DSCR of 34.34x provides comfortable coverage of debt payments with room to spare.</t>
+  </si>
+  <si>
+    <t>Maintain this ratio as you take on any additional debt.</t>
+  </si>
+  <si>
+    <t>Revenue Concentration</t>
+  </si>
+  <si>
+    <t>Revenue is anchored to enrollment-driven income — the strongest foundation for a school model. A focused revenue stream is a strength when backed by dependable demand.</t>
+  </si>
+  <si>
+    <t>Continue to pressure-test enrollment assumptions: recruitment pipeline, waitlist depth, retention rates, and collection reliability.</t>
+  </si>
+  <si>
+    <t>Reserve Strength</t>
+  </si>
+  <si>
+    <t>25.1 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+  </si>
+  <si>
+    <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
+  </si>
+  <si>
+    <t>7 Healthy  |  0 Watch  |  0 Needs Attention</t>
+  </si>
+  <si>
+    <t>Built by SchoolStack Budget  •  budget.schoolstack.ai</t>
   </si>
 </sst>
 </file>
@@ -886,7 +1042,7 @@
     <numFmt numFmtId="169" formatCode="0.00x"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1000,6 +1156,30 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF16A34A"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFD97706"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFDC2626"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -1108,7 +1288,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1168,11 +1348,231 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="24">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3368,6 +3768,679 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF328555"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:H35"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="36" t="s">
+        <v>272</v>
+      </c>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B3" s="53" t="s">
+        <v>273</v>
+      </c>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="54" t="s">
+        <v>274</v>
+      </c>
+      <c r="D4" s="55" t="s">
+        <v>275</v>
+      </c>
+      <c r="F4" s="56" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="C6" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="57" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="57" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="57" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="57" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="C7" s="58">
+        <v>120</v>
+      </c>
+      <c r="D7" s="58">
+        <v>200</v>
+      </c>
+      <c r="E7" s="58">
+        <v>300</v>
+      </c>
+      <c r="F7" s="58">
+        <v>375</v>
+      </c>
+      <c r="G7" s="58">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="C8" s="59">
+        <v>1288333</v>
+      </c>
+      <c r="D8" s="59">
+        <v>2522800</v>
+      </c>
+      <c r="E8" s="59">
+        <v>3784600</v>
+      </c>
+      <c r="F8" s="59">
+        <v>4759125</v>
+      </c>
+      <c r="G8" s="59">
+        <v>5184400</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="C9" s="59">
+        <v>1026431</v>
+      </c>
+      <c r="D9" s="59">
+        <v>1231718</v>
+      </c>
+      <c r="E9" s="59">
+        <v>1231718</v>
+      </c>
+      <c r="F9" s="59">
+        <v>1231718</v>
+      </c>
+      <c r="G9" s="59">
+        <v>1231718</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" s="59">
+        <v>545000</v>
+      </c>
+      <c r="D10" s="59">
+        <v>887860</v>
+      </c>
+      <c r="E10" s="59">
+        <v>1190521</v>
+      </c>
+      <c r="F10" s="59">
+        <v>1439089</v>
+      </c>
+      <c r="G10" s="59">
+        <v>1554924</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="C11" s="59">
+        <v>164825</v>
+      </c>
+      <c r="D11" s="59">
+        <v>89825</v>
+      </c>
+      <c r="E11" s="59">
+        <v>89825</v>
+      </c>
+      <c r="F11" s="59">
+        <v>74825</v>
+      </c>
+      <c r="G11" s="59">
+        <v>69825</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="60" t="s">
+        <v>179</v>
+      </c>
+      <c r="C12" s="61">
+        <v>-447923</v>
+      </c>
+      <c r="D12" s="62">
+        <v>313398</v>
+      </c>
+      <c r="E12" s="62">
+        <v>1272536</v>
+      </c>
+      <c r="F12" s="62">
+        <v>2013494</v>
+      </c>
+      <c r="G12" s="62">
+        <v>2327934</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="60" t="s">
+        <v>280</v>
+      </c>
+      <c r="C13" s="62">
+        <v>52077</v>
+      </c>
+      <c r="D13" s="62">
+        <v>365475</v>
+      </c>
+      <c r="E13" s="62">
+        <v>1638011</v>
+      </c>
+      <c r="F13" s="62">
+        <v>3651505</v>
+      </c>
+      <c r="G13" s="62">
+        <v>5979439</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="60" t="s">
+        <v>281</v>
+      </c>
+      <c r="C14" s="63">
+        <v>-0.34767641595767557</v>
+      </c>
+      <c r="D14" s="64">
+        <v>0.12422625654035199</v>
+      </c>
+      <c r="E14" s="64">
+        <v>0.3362405538233895</v>
+      </c>
+      <c r="F14" s="64">
+        <v>0.42308071336642766</v>
+      </c>
+      <c r="G14" s="64">
+        <v>0.44902669547102847</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="60" t="s">
+        <v>246</v>
+      </c>
+      <c r="C15" s="65">
+        <v>10736.108333333334</v>
+      </c>
+      <c r="D15" s="65">
+        <v>12614</v>
+      </c>
+      <c r="E15" s="65">
+        <v>12615.333333333334</v>
+      </c>
+      <c r="F15" s="65">
+        <v>12691</v>
+      </c>
+      <c r="G15" s="65">
+        <v>12961</v>
+      </c>
+      <c r="H15" s="66" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="60" t="s">
+        <v>283</v>
+      </c>
+      <c r="C16" s="63">
+        <v>0.7967124959152642</v>
+      </c>
+      <c r="D16" s="64">
+        <v>0.4882345013477089</v>
+      </c>
+      <c r="E16" s="64">
+        <v>0.3254552660783174</v>
+      </c>
+      <c r="F16" s="64">
+        <v>0.25881186142410634</v>
+      </c>
+      <c r="G16" s="64">
+        <v>0.23758159092662604</v>
+      </c>
+      <c r="H16" s="66" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="60" t="s">
+        <v>285</v>
+      </c>
+      <c r="C17" s="64">
+        <v>0.12690818289991795</v>
+      </c>
+      <c r="D17" s="64">
+        <v>0.10558030759473601</v>
+      </c>
+      <c r="E17" s="64">
+        <v>0.09437095069492152</v>
+      </c>
+      <c r="F17" s="64">
+        <v>0.09071556220943976</v>
+      </c>
+      <c r="G17" s="64">
+        <v>0.08997708510145823</v>
+      </c>
+      <c r="H17" s="66" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="60" t="s">
+        <v>287</v>
+      </c>
+      <c r="C18" s="63">
+        <v>-0.219739772248324</v>
+      </c>
+      <c r="D18" s="64">
+        <v>0.15983114000317108</v>
+      </c>
+      <c r="E18" s="64">
+        <v>0.3599748982719442</v>
+      </c>
+      <c r="F18" s="64">
+        <v>0.4388029312110945</v>
+      </c>
+      <c r="G18" s="64">
+        <v>0.46249479206851324</v>
+      </c>
+      <c r="H18" s="66" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="60" t="s">
+        <v>289</v>
+      </c>
+      <c r="C19" s="67">
+        <v>1</v>
+      </c>
+      <c r="D19" s="67"/>
+      <c r="E19" s="67"/>
+      <c r="F19" s="67"/>
+      <c r="G19" s="67"/>
+      <c r="H19" s="66" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="60" t="s">
+        <v>197</v>
+      </c>
+      <c r="C20" s="68">
+        <v>-1.7175671166388593</v>
+      </c>
+      <c r="D20" s="69">
+        <v>4.488973003061509</v>
+      </c>
+      <c r="E20" s="69">
+        <v>15.16683551349847</v>
+      </c>
+      <c r="F20" s="69">
+        <v>27.909361844303376</v>
+      </c>
+      <c r="G20" s="69">
+        <v>34.33953455066237</v>
+      </c>
+      <c r="H20" s="66" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="60" t="s">
+        <v>292</v>
+      </c>
+      <c r="C21" s="70" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="66" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="60" t="s">
+        <v>293</v>
+      </c>
+      <c r="C22" s="70" t="s">
+        <v>294</v>
+      </c>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="66" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="71" t="s">
+        <v>299</v>
+      </c>
+      <c r="C25" s="72" t="s">
+        <v>300</v>
+      </c>
+      <c r="D25" s="73" t="s">
+        <v>301</v>
+      </c>
+      <c r="E25" s="73"/>
+      <c r="F25" s="74" t="s">
+        <v>302</v>
+      </c>
+      <c r="G25" s="74"/>
+      <c r="H25" s="74"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="71" t="s">
+        <v>303</v>
+      </c>
+      <c r="C26" s="72" t="s">
+        <v>300</v>
+      </c>
+      <c r="D26" s="73" t="s">
+        <v>304</v>
+      </c>
+      <c r="E26" s="73"/>
+      <c r="F26" s="74" t="s">
+        <v>305</v>
+      </c>
+      <c r="G26" s="74"/>
+      <c r="H26" s="74"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="71" t="s">
+        <v>306</v>
+      </c>
+      <c r="C27" s="72" t="s">
+        <v>300</v>
+      </c>
+      <c r="D27" s="73" t="s">
+        <v>307</v>
+      </c>
+      <c r="E27" s="73"/>
+      <c r="F27" s="74" t="s">
+        <v>308</v>
+      </c>
+      <c r="G27" s="74"/>
+      <c r="H27" s="74"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="71" t="s">
+        <v>309</v>
+      </c>
+      <c r="C28" s="72" t="s">
+        <v>300</v>
+      </c>
+      <c r="D28" s="73" t="s">
+        <v>310</v>
+      </c>
+      <c r="E28" s="73"/>
+      <c r="F28" s="74" t="s">
+        <v>311</v>
+      </c>
+      <c r="G28" s="74"/>
+      <c r="H28" s="74"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="71" t="s">
+        <v>312</v>
+      </c>
+      <c r="C29" s="72" t="s">
+        <v>300</v>
+      </c>
+      <c r="D29" s="73" t="s">
+        <v>313</v>
+      </c>
+      <c r="E29" s="73"/>
+      <c r="F29" s="74" t="s">
+        <v>314</v>
+      </c>
+      <c r="G29" s="74"/>
+      <c r="H29" s="74"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="71" t="s">
+        <v>315</v>
+      </c>
+      <c r="C30" s="72" t="s">
+        <v>300</v>
+      </c>
+      <c r="D30" s="73" t="s">
+        <v>316</v>
+      </c>
+      <c r="E30" s="73"/>
+      <c r="F30" s="74" t="s">
+        <v>317</v>
+      </c>
+      <c r="G30" s="74"/>
+      <c r="H30" s="74"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="71" t="s">
+        <v>318</v>
+      </c>
+      <c r="C31" s="72" t="s">
+        <v>300</v>
+      </c>
+      <c r="D31" s="73" t="s">
+        <v>319</v>
+      </c>
+      <c r="E31" s="73"/>
+      <c r="F31" s="74" t="s">
+        <v>320</v>
+      </c>
+      <c r="G31" s="74"/>
+      <c r="H31" s="74"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="71" t="s">
+        <v>271</v>
+      </c>
+      <c r="C33" s="60" t="s">
+        <v>321</v>
+      </c>
+      <c r="D33" s="60"/>
+      <c r="E33" s="60"/>
+      <c r="F33" s="60"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="75" t="s">
+        <v>322</v>
+      </c>
+      <c r="C35" s="75"/>
+      <c r="D35" s="75"/>
+      <c r="E35" s="75"/>
+      <c r="F35" s="75"/>
+      <c r="G35" s="75"/>
+      <c r="H35" s="75"/>
+    </row>
+  </sheetData>
+  <mergeCells count="23">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C12:G12">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>C12&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>C12&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>C12&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C13:G13">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>C13&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>C13&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>C13&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14:G14">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>C14&gt;=0.05</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="2">
+      <formula>C14&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="3">
+      <formula>C14&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C15:G15">
+    <cfRule type="expression" dxfId="9" priority="1">
+      <formula>C15&gt;=10000</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="2">
+      <formula>C15&gt;=7000</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="3">
+      <formula>C15&lt;7000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:G16">
+    <cfRule type="expression" dxfId="12" priority="1">
+      <formula>C16&lt;=0.55</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="2">
+      <formula>C16&lt;=0.65</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="3">
+      <formula>C16&gt;0.65</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C17:G17">
+    <cfRule type="expression" dxfId="15" priority="1">
+      <formula>C17&lt;=0.15</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="2">
+      <formula>C17&lt;=0.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="3">
+      <formula>C17&gt;0.25</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C18:G18">
+    <cfRule type="expression" dxfId="18" priority="1">
+      <formula>C18&gt;=0.10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="2">
+      <formula>C18&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="3">
+      <formula>C18&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C20:G20">
+    <cfRule type="expression" dxfId="21" priority="1">
+      <formula>C20&gt;=1.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="2">
+      <formula>C20&gt;=1.0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="3">
+      <formula>C20&lt;1.0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;10&amp;BCivic Scholars Charter&amp;R&amp;8&amp;IFinancial Health</oddHeader>
+    <oddFooter>&amp;L&amp;8Built by SchoolStack Budget  •  budget.schoolstack.ai&amp;C&amp;8Page &amp;P of &amp;N&amp;R&amp;8&amp;D</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
@@ -40,7 +40,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Debt Schedule'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Cash Flow Monthly Y1'!$A1:$N13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Cash Flow Monthly Y1'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'5-Year P&amp;L'!$A1:$F9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'5-Year P&amp;L'!$A1:$F10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'5-Year P&amp;L'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="10">'5-Year Balance Sheet'!$A1:$F17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="10">'5-Year Balance Sheet'!$1:$1</definedName>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="326">
   <si>
     <t>SchoolStack - Assumptions &amp; Drivers</t>
   </si>
@@ -606,6 +606,12 @@
     <t>Cumulative Net Income</t>
   </si>
   <si>
+    <t>Break-even</t>
+  </si>
+  <si>
+    <t>✓ Break-even</t>
+  </si>
+  <si>
     <t>ASSETS</t>
   </si>
   <si>
@@ -960,18 +966,21 @@
     <t>Viability</t>
   </si>
   <si>
+    <t>◐ Watch closely</t>
+  </si>
+  <si>
+    <t>The model reaches break-even by Year 3, but margins remain thin. A revenue shortfall could push it negative.</t>
+  </si>
+  <si>
+    <t>Track monthly revenue vs. budget and have a contingency plan if you miss targets.</t>
+  </si>
+  <si>
+    <t>Liquidity</t>
+  </si>
+  <si>
     <t>● Healthy</t>
   </si>
   <si>
-    <t>The model reaches net income early and sustains strong margins through Year 5.</t>
-  </si>
-  <si>
-    <t>Monitor enrollment actuals vs. projections in Year 1.</t>
-  </si>
-  <si>
-    <t>Liquidity</t>
-  </si>
-  <si>
     <t>Cash stays positive throughout the projection and reserves exceed 3 months of expenses.</t>
   </si>
   <si>
@@ -1023,7 +1032,7 @@
     <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
   </si>
   <si>
-    <t>7 Healthy  |  0 Watch  |  0 Needs Attention</t>
+    <t>6 Healthy  |  1 Watch  |  0 Needs Attention</t>
   </si>
   <si>
     <t>Built by SchoolStack Budget  •  budget.schoolstack.ai</t>
@@ -1096,6 +1105,12 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF16A34A"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FF1E293B"/>
       <sz val="16"/>
       <name val="Calibri"/>
@@ -1159,12 +1174,6 @@
     <font>
       <i/>
       <color rgb="FF6B7280"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF16A34A"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -1288,7 +1297,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1322,6 +1331,12 @@
     <xf numFmtId="166" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1331,25 +1346,25 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1377,26 +1392,26 @@
     <xf numFmtId="166" fontId="4" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="169" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2141,7 +2156,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -2361,6 +2376,26 @@
       <c r="F9" s="27">
         <f>E9+F7</f>
         <v>5479439</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="B10" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="E10" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2407,7 +2442,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -2417,7 +2452,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B3" s="15">
         <v>52077</v>
@@ -2437,7 +2472,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B4" s="15">
         <v>0</v>
@@ -2457,7 +2492,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B5" s="16">
         <f>SUM(B3:B4)</f>
@@ -2482,7 +2517,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -2492,7 +2527,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B8" s="15">
         <v>478925</v>
@@ -2512,7 +2547,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B9" s="15">
         <v>0</v>
@@ -2532,7 +2567,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B10" s="16">
         <f>SUM(B8:B9)</f>
@@ -2557,7 +2592,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -2567,7 +2602,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B13" s="15">
         <v>0</v>
@@ -2587,7 +2622,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B14" s="15">
         <v>-426848</v>
@@ -2607,7 +2642,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B15" s="16">
         <f>B5-B10</f>
@@ -2632,7 +2667,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B17" s="27" t="str">
         <f>B5-B10-B15</f>
@@ -2699,7 +2734,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -2709,7 +2744,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B3" s="15">
         <v>-283098</v>
@@ -2749,32 +2784,32 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="B5" s="31">
+        <v>199</v>
+      </c>
+      <c r="B5" s="33">
         <f>IF(B4=0,"N/A",B3/B4)</f>
         <v>-5.68</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="33">
         <f>IF(C4=0,"N/A",C3/C4)</f>
         <v>8.09</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="33">
         <f>IF(D4=0,"N/A",D3/D4)</f>
         <v>27.34</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="33">
         <f>IF(E4=0,"N/A",E3/E4)</f>
         <v>41.91</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="33">
         <f>IF(F4=0,"N/A",F3/F4)</f>
         <v>48.12</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -2784,7 +2819,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B8" s="15">
         <v>52077</v>
@@ -2804,7 +2839,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B9" s="15">
         <v>130953</v>
@@ -2824,52 +2859,52 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="B10" s="32">
+        <v>203</v>
+      </c>
+      <c r="B10" s="34">
         <f>IF(B9=0,0,B8/B9)</f>
         <v>0.4</v>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="34">
         <f>IF(C9=0,0,C8/C9)</f>
         <v>2.07</v>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="34">
         <f>IF(D9=0,0,D8/D9)</f>
         <v>8.11</v>
       </c>
-      <c r="E10" s="32">
+      <c r="E10" s="34">
         <f>IF(E9=0,0,E8/E9)</f>
         <v>16.41</v>
       </c>
-      <c r="F10" s="32">
+      <c r="F10" s="34">
         <f>IF(F9=0,0,F8/F9)</f>
         <v>25.75</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="B11" s="33">
+        <v>204</v>
+      </c>
+      <c r="B11" s="35">
         <v>12</v>
       </c>
-      <c r="C11" s="33">
+      <c r="C11" s="35">
         <v>63</v>
       </c>
-      <c r="D11" s="33">
+      <c r="D11" s="35">
         <v>247</v>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="35">
         <v>499</v>
       </c>
-      <c r="F11" s="33">
+      <c r="F11" s="35">
         <v>783</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -2879,92 +2914,92 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="B14" s="34" t="str">
+        <v>206</v>
+      </c>
+      <c r="B14" s="36" t="str">
         <f>IF(B5&gt;=1.2,"PASS","FAIL")</f>
         <v>FAIL</v>
       </c>
-      <c r="C14" s="35" t="str">
+      <c r="C14" s="37" t="str">
         <f>IF(C5&gt;=1.2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="D14" s="35" t="str">
+      <c r="D14" s="37" t="str">
         <f>IF(D5&gt;=1.2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="E14" s="35" t="str">
+      <c r="E14" s="37" t="str">
         <f>IF(E5&gt;=1.2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="F14" s="35" t="str">
+      <c r="F14" s="37" t="str">
         <f>IF(F5&gt;=1.2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="B15" s="34" t="str">
+        <v>207</v>
+      </c>
+      <c r="B15" s="36" t="str">
         <f>IF(B10&gt;=2,"PASS","FAIL")</f>
         <v>FAIL</v>
       </c>
-      <c r="C15" s="35" t="str">
+      <c r="C15" s="37" t="str">
         <f>IF(C10&gt;=2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="D15" s="35" t="str">
+      <c r="D15" s="37" t="str">
         <f>IF(D10&gt;=2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="E15" s="35" t="str">
+      <c r="E15" s="37" t="str">
         <f>IF(E10&gt;=2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="F15" s="35" t="str">
+      <c r="F15" s="37" t="str">
         <f>IF(F10&gt;=2,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="B16" s="34" t="s">
-        <v>207</v>
-      </c>
-      <c r="C16" s="35" t="s">
         <v>208</v>
       </c>
-      <c r="D16" s="35" t="s">
-        <v>208</v>
-      </c>
-      <c r="E16" s="35" t="s">
-        <v>208</v>
-      </c>
-      <c r="F16" s="35" t="s">
-        <v>208</v>
+      <c r="B16" s="36" t="s">
+        <v>209</v>
+      </c>
+      <c r="C16" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="D16" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="E16" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="F16" s="37" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="B17" s="36" t="s">
         <v>209</v>
       </c>
-      <c r="B17" s="34" t="s">
-        <v>207</v>
-      </c>
-      <c r="C17" s="34" t="s">
-        <v>207</v>
-      </c>
-      <c r="D17" s="35" t="s">
-        <v>208</v>
-      </c>
-      <c r="E17" s="35" t="s">
-        <v>208</v>
-      </c>
-      <c r="F17" s="35" t="s">
-        <v>208</v>
+      <c r="C17" s="36" t="s">
+        <v>209</v>
+      </c>
+      <c r="D17" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="E17" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="F17" s="37" t="s">
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -2991,65 +3026,65 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
-        <v>210</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
+      <c r="A1" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="37" t="s">
-        <v>211</v>
-      </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
+      <c r="A2" s="39" t="s">
+        <v>213</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="B5" s="34" t="s">
-        <v>207</v>
+        <v>215</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>209</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="B6" s="34" t="s">
-        <v>207</v>
+        <v>217</v>
+      </c>
+      <c r="B6" s="36" t="s">
+        <v>209</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="B7" s="34" t="s">
-        <v>207</v>
+        <v>219</v>
+      </c>
+      <c r="B7" s="36" t="s">
+        <v>209</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="B8" s="35" t="s">
-        <v>208</v>
+        <v>221</v>
+      </c>
+      <c r="B8" s="37" t="s">
+        <v>210</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>36</v>
@@ -3057,59 +3092,59 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="B9" s="34" t="s">
-        <v>207</v>
+        <v>222</v>
+      </c>
+      <c r="B9" s="36" t="s">
+        <v>209</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="B10" s="35" t="s">
-        <v>208</v>
+        <v>224</v>
+      </c>
+      <c r="B10" s="37" t="s">
+        <v>210</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="B14" s="38" t="s">
-        <v>228</v>
+        <v>229</v>
+      </c>
+      <c r="B14" s="40" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B17" s="18">
         <v>1288333</v>
@@ -3117,7 +3152,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B18" s="18">
         <v>1736256</v>
@@ -3125,7 +3160,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B19" s="18">
         <v>-447923</v>
@@ -3133,9 +3168,9 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="B20" s="39">
+        <v>235</v>
+      </c>
+      <c r="B20" s="41">
         <v>-0.34767641595767557</v>
       </c>
     </row>
@@ -3149,7 +3184,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B22" s="18">
         <v>52077</v>
@@ -3157,7 +3192,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B23" s="18">
         <v>500000</v>
@@ -3165,23 +3200,23 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>36</v>
@@ -3189,7 +3224,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B27" s="18">
         <v>10736</v>
@@ -3197,7 +3232,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B28" s="18">
         <v>14469</v>
@@ -3230,44 +3265,44 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="40" t="s">
-        <v>242</v>
-      </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
+      <c r="A2" s="42" t="s">
+        <v>244</v>
+      </c>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="41" t="s">
-        <v>243</v>
-      </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
+      <c r="A3" s="43" t="s">
+        <v>245</v>
+      </c>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
     </row>
     <row r="4" ht="16" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="42" t="s">
-        <v>244</v>
-      </c>
-      <c r="B4" s="42"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
+      <c r="A4" s="44" t="s">
+        <v>246</v>
+      </c>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
@@ -3293,23 +3328,23 @@
       <c r="A7" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="33">
+      <c r="B7" s="35">
         <f>Assumptions!$B$17</f>
         <v>120</v>
       </c>
-      <c r="C7" s="33">
+      <c r="C7" s="35">
         <f>Assumptions!$C$17</f>
         <v>200</v>
       </c>
-      <c r="D7" s="33">
+      <c r="D7" s="35">
         <f>Assumptions!$D$17</f>
         <v>300</v>
       </c>
-      <c r="E7" s="33">
+      <c r="E7" s="35">
         <f>Assumptions!$E$17</f>
         <v>375</v>
       </c>
-      <c r="F7" s="33">
+      <c r="F7" s="35">
         <f>Assumptions!$F$17</f>
         <v>400</v>
       </c>
@@ -3441,7 +3476,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B13" s="27">
         <v>52077</v>
@@ -3461,7 +3496,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B14" s="15">
         <v>10736</v>
@@ -3501,33 +3536,33 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="B16" s="31">
+        <v>199</v>
+      </c>
+      <c r="B16" s="33">
         <v>-5.68</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="33">
         <v>8.09</v>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="33">
         <v>27.34</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="33">
         <v>41.91</v>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="33">
         <v>48.12</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="42" t="s">
-        <v>247</v>
-      </c>
-      <c r="B18" s="42"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
+      <c r="A18" s="44" t="s">
+        <v>249</v>
+      </c>
+      <c r="B18" s="44"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3563,56 +3598,56 @@
     <row r="1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" ht="10" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" ht="40" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="43" t="s">
-        <v>248</v>
-      </c>
-      <c r="C3" s="43"/>
+      <c r="B3" s="45" t="s">
+        <v>250</v>
+      </c>
+      <c r="C3" s="45"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="44" t="s">
-        <v>249</v>
-      </c>
-      <c r="C4" s="44"/>
+      <c r="B4" s="46" t="s">
+        <v>251</v>
+      </c>
+      <c r="C4" s="46"/>
     </row>
     <row r="6" ht="4" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="46" t="s">
-        <v>250</v>
+      <c r="B8" s="48" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="47" t="s">
+      <c r="B9" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="47"/>
+      <c r="C9" s="49"/>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="48" t="s">
-        <v>251</v>
-      </c>
-      <c r="C10" s="48"/>
+      <c r="B10" s="50" t="s">
+        <v>253</v>
+      </c>
+      <c r="C10" s="50"/>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="46" t="s">
-        <v>252</v>
-      </c>
-      <c r="C12" s="49" t="s">
-        <v>253</v>
+      <c r="B12" s="48" t="s">
+        <v>254</v>
+      </c>
+      <c r="C12" s="51" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C15" s="5"/>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="13" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C16" s="27">
         <v>5184400</v>
@@ -3620,7 +3655,7 @@
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="13" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C17" s="27">
         <v>2327934</v>
@@ -3628,7 +3663,7 @@
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C18" s="27">
         <v>5479439</v>
@@ -3636,108 +3671,108 @@
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="C19" s="50" t="s">
-        <v>257</v>
+        <v>229</v>
+      </c>
+      <c r="C19" s="52" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="B22" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C22" s="5"/>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="51" t="s">
-        <v>259</v>
-      </c>
-      <c r="C23" s="52"/>
+      <c r="B23" s="53" t="s">
+        <v>261</v>
+      </c>
+      <c r="C23" s="54"/>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="51" t="s">
-        <v>260</v>
-      </c>
-      <c r="C24" s="52"/>
+      <c r="B24" s="53" t="s">
+        <v>262</v>
+      </c>
+      <c r="C24" s="54"/>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="51" t="s">
-        <v>261</v>
-      </c>
-      <c r="C25" s="52"/>
+      <c r="B25" s="53" t="s">
+        <v>263</v>
+      </c>
+      <c r="C25" s="54"/>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="51" t="s">
-        <v>262</v>
-      </c>
-      <c r="C26" s="52"/>
+      <c r="B26" s="53" t="s">
+        <v>264</v>
+      </c>
+      <c r="C26" s="54"/>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="51" t="s">
+      <c r="B27" s="53" t="s">
         <v>168</v>
       </c>
-      <c r="C27" s="52"/>
+      <c r="C27" s="54"/>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="51" t="s">
-        <v>263</v>
-      </c>
-      <c r="C28" s="52"/>
+      <c r="B28" s="53" t="s">
+        <v>265</v>
+      </c>
+      <c r="C28" s="54"/>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="51" t="s">
-        <v>264</v>
-      </c>
-      <c r="C29" s="52"/>
+      <c r="B29" s="53" t="s">
+        <v>266</v>
+      </c>
+      <c r="C29" s="54"/>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="51" t="s">
-        <v>265</v>
-      </c>
-      <c r="C30" s="52"/>
+      <c r="B30" s="53" t="s">
+        <v>267</v>
+      </c>
+      <c r="C30" s="54"/>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="51" t="s">
-        <v>266</v>
-      </c>
-      <c r="C31" s="52"/>
+      <c r="B31" s="53" t="s">
+        <v>268</v>
+      </c>
+      <c r="C31" s="54"/>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="51" t="s">
-        <v>267</v>
-      </c>
-      <c r="C32" s="52"/>
+      <c r="B32" s="53" t="s">
+        <v>269</v>
+      </c>
+      <c r="C32" s="54"/>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="51" t="s">
-        <v>268</v>
-      </c>
-      <c r="C33" s="52"/>
+      <c r="B33" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="C33" s="54"/>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="51" t="s">
-        <v>269</v>
-      </c>
-      <c r="C34" s="52"/>
+      <c r="B34" s="53" t="s">
+        <v>271</v>
+      </c>
+      <c r="C34" s="54"/>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="51" t="s">
-        <v>270</v>
-      </c>
-      <c r="C35" s="52"/>
+      <c r="B35" s="53" t="s">
+        <v>272</v>
+      </c>
+      <c r="C35" s="54"/>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B36" s="51" t="s">
-        <v>271</v>
-      </c>
-      <c r="C36" s="52"/>
+      <c r="B36" s="53" t="s">
+        <v>273</v>
+      </c>
+      <c r="C36" s="54"/>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B39" s="42" t="s">
-        <v>247</v>
-      </c>
-      <c r="C39" s="42"/>
+      <c r="B39" s="44" t="s">
+        <v>249</v>
+      </c>
+      <c r="C39" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3785,78 +3820,78 @@
   </cols>
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="36" t="s">
-        <v>272</v>
-      </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
+      <c r="B2" s="38" t="s">
+        <v>274</v>
+      </c>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="53" t="s">
-        <v>273</v>
-      </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
+      <c r="B3" s="55" t="s">
+        <v>275</v>
+      </c>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="54" t="s">
-        <v>274</v>
-      </c>
-      <c r="D4" s="55" t="s">
-        <v>275</v>
-      </c>
-      <c r="F4" s="56" t="s">
+      <c r="B4" s="56" t="s">
         <v>276</v>
+      </c>
+      <c r="D4" s="57" t="s">
+        <v>277</v>
+      </c>
+      <c r="F4" s="58" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="C6" s="57" t="s">
+        <v>279</v>
+      </c>
+      <c r="C6" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="57" t="s">
+      <c r="D6" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="57" t="s">
+      <c r="E6" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="57" t="s">
+      <c r="F6" s="59" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="57" t="s">
+      <c r="G6" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="57" t="s">
-        <v>278</v>
+      <c r="H6" s="59" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="C7" s="58">
+        <v>281</v>
+      </c>
+      <c r="C7" s="60">
         <v>120</v>
       </c>
-      <c r="D7" s="58">
+      <c r="D7" s="60">
         <v>200</v>
       </c>
-      <c r="E7" s="58">
+      <c r="E7" s="60">
         <v>300</v>
       </c>
-      <c r="F7" s="58">
+      <c r="F7" s="60">
         <v>375</v>
       </c>
-      <c r="G7" s="58">
+      <c r="G7" s="60">
         <v>400</v>
       </c>
     </row>
@@ -3864,19 +3899,19 @@
       <c r="B8" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="C8" s="59">
+      <c r="C8" s="61">
         <v>1288333</v>
       </c>
-      <c r="D8" s="59">
+      <c r="D8" s="61">
         <v>2522800</v>
       </c>
-      <c r="E8" s="59">
+      <c r="E8" s="61">
         <v>3784600</v>
       </c>
-      <c r="F8" s="59">
+      <c r="F8" s="61">
         <v>4759125</v>
       </c>
-      <c r="G8" s="59">
+      <c r="G8" s="61">
         <v>5184400</v>
       </c>
     </row>
@@ -3884,19 +3919,19 @@
       <c r="B9" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="C9" s="59">
+      <c r="C9" s="61">
         <v>1026431</v>
       </c>
-      <c r="D9" s="59">
+      <c r="D9" s="61">
         <v>1231718</v>
       </c>
-      <c r="E9" s="59">
+      <c r="E9" s="61">
         <v>1231718</v>
       </c>
-      <c r="F9" s="59">
+      <c r="F9" s="61">
         <v>1231718</v>
       </c>
-      <c r="G9" s="59">
+      <c r="G9" s="61">
         <v>1231718</v>
       </c>
     </row>
@@ -3904,19 +3939,19 @@
       <c r="B10" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="59">
+      <c r="C10" s="61">
         <v>545000</v>
       </c>
-      <c r="D10" s="59">
+      <c r="D10" s="61">
         <v>887860</v>
       </c>
-      <c r="E10" s="59">
+      <c r="E10" s="61">
         <v>1190521</v>
       </c>
-      <c r="F10" s="59">
+      <c r="F10" s="61">
         <v>1439089</v>
       </c>
-      <c r="G10" s="59">
+      <c r="G10" s="61">
         <v>1554924</v>
       </c>
     </row>
@@ -3924,399 +3959,399 @@
       <c r="B11" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="C11" s="59">
+      <c r="C11" s="61">
         <v>164825</v>
       </c>
-      <c r="D11" s="59">
+      <c r="D11" s="61">
         <v>89825</v>
       </c>
-      <c r="E11" s="59">
+      <c r="E11" s="61">
         <v>89825</v>
       </c>
-      <c r="F11" s="59">
+      <c r="F11" s="61">
         <v>74825</v>
       </c>
-      <c r="G11" s="59">
+      <c r="G11" s="61">
         <v>69825</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="60" t="s">
+      <c r="B12" s="62" t="s">
         <v>179</v>
       </c>
-      <c r="C12" s="61">
+      <c r="C12" s="63">
         <v>-447923</v>
       </c>
-      <c r="D12" s="62">
+      <c r="D12" s="64">
         <v>313398</v>
       </c>
-      <c r="E12" s="62">
+      <c r="E12" s="64">
         <v>1272536</v>
       </c>
-      <c r="F12" s="62">
+      <c r="F12" s="64">
         <v>2013494</v>
       </c>
-      <c r="G12" s="62">
+      <c r="G12" s="64">
         <v>2327934</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="60" t="s">
-        <v>280</v>
-      </c>
-      <c r="C13" s="62">
+      <c r="B13" s="62" t="s">
+        <v>282</v>
+      </c>
+      <c r="C13" s="64">
         <v>52077</v>
       </c>
-      <c r="D13" s="62">
+      <c r="D13" s="64">
         <v>365475</v>
       </c>
-      <c r="E13" s="62">
+      <c r="E13" s="64">
         <v>1638011</v>
       </c>
-      <c r="F13" s="62">
+      <c r="F13" s="64">
         <v>3651505</v>
       </c>
-      <c r="G13" s="62">
+      <c r="G13" s="64">
         <v>5979439</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="60" t="s">
-        <v>281</v>
-      </c>
-      <c r="C14" s="63">
+      <c r="B14" s="62" t="s">
+        <v>283</v>
+      </c>
+      <c r="C14" s="65">
         <v>-0.34767641595767557</v>
       </c>
-      <c r="D14" s="64">
+      <c r="D14" s="66">
         <v>0.12422625654035199</v>
       </c>
-      <c r="E14" s="64">
+      <c r="E14" s="66">
         <v>0.3362405538233895</v>
       </c>
-      <c r="F14" s="64">
+      <c r="F14" s="66">
         <v>0.42308071336642766</v>
       </c>
-      <c r="G14" s="64">
+      <c r="G14" s="66">
         <v>0.44902669547102847</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="60" t="s">
-        <v>246</v>
-      </c>
-      <c r="C15" s="65">
+      <c r="B15" s="62" t="s">
+        <v>248</v>
+      </c>
+      <c r="C15" s="67">
         <v>10736.108333333334</v>
       </c>
-      <c r="D15" s="65">
+      <c r="D15" s="67">
         <v>12614</v>
       </c>
-      <c r="E15" s="65">
+      <c r="E15" s="67">
         <v>12615.333333333334</v>
       </c>
-      <c r="F15" s="65">
+      <c r="F15" s="67">
         <v>12691</v>
       </c>
-      <c r="G15" s="65">
+      <c r="G15" s="67">
         <v>12961</v>
       </c>
-      <c r="H15" s="66" t="s">
-        <v>282</v>
+      <c r="H15" s="68" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="60" t="s">
-        <v>283</v>
-      </c>
-      <c r="C16" s="63">
+      <c r="B16" s="62" t="s">
+        <v>285</v>
+      </c>
+      <c r="C16" s="65">
         <v>0.7967124959152642</v>
       </c>
-      <c r="D16" s="64">
+      <c r="D16" s="66">
         <v>0.4882345013477089</v>
       </c>
-      <c r="E16" s="64">
+      <c r="E16" s="66">
         <v>0.3254552660783174</v>
       </c>
-      <c r="F16" s="64">
+      <c r="F16" s="66">
         <v>0.25881186142410634</v>
       </c>
-      <c r="G16" s="64">
+      <c r="G16" s="66">
         <v>0.23758159092662604</v>
       </c>
-      <c r="H16" s="66" t="s">
-        <v>284</v>
+      <c r="H16" s="68" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="60" t="s">
-        <v>285</v>
-      </c>
-      <c r="C17" s="64">
+      <c r="B17" s="62" t="s">
+        <v>287</v>
+      </c>
+      <c r="C17" s="66">
         <v>0.12690818289991795</v>
       </c>
-      <c r="D17" s="64">
+      <c r="D17" s="66">
         <v>0.10558030759473601</v>
       </c>
-      <c r="E17" s="64">
+      <c r="E17" s="66">
         <v>0.09437095069492152</v>
       </c>
-      <c r="F17" s="64">
+      <c r="F17" s="66">
         <v>0.09071556220943976</v>
       </c>
-      <c r="G17" s="64">
+      <c r="G17" s="66">
         <v>0.08997708510145823</v>
       </c>
-      <c r="H17" s="66" t="s">
-        <v>286</v>
+      <c r="H17" s="68" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="60" t="s">
-        <v>287</v>
-      </c>
-      <c r="C18" s="63">
+      <c r="B18" s="62" t="s">
+        <v>289</v>
+      </c>
+      <c r="C18" s="65">
         <v>-0.219739772248324</v>
       </c>
-      <c r="D18" s="64">
+      <c r="D18" s="66">
         <v>0.15983114000317108</v>
       </c>
-      <c r="E18" s="64">
+      <c r="E18" s="66">
         <v>0.3599748982719442</v>
       </c>
-      <c r="F18" s="64">
+      <c r="F18" s="66">
         <v>0.4388029312110945</v>
       </c>
-      <c r="G18" s="64">
+      <c r="G18" s="66">
         <v>0.46249479206851324</v>
       </c>
-      <c r="H18" s="66" t="s">
-        <v>288</v>
+      <c r="H18" s="68" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="60" t="s">
-        <v>289</v>
-      </c>
-      <c r="C19" s="67">
-        <v>1</v>
-      </c>
-      <c r="D19" s="67"/>
-      <c r="E19" s="67"/>
-      <c r="F19" s="67"/>
-      <c r="G19" s="67"/>
-      <c r="H19" s="66" t="s">
-        <v>290</v>
+      <c r="B19" s="62" t="s">
+        <v>291</v>
+      </c>
+      <c r="C19" s="69">
+        <v>3</v>
+      </c>
+      <c r="D19" s="69"/>
+      <c r="E19" s="69"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="69"/>
+      <c r="H19" s="68" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="60" t="s">
-        <v>197</v>
-      </c>
-      <c r="C20" s="68">
+      <c r="B20" s="62" t="s">
+        <v>199</v>
+      </c>
+      <c r="C20" s="70">
         <v>-1.7175671166388593</v>
       </c>
-      <c r="D20" s="69">
+      <c r="D20" s="71">
         <v>4.488973003061509</v>
       </c>
-      <c r="E20" s="69">
+      <c r="E20" s="71">
         <v>15.16683551349847</v>
       </c>
-      <c r="F20" s="69">
+      <c r="F20" s="71">
         <v>27.909361844303376</v>
       </c>
-      <c r="G20" s="69">
+      <c r="G20" s="71">
         <v>34.33953455066237</v>
       </c>
-      <c r="H20" s="66" t="s">
-        <v>291</v>
+      <c r="H20" s="68" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="60" t="s">
-        <v>292</v>
-      </c>
-      <c r="C21" s="70" t="s">
-        <v>24</v>
-      </c>
-      <c r="D21" s="70"/>
-      <c r="E21" s="70"/>
-      <c r="F21" s="70"/>
-      <c r="G21" s="70"/>
-      <c r="H21" s="66" t="s">
+      <c r="B21" s="62" t="s">
+        <v>294</v>
+      </c>
+      <c r="C21" s="72" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" s="72"/>
+      <c r="E21" s="72"/>
+      <c r="F21" s="72"/>
+      <c r="G21" s="72"/>
+      <c r="H21" s="68" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="60" t="s">
-        <v>293</v>
-      </c>
-      <c r="C22" s="70" t="s">
-        <v>294</v>
-      </c>
-      <c r="D22" s="70"/>
-      <c r="E22" s="70"/>
-      <c r="F22" s="70"/>
-      <c r="G22" s="70"/>
-      <c r="H22" s="66" t="s">
-        <v>294</v>
+      <c r="B22" s="62" t="s">
+        <v>295</v>
+      </c>
+      <c r="C22" s="72" t="s">
+        <v>296</v>
+      </c>
+      <c r="D22" s="72"/>
+      <c r="E22" s="72"/>
+      <c r="F22" s="72"/>
+      <c r="G22" s="72"/>
+      <c r="H22" s="68" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="71" t="s">
-        <v>299</v>
-      </c>
-      <c r="C25" s="72" t="s">
-        <v>300</v>
-      </c>
-      <c r="D25" s="73" t="s">
+      <c r="B25" s="73" t="s">
         <v>301</v>
       </c>
-      <c r="E25" s="73"/>
-      <c r="F25" s="74" t="s">
+      <c r="C25" s="74" t="s">
         <v>302</v>
       </c>
-      <c r="G25" s="74"/>
-      <c r="H25" s="74"/>
+      <c r="D25" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="E25" s="75"/>
+      <c r="F25" s="76" t="s">
+        <v>304</v>
+      </c>
+      <c r="G25" s="76"/>
+      <c r="H25" s="76"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="71" t="s">
-        <v>303</v>
-      </c>
-      <c r="C26" s="72" t="s">
-        <v>300</v>
-      </c>
-      <c r="D26" s="73" t="s">
-        <v>304</v>
-      </c>
-      <c r="E26" s="73"/>
-      <c r="F26" s="74" t="s">
+      <c r="B26" s="73" t="s">
         <v>305</v>
       </c>
-      <c r="G26" s="74"/>
-      <c r="H26" s="74"/>
+      <c r="C26" s="32" t="s">
+        <v>306</v>
+      </c>
+      <c r="D26" s="75" t="s">
+        <v>307</v>
+      </c>
+      <c r="E26" s="75"/>
+      <c r="F26" s="76" t="s">
+        <v>308</v>
+      </c>
+      <c r="G26" s="76"/>
+      <c r="H26" s="76"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="71" t="s">
+      <c r="B27" s="73" t="s">
+        <v>309</v>
+      </c>
+      <c r="C27" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="C27" s="72" t="s">
-        <v>300</v>
-      </c>
-      <c r="D27" s="73" t="s">
-        <v>307</v>
-      </c>
-      <c r="E27" s="73"/>
-      <c r="F27" s="74" t="s">
-        <v>308</v>
-      </c>
-      <c r="G27" s="74"/>
-      <c r="H27" s="74"/>
+      <c r="D27" s="75" t="s">
+        <v>310</v>
+      </c>
+      <c r="E27" s="75"/>
+      <c r="F27" s="76" t="s">
+        <v>311</v>
+      </c>
+      <c r="G27" s="76"/>
+      <c r="H27" s="76"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="71" t="s">
-        <v>309</v>
-      </c>
-      <c r="C28" s="72" t="s">
-        <v>300</v>
-      </c>
-      <c r="D28" s="73" t="s">
-        <v>310</v>
-      </c>
-      <c r="E28" s="73"/>
-      <c r="F28" s="74" t="s">
-        <v>311</v>
-      </c>
-      <c r="G28" s="74"/>
-      <c r="H28" s="74"/>
+      <c r="B28" s="73" t="s">
+        <v>312</v>
+      </c>
+      <c r="C28" s="32" t="s">
+        <v>306</v>
+      </c>
+      <c r="D28" s="75" t="s">
+        <v>313</v>
+      </c>
+      <c r="E28" s="75"/>
+      <c r="F28" s="76" t="s">
+        <v>314</v>
+      </c>
+      <c r="G28" s="76"/>
+      <c r="H28" s="76"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="71" t="s">
-        <v>312</v>
-      </c>
-      <c r="C29" s="72" t="s">
-        <v>300</v>
-      </c>
-      <c r="D29" s="73" t="s">
-        <v>313</v>
-      </c>
-      <c r="E29" s="73"/>
-      <c r="F29" s="74" t="s">
-        <v>314</v>
-      </c>
-      <c r="G29" s="74"/>
-      <c r="H29" s="74"/>
+      <c r="B29" s="73" t="s">
+        <v>315</v>
+      </c>
+      <c r="C29" s="32" t="s">
+        <v>306</v>
+      </c>
+      <c r="D29" s="75" t="s">
+        <v>316</v>
+      </c>
+      <c r="E29" s="75"/>
+      <c r="F29" s="76" t="s">
+        <v>317</v>
+      </c>
+      <c r="G29" s="76"/>
+      <c r="H29" s="76"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="71" t="s">
-        <v>315</v>
-      </c>
-      <c r="C30" s="72" t="s">
-        <v>300</v>
-      </c>
-      <c r="D30" s="73" t="s">
-        <v>316</v>
-      </c>
-      <c r="E30" s="73"/>
-      <c r="F30" s="74" t="s">
-        <v>317</v>
-      </c>
-      <c r="G30" s="74"/>
-      <c r="H30" s="74"/>
+      <c r="B30" s="73" t="s">
+        <v>318</v>
+      </c>
+      <c r="C30" s="32" t="s">
+        <v>306</v>
+      </c>
+      <c r="D30" s="75" t="s">
+        <v>319</v>
+      </c>
+      <c r="E30" s="75"/>
+      <c r="F30" s="76" t="s">
+        <v>320</v>
+      </c>
+      <c r="G30" s="76"/>
+      <c r="H30" s="76"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="71" t="s">
-        <v>318</v>
-      </c>
-      <c r="C31" s="72" t="s">
-        <v>300</v>
-      </c>
-      <c r="D31" s="73" t="s">
-        <v>319</v>
-      </c>
-      <c r="E31" s="73"/>
-      <c r="F31" s="74" t="s">
-        <v>320</v>
-      </c>
-      <c r="G31" s="74"/>
-      <c r="H31" s="74"/>
+      <c r="B31" s="73" t="s">
+        <v>321</v>
+      </c>
+      <c r="C31" s="32" t="s">
+        <v>306</v>
+      </c>
+      <c r="D31" s="75" t="s">
+        <v>322</v>
+      </c>
+      <c r="E31" s="75"/>
+      <c r="F31" s="76" t="s">
+        <v>323</v>
+      </c>
+      <c r="G31" s="76"/>
+      <c r="H31" s="76"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="71" t="s">
-        <v>271</v>
-      </c>
-      <c r="C33" s="60" t="s">
-        <v>321</v>
-      </c>
-      <c r="D33" s="60"/>
-      <c r="E33" s="60"/>
-      <c r="F33" s="60"/>
+      <c r="B33" s="73" t="s">
+        <v>273</v>
+      </c>
+      <c r="C33" s="62" t="s">
+        <v>324</v>
+      </c>
+      <c r="D33" s="62"/>
+      <c r="E33" s="62"/>
+      <c r="F33" s="62"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="75" t="s">
-        <v>322</v>
-      </c>
-      <c r="C35" s="75"/>
-      <c r="D35" s="75"/>
-      <c r="E35" s="75"/>
-      <c r="F35" s="75"/>
-      <c r="G35" s="75"/>
-      <c r="H35" s="75"/>
+      <c r="B35" s="77" t="s">
+        <v>325</v>
+      </c>
+      <c r="C35" s="77"/>
+      <c r="D35" s="77"/>
+      <c r="E35" s="77"/>
+      <c r="F35" s="77"/>
+      <c r="G35" s="77"/>
+      <c r="H35" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="23">

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
@@ -4461,10 +4461,10 @@
       <formula>C20&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1.0</formula>
+      <formula>C20&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1.0</formula>
+      <formula>C20&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="326">
   <si>
     <t>SchoolStack - Assumptions &amp; Drivers</t>
   </si>
@@ -1297,7 +1297,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1399,6 +1399,9 @@
     </xf>
     <xf numFmtId="169" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4169,13 +4172,26 @@
       <c r="B21" s="62" t="s">
         <v>294</v>
       </c>
-      <c r="C21" s="72" t="s">
-        <v>25</v>
-      </c>
-      <c r="D21" s="72"/>
-      <c r="E21" s="72"/>
-      <c r="F21" s="72"/>
-      <c r="G21" s="72"/>
+      <c r="C21" s="72" t="str">
+        <f>IF('5-Year P&amp;L'!B9&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="72" t="str">
+        <f>IF('5-Year P&amp;L'!C9&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="32" t="str">
+        <f>IF('5-Year P&amp;L'!D9&gt;=0,"✓ Break-even","")</f>
+        <v>✓ Break-even</v>
+      </c>
+      <c r="F21" s="72" t="str">
+        <f>IF('5-Year P&amp;L'!E9&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="72" t="str">
+        <f>IF('5-Year P&amp;L'!F9&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
       <c r="H21" s="68" t="s">
         <v>23</v>
       </c>
@@ -4184,13 +4200,13 @@
       <c r="B22" s="62" t="s">
         <v>295</v>
       </c>
-      <c r="C22" s="72" t="s">
+      <c r="C22" s="73" t="s">
         <v>296</v>
       </c>
-      <c r="D22" s="72"/>
-      <c r="E22" s="72"/>
-      <c r="F22" s="72"/>
-      <c r="G22" s="72"/>
+      <c r="D22" s="73"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="73"/>
+      <c r="G22" s="73"/>
       <c r="H22" s="68" t="s">
         <v>296</v>
       </c>
@@ -4213,126 +4229,126 @@
       <c r="H24" s="5"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="73" t="s">
+      <c r="B25" s="74" t="s">
         <v>301</v>
       </c>
-      <c r="C25" s="74" t="s">
+      <c r="C25" s="75" t="s">
         <v>302</v>
       </c>
-      <c r="D25" s="75" t="s">
+      <c r="D25" s="76" t="s">
         <v>303</v>
       </c>
-      <c r="E25" s="75"/>
-      <c r="F25" s="76" t="s">
+      <c r="E25" s="76"/>
+      <c r="F25" s="77" t="s">
         <v>304</v>
       </c>
-      <c r="G25" s="76"/>
-      <c r="H25" s="76"/>
+      <c r="G25" s="77"/>
+      <c r="H25" s="77"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="73" t="s">
+      <c r="B26" s="74" t="s">
         <v>305</v>
       </c>
       <c r="C26" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="D26" s="75" t="s">
+      <c r="D26" s="76" t="s">
         <v>307</v>
       </c>
-      <c r="E26" s="75"/>
-      <c r="F26" s="76" t="s">
+      <c r="E26" s="76"/>
+      <c r="F26" s="77" t="s">
         <v>308</v>
       </c>
-      <c r="G26" s="76"/>
-      <c r="H26" s="76"/>
+      <c r="G26" s="77"/>
+      <c r="H26" s="77"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="73" t="s">
+      <c r="B27" s="74" t="s">
         <v>309</v>
       </c>
       <c r="C27" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="D27" s="75" t="s">
+      <c r="D27" s="76" t="s">
         <v>310</v>
       </c>
-      <c r="E27" s="75"/>
-      <c r="F27" s="76" t="s">
+      <c r="E27" s="76"/>
+      <c r="F27" s="77" t="s">
         <v>311</v>
       </c>
-      <c r="G27" s="76"/>
-      <c r="H27" s="76"/>
+      <c r="G27" s="77"/>
+      <c r="H27" s="77"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="73" t="s">
+      <c r="B28" s="74" t="s">
         <v>312</v>
       </c>
       <c r="C28" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="D28" s="75" t="s">
+      <c r="D28" s="76" t="s">
         <v>313</v>
       </c>
-      <c r="E28" s="75"/>
-      <c r="F28" s="76" t="s">
+      <c r="E28" s="76"/>
+      <c r="F28" s="77" t="s">
         <v>314</v>
       </c>
-      <c r="G28" s="76"/>
-      <c r="H28" s="76"/>
+      <c r="G28" s="77"/>
+      <c r="H28" s="77"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="73" t="s">
+      <c r="B29" s="74" t="s">
         <v>315</v>
       </c>
       <c r="C29" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="D29" s="75" t="s">
+      <c r="D29" s="76" t="s">
         <v>316</v>
       </c>
-      <c r="E29" s="75"/>
-      <c r="F29" s="76" t="s">
+      <c r="E29" s="76"/>
+      <c r="F29" s="77" t="s">
         <v>317</v>
       </c>
-      <c r="G29" s="76"/>
-      <c r="H29" s="76"/>
+      <c r="G29" s="77"/>
+      <c r="H29" s="77"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="73" t="s">
+      <c r="B30" s="74" t="s">
         <v>318</v>
       </c>
       <c r="C30" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="D30" s="75" t="s">
+      <c r="D30" s="76" t="s">
         <v>319</v>
       </c>
-      <c r="E30" s="75"/>
-      <c r="F30" s="76" t="s">
+      <c r="E30" s="76"/>
+      <c r="F30" s="77" t="s">
         <v>320</v>
       </c>
-      <c r="G30" s="76"/>
-      <c r="H30" s="76"/>
+      <c r="G30" s="77"/>
+      <c r="H30" s="77"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="73" t="s">
+      <c r="B31" s="74" t="s">
         <v>321</v>
       </c>
       <c r="C31" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="D31" s="75" t="s">
+      <c r="D31" s="76" t="s">
         <v>322</v>
       </c>
-      <c r="E31" s="75"/>
-      <c r="F31" s="76" t="s">
+      <c r="E31" s="76"/>
+      <c r="F31" s="77" t="s">
         <v>323</v>
       </c>
-      <c r="G31" s="76"/>
-      <c r="H31" s="76"/>
+      <c r="G31" s="77"/>
+      <c r="H31" s="77"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="73" t="s">
+      <c r="B33" s="74" t="s">
         <v>273</v>
       </c>
       <c r="C33" s="62" t="s">
@@ -4343,22 +4359,21 @@
       <c r="F33" s="62"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="77" t="s">
+      <c r="B35" s="78" t="s">
         <v>325</v>
       </c>
-      <c r="C35" s="77"/>
-      <c r="D35" s="77"/>
-      <c r="E35" s="77"/>
-      <c r="F35" s="77"/>
-      <c r="G35" s="77"/>
-      <c r="H35" s="77"/>
+      <c r="C35" s="78"/>
+      <c r="D35" s="78"/>
+      <c r="E35" s="78"/>
+      <c r="F35" s="78"/>
+      <c r="G35" s="78"/>
+      <c r="H35" s="78"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="22">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C21:G21"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:H24"/>
@@ -4439,10 +4454,10 @@
       <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.25</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.25</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:G18">

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="326">
   <si>
     <t>SchoolStack - Assumptions &amp; Drivers</t>
   </si>
@@ -945,10 +945,10 @@
     <t>Break-even Year</t>
   </si>
   <si>
-    <t>Cash Runway</t>
-  </si>
-  <si>
-    <t>60+ months</t>
+    <t>Cash Runway (Months)</t>
+  </si>
+  <si>
+    <t>≥ 24 months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1190,7 +1190,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1225,6 +1225,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF8E1"/>
       </patternFill>
     </fill>
   </fills>
@@ -1297,7 +1302,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1393,7 +1398,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="169" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1403,7 +1410,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4137,10 +4149,18 @@
       <c r="C19" s="69">
         <v>3</v>
       </c>
-      <c r="D19" s="69"/>
-      <c r="E19" s="69"/>
-      <c r="F19" s="69"/>
-      <c r="G19" s="69"/>
+      <c r="D19" s="69">
+        <v>3</v>
+      </c>
+      <c r="E19" s="69">
+        <v>3</v>
+      </c>
+      <c r="F19" s="69">
+        <v>3</v>
+      </c>
+      <c r="G19" s="69">
+        <v>3</v>
+      </c>
       <c r="H19" s="68" t="s">
         <v>292</v>
       </c>
@@ -4177,19 +4197,19 @@
         <v>0</v>
       </c>
       <c r="D21" s="72" t="str">
-        <f>IF('5-Year P&amp;L'!C9&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year P&amp;L'!C9&gt;=0,'5-Year P&amp;L'!B9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="E21" s="32" t="str">
-        <f>IF('5-Year P&amp;L'!D9&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year P&amp;L'!D9&gt;=0,'5-Year P&amp;L'!C9&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
       <c r="F21" s="72" t="str">
-        <f>IF('5-Year P&amp;L'!E9&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year P&amp;L'!E9&gt;=0,'5-Year P&amp;L'!D9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="G21" s="72" t="str">
-        <f>IF('5-Year P&amp;L'!F9&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year P&amp;L'!F9&gt;=0,'5-Year P&amp;L'!E9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="H21" s="68" t="s">
@@ -4200,13 +4220,21 @@
       <c r="B22" s="62" t="s">
         <v>295</v>
       </c>
-      <c r="C22" s="73" t="s">
-        <v>296</v>
-      </c>
-      <c r="D22" s="73"/>
-      <c r="E22" s="73"/>
-      <c r="F22" s="73"/>
-      <c r="G22" s="73"/>
+      <c r="C22" s="73">
+        <v>0</v>
+      </c>
+      <c r="D22" s="73">
+        <v>2</v>
+      </c>
+      <c r="E22" s="73">
+        <v>8</v>
+      </c>
+      <c r="F22" s="74">
+        <v>16</v>
+      </c>
+      <c r="G22" s="69">
+        <v>25</v>
+      </c>
       <c r="H22" s="68" t="s">
         <v>296</v>
       </c>
@@ -4229,126 +4257,126 @@
       <c r="H24" s="5"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="74" t="s">
+      <c r="B25" s="75" t="s">
         <v>301</v>
       </c>
-      <c r="C25" s="75" t="s">
+      <c r="C25" s="76" t="s">
         <v>302</v>
       </c>
-      <c r="D25" s="76" t="s">
+      <c r="D25" s="77" t="s">
         <v>303</v>
       </c>
-      <c r="E25" s="76"/>
-      <c r="F25" s="77" t="s">
+      <c r="E25" s="77"/>
+      <c r="F25" s="78" t="s">
         <v>304</v>
       </c>
-      <c r="G25" s="77"/>
-      <c r="H25" s="77"/>
+      <c r="G25" s="78"/>
+      <c r="H25" s="78"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="74" t="s">
+      <c r="B26" s="75" t="s">
         <v>305</v>
       </c>
       <c r="C26" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="D26" s="76" t="s">
+      <c r="D26" s="77" t="s">
         <v>307</v>
       </c>
-      <c r="E26" s="76"/>
-      <c r="F26" s="77" t="s">
+      <c r="E26" s="77"/>
+      <c r="F26" s="78" t="s">
         <v>308</v>
       </c>
-      <c r="G26" s="77"/>
-      <c r="H26" s="77"/>
+      <c r="G26" s="78"/>
+      <c r="H26" s="78"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="74" t="s">
+      <c r="B27" s="75" t="s">
         <v>309</v>
       </c>
       <c r="C27" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="D27" s="76" t="s">
+      <c r="D27" s="77" t="s">
         <v>310</v>
       </c>
-      <c r="E27" s="76"/>
-      <c r="F27" s="77" t="s">
+      <c r="E27" s="77"/>
+      <c r="F27" s="78" t="s">
         <v>311</v>
       </c>
-      <c r="G27" s="77"/>
-      <c r="H27" s="77"/>
+      <c r="G27" s="78"/>
+      <c r="H27" s="78"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="74" t="s">
+      <c r="B28" s="75" t="s">
         <v>312</v>
       </c>
       <c r="C28" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="D28" s="76" t="s">
+      <c r="D28" s="77" t="s">
         <v>313</v>
       </c>
-      <c r="E28" s="76"/>
-      <c r="F28" s="77" t="s">
+      <c r="E28" s="77"/>
+      <c r="F28" s="78" t="s">
         <v>314</v>
       </c>
-      <c r="G28" s="77"/>
-      <c r="H28" s="77"/>
+      <c r="G28" s="78"/>
+      <c r="H28" s="78"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="74" t="s">
+      <c r="B29" s="75" t="s">
         <v>315</v>
       </c>
       <c r="C29" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="D29" s="76" t="s">
+      <c r="D29" s="77" t="s">
         <v>316</v>
       </c>
-      <c r="E29" s="76"/>
-      <c r="F29" s="77" t="s">
+      <c r="E29" s="77"/>
+      <c r="F29" s="78" t="s">
         <v>317</v>
       </c>
-      <c r="G29" s="77"/>
-      <c r="H29" s="77"/>
+      <c r="G29" s="78"/>
+      <c r="H29" s="78"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="74" t="s">
+      <c r="B30" s="75" t="s">
         <v>318</v>
       </c>
       <c r="C30" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="D30" s="76" t="s">
+      <c r="D30" s="77" t="s">
         <v>319</v>
       </c>
-      <c r="E30" s="76"/>
-      <c r="F30" s="77" t="s">
+      <c r="E30" s="77"/>
+      <c r="F30" s="78" t="s">
         <v>320</v>
       </c>
-      <c r="G30" s="77"/>
-      <c r="H30" s="77"/>
+      <c r="G30" s="78"/>
+      <c r="H30" s="78"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="74" t="s">
+      <c r="B31" s="75" t="s">
         <v>321</v>
       </c>
       <c r="C31" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="D31" s="76" t="s">
+      <c r="D31" s="77" t="s">
         <v>322</v>
       </c>
-      <c r="E31" s="76"/>
-      <c r="F31" s="77" t="s">
+      <c r="E31" s="77"/>
+      <c r="F31" s="78" t="s">
         <v>323</v>
       </c>
-      <c r="G31" s="77"/>
-      <c r="H31" s="77"/>
+      <c r="G31" s="78"/>
+      <c r="H31" s="78"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="74" t="s">
+      <c r="B33" s="75" t="s">
         <v>273</v>
       </c>
       <c r="C33" s="62" t="s">
@@ -4359,22 +4387,20 @@
       <c r="F33" s="62"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="78" t="s">
+      <c r="B35" s="79" t="s">
         <v>325</v>
       </c>
-      <c r="C35" s="78"/>
-      <c r="D35" s="78"/>
-      <c r="E35" s="78"/>
-      <c r="F35" s="78"/>
-      <c r="G35" s="78"/>
-      <c r="H35" s="78"/>
+      <c r="C35" s="79"/>
+      <c r="D35" s="79"/>
+      <c r="E35" s="79"/>
+      <c r="F35" s="79"/>
+      <c r="G35" s="79"/>
+      <c r="H35" s="79"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
@@ -999,7 +999,7 @@
     <t>Facility Burden</t>
   </si>
   <si>
-    <t>Facility costs at 9% of revenue are well-managed and leave budget for programs.</t>
+    <t>Facility costs at 6% of revenue are well-managed and leave budget for programs.</t>
   </si>
   <si>
     <t>Watch for rent escalation clauses that could push this higher over time.</t>
@@ -1302,7 +1302,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1398,6 +1398,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4100,20 +4103,20 @@
       <c r="B17" s="62" t="s">
         <v>287</v>
       </c>
-      <c r="C17" s="66">
-        <v>0.12690818289991795</v>
+      <c r="C17" s="69">
+        <v>0.21888750812095942</v>
       </c>
       <c r="D17" s="66">
-        <v>0.10558030759473601</v>
+        <v>0.1151339781195497</v>
       </c>
       <c r="E17" s="66">
-        <v>0.09437095069492152</v>
+        <v>0.07904835385509698</v>
       </c>
       <c r="F17" s="66">
-        <v>0.09071556220943976</v>
+        <v>0.06474930412628371</v>
       </c>
       <c r="G17" s="66">
-        <v>0.08997708510145823</v>
+        <v>0.06122075900007716</v>
       </c>
       <c r="H17" s="68" t="s">
         <v>288</v>
@@ -4146,19 +4149,19 @@
       <c r="B19" s="62" t="s">
         <v>291</v>
       </c>
-      <c r="C19" s="69">
+      <c r="C19" s="70">
         <v>3</v>
       </c>
-      <c r="D19" s="69">
+      <c r="D19" s="70">
         <v>3</v>
       </c>
-      <c r="E19" s="69">
+      <c r="E19" s="70">
         <v>3</v>
       </c>
-      <c r="F19" s="69">
+      <c r="F19" s="70">
         <v>3</v>
       </c>
-      <c r="G19" s="69">
+      <c r="G19" s="70">
         <v>3</v>
       </c>
       <c r="H19" s="68" t="s">
@@ -4169,19 +4172,19 @@
       <c r="B20" s="62" t="s">
         <v>199</v>
       </c>
-      <c r="C20" s="70">
+      <c r="C20" s="71">
         <v>-1.7175671166388593</v>
       </c>
-      <c r="D20" s="71">
+      <c r="D20" s="72">
         <v>4.488973003061509</v>
       </c>
-      <c r="E20" s="71">
+      <c r="E20" s="72">
         <v>15.16683551349847</v>
       </c>
-      <c r="F20" s="71">
+      <c r="F20" s="72">
         <v>27.909361844303376</v>
       </c>
-      <c r="G20" s="71">
+      <c r="G20" s="72">
         <v>34.33953455066237</v>
       </c>
       <c r="H20" s="68" t="s">
@@ -4192,11 +4195,11 @@
       <c r="B21" s="62" t="s">
         <v>294</v>
       </c>
-      <c r="C21" s="72" t="str">
+      <c r="C21" s="73" t="str">
         <f>IF('5-Year P&amp;L'!B9&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="72" t="str">
+      <c r="D21" s="73" t="str">
         <f>IF(AND('5-Year P&amp;L'!C9&gt;=0,'5-Year P&amp;L'!B9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
@@ -4204,11 +4207,11 @@
         <f>IF(AND('5-Year P&amp;L'!D9&gt;=0,'5-Year P&amp;L'!C9&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="F21" s="72" t="str">
+      <c r="F21" s="73" t="str">
         <f>IF(AND('5-Year P&amp;L'!E9&gt;=0,'5-Year P&amp;L'!D9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="72" t="str">
+      <c r="G21" s="73" t="str">
         <f>IF(AND('5-Year P&amp;L'!F9&gt;=0,'5-Year P&amp;L'!E9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
@@ -4220,19 +4223,19 @@
       <c r="B22" s="62" t="s">
         <v>295</v>
       </c>
-      <c r="C22" s="73">
+      <c r="C22" s="74">
         <v>0</v>
       </c>
-      <c r="D22" s="73">
+      <c r="D22" s="74">
         <v>2</v>
       </c>
-      <c r="E22" s="73">
+      <c r="E22" s="74">
         <v>8</v>
       </c>
-      <c r="F22" s="74">
+      <c r="F22" s="75">
         <v>16</v>
       </c>
-      <c r="G22" s="69">
+      <c r="G22" s="70">
         <v>25</v>
       </c>
       <c r="H22" s="68" t="s">
@@ -4257,126 +4260,126 @@
       <c r="H24" s="5"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="75" t="s">
+      <c r="B25" s="76" t="s">
         <v>301</v>
       </c>
-      <c r="C25" s="76" t="s">
+      <c r="C25" s="77" t="s">
         <v>302</v>
       </c>
-      <c r="D25" s="77" t="s">
+      <c r="D25" s="78" t="s">
         <v>303</v>
       </c>
-      <c r="E25" s="77"/>
-      <c r="F25" s="78" t="s">
+      <c r="E25" s="78"/>
+      <c r="F25" s="79" t="s">
         <v>304</v>
       </c>
-      <c r="G25" s="78"/>
-      <c r="H25" s="78"/>
+      <c r="G25" s="79"/>
+      <c r="H25" s="79"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="75" t="s">
+      <c r="B26" s="76" t="s">
         <v>305</v>
       </c>
       <c r="C26" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="D26" s="77" t="s">
+      <c r="D26" s="78" t="s">
         <v>307</v>
       </c>
-      <c r="E26" s="77"/>
-      <c r="F26" s="78" t="s">
+      <c r="E26" s="78"/>
+      <c r="F26" s="79" t="s">
         <v>308</v>
       </c>
-      <c r="G26" s="78"/>
-      <c r="H26" s="78"/>
+      <c r="G26" s="79"/>
+      <c r="H26" s="79"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="75" t="s">
+      <c r="B27" s="76" t="s">
         <v>309</v>
       </c>
       <c r="C27" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="D27" s="77" t="s">
+      <c r="D27" s="78" t="s">
         <v>310</v>
       </c>
-      <c r="E27" s="77"/>
-      <c r="F27" s="78" t="s">
+      <c r="E27" s="78"/>
+      <c r="F27" s="79" t="s">
         <v>311</v>
       </c>
-      <c r="G27" s="78"/>
-      <c r="H27" s="78"/>
+      <c r="G27" s="79"/>
+      <c r="H27" s="79"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="75" t="s">
+      <c r="B28" s="76" t="s">
         <v>312</v>
       </c>
       <c r="C28" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="D28" s="77" t="s">
+      <c r="D28" s="78" t="s">
         <v>313</v>
       </c>
-      <c r="E28" s="77"/>
-      <c r="F28" s="78" t="s">
+      <c r="E28" s="78"/>
+      <c r="F28" s="79" t="s">
         <v>314</v>
       </c>
-      <c r="G28" s="78"/>
-      <c r="H28" s="78"/>
+      <c r="G28" s="79"/>
+      <c r="H28" s="79"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="75" t="s">
+      <c r="B29" s="76" t="s">
         <v>315</v>
       </c>
       <c r="C29" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="D29" s="77" t="s">
+      <c r="D29" s="78" t="s">
         <v>316</v>
       </c>
-      <c r="E29" s="77"/>
-      <c r="F29" s="78" t="s">
+      <c r="E29" s="78"/>
+      <c r="F29" s="79" t="s">
         <v>317</v>
       </c>
-      <c r="G29" s="78"/>
-      <c r="H29" s="78"/>
+      <c r="G29" s="79"/>
+      <c r="H29" s="79"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="75" t="s">
+      <c r="B30" s="76" t="s">
         <v>318</v>
       </c>
       <c r="C30" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="D30" s="77" t="s">
+      <c r="D30" s="78" t="s">
         <v>319</v>
       </c>
-      <c r="E30" s="77"/>
-      <c r="F30" s="78" t="s">
+      <c r="E30" s="78"/>
+      <c r="F30" s="79" t="s">
         <v>320</v>
       </c>
-      <c r="G30" s="78"/>
-      <c r="H30" s="78"/>
+      <c r="G30" s="79"/>
+      <c r="H30" s="79"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="75" t="s">
+      <c r="B31" s="76" t="s">
         <v>321</v>
       </c>
       <c r="C31" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="D31" s="77" t="s">
+      <c r="D31" s="78" t="s">
         <v>322</v>
       </c>
-      <c r="E31" s="77"/>
-      <c r="F31" s="78" t="s">
+      <c r="E31" s="78"/>
+      <c r="F31" s="79" t="s">
         <v>323</v>
       </c>
-      <c r="G31" s="78"/>
-      <c r="H31" s="78"/>
+      <c r="G31" s="79"/>
+      <c r="H31" s="79"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="75" t="s">
+      <c r="B33" s="76" t="s">
         <v>273</v>
       </c>
       <c r="C33" s="62" t="s">
@@ -4387,15 +4390,15 @@
       <c r="F33" s="62"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="79" t="s">
+      <c r="B35" s="80" t="s">
         <v>325</v>
       </c>
-      <c r="C35" s="79"/>
-      <c r="D35" s="79"/>
-      <c r="E35" s="79"/>
-      <c r="F35" s="79"/>
-      <c r="G35" s="79"/>
-      <c r="H35" s="79"/>
+      <c r="C35" s="80"/>
+      <c r="D35" s="80"/>
+      <c r="E35" s="80"/>
+      <c r="F35" s="80"/>
+      <c r="G35" s="80"/>
+      <c r="H35" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="20">

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
@@ -1008,7 +1008,7 @@
     <t>Debt Affordability</t>
   </si>
   <si>
-    <t>DSCR of 34.34x provides comfortable coverage of debt payments with room to spare.</t>
+    <t>DSCR of 48.12x provides comfortable coverage of debt payments with room to spare.</t>
   </si>
   <si>
     <t>Maintain this ratio as you take on any additional debt.</t>
@@ -1026,7 +1026,7 @@
     <t>Reserve Strength</t>
   </si>
   <si>
-    <t>25.1 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+    <t>25.3 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
   </si>
   <si>
     <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
@@ -3978,19 +3978,19 @@
         <v>169</v>
       </c>
       <c r="C11" s="61">
-        <v>164825</v>
+        <v>49825</v>
       </c>
       <c r="D11" s="61">
-        <v>89825</v>
+        <v>49825</v>
       </c>
       <c r="E11" s="61">
-        <v>89825</v>
+        <v>49825</v>
       </c>
       <c r="F11" s="61">
-        <v>74825</v>
+        <v>49825</v>
       </c>
       <c r="G11" s="61">
-        <v>69825</v>
+        <v>49825</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -4173,19 +4173,19 @@
         <v>199</v>
       </c>
       <c r="C20" s="71">
-        <v>-1.7175671166388593</v>
+        <v>-5.681846462619167</v>
       </c>
       <c r="D20" s="72">
-        <v>4.488973003061509</v>
+        <v>8.092764676367285</v>
       </c>
       <c r="E20" s="72">
-        <v>15.16683551349847</v>
+        <v>27.342920220772704</v>
       </c>
       <c r="F20" s="72">
-        <v>27.909361844303376</v>
+        <v>41.91305569493226</v>
       </c>
       <c r="G20" s="72">
-        <v>34.33953455066237</v>
+        <v>48.12359257400903</v>
       </c>
       <c r="H20" s="68" t="s">
         <v>293</v>

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
@@ -1008,7 +1008,7 @@
     <t>Debt Affordability</t>
   </si>
   <si>
-    <t>DSCR of 48.12x provides comfortable coverage of debt payments with room to spare.</t>
+    <t>DSCR of 34.34x provides comfortable coverage of debt payments with room to spare.</t>
   </si>
   <si>
     <t>Maintain this ratio as you take on any additional debt.</t>
@@ -1026,7 +1026,7 @@
     <t>Reserve Strength</t>
   </si>
   <si>
-    <t>25.3 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+    <t>25.1 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
   </si>
   <si>
     <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
@@ -3978,19 +3978,19 @@
         <v>169</v>
       </c>
       <c r="C11" s="61">
-        <v>49825</v>
+        <v>164825</v>
       </c>
       <c r="D11" s="61">
-        <v>49825</v>
+        <v>89825</v>
       </c>
       <c r="E11" s="61">
-        <v>49825</v>
+        <v>89825</v>
       </c>
       <c r="F11" s="61">
-        <v>49825</v>
+        <v>74825</v>
       </c>
       <c r="G11" s="61">
-        <v>49825</v>
+        <v>69825</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -4173,19 +4173,19 @@
         <v>199</v>
       </c>
       <c r="C20" s="71">
-        <v>-5.681846462619167</v>
+        <v>-1.7175671166388593</v>
       </c>
       <c r="D20" s="72">
-        <v>8.092764676367285</v>
+        <v>4.488973003061509</v>
       </c>
       <c r="E20" s="72">
-        <v>27.342920220772704</v>
+        <v>15.16683551349847</v>
       </c>
       <c r="F20" s="72">
-        <v>41.91305569493226</v>
+        <v>27.909361844303376</v>
       </c>
       <c r="G20" s="72">
-        <v>48.12359257400903</v>
+        <v>34.33953455066237</v>
       </c>
       <c r="H20" s="68" t="s">
         <v>293</v>

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
@@ -798,7 +798,7 @@
     <t>Charter School  |  OH  |  Est. 2026</t>
   </si>
   <si>
-    <t>Prepared March 26, 2026</t>
+    <t>Prepared March 27, 2026</t>
   </si>
   <si>
     <t>Cash Balance</t>
@@ -825,7 +825,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>March 26, 2026</t>
+    <t>March 27, 2026</t>
   </si>
   <si>
     <t>UNDERWRITING HIGHLIGHTS</t>
@@ -885,7 +885,7 @@
     <t>Civic Scholars Charter — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated March 26, 2026</t>
+    <t>Generated March 27, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
@@ -708,13 +708,13 @@
     <t>DSCR ≥ 1.20x (2026-27)</t>
   </si>
   <si>
-    <t>-5.68x</t>
+    <t>-5.09x</t>
   </si>
   <si>
     <t>Min 2 Months Cash Reserve (2026-27)</t>
   </si>
   <si>
-    <t>0.4 months</t>
+    <t>0.6 months</t>
   </si>
   <si>
     <t>Positive Net Income (2026-27)</t>
@@ -780,7 +780,7 @@
     <t>2026-27 Cash Reserve (Months)</t>
   </si>
   <si>
-    <t>0.4</t>
+    <t>0.6</t>
   </si>
   <si>
     <t>Break-Even Year</t>
@@ -990,7 +990,7 @@
     <t>Staffing Burden</t>
   </si>
   <si>
-    <t>Staffing at 24% of revenue leaves room for facilities, programs, and reserves.</t>
+    <t>Staffing at 41% of revenue leaves room for facilities, programs, and reserves.</t>
   </si>
   <si>
     <t>As you add staff, ensure staffing stays below 60% of revenue.</t>
@@ -1008,7 +1008,7 @@
     <t>Debt Affordability</t>
   </si>
   <si>
-    <t>DSCR of 48.12x provides comfortable coverage of debt payments with room to spare.</t>
+    <t>DSCR of 30.43x provides comfortable coverage of debt payments with room to spare.</t>
   </si>
   <si>
     <t>Maintain this ratio as you take on any additional debt.</t>
@@ -1026,7 +1026,7 @@
     <t>Reserve Strength</t>
   </si>
   <si>
-    <t>25.3 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+    <t>11.3 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
   </si>
   <si>
     <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
@@ -1302,7 +1302,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1391,6 +1391,9 @@
     <xf numFmtId="165" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="165" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1398,9 +1401,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1414,9 +1414,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2232,23 +2229,23 @@
       </c>
       <c r="B3" s="15">
         <f>'Staffing Plan'!B28</f>
-        <v>1026431</v>
+        <v>997040</v>
       </c>
       <c r="C3" s="15">
         <f>'Staffing Plan'!C28</f>
-        <v>1231718</v>
+        <v>1478601</v>
       </c>
       <c r="D3" s="15">
         <f>'Staffing Plan'!D28</f>
-        <v>1231718</v>
+        <v>1796022</v>
       </c>
       <c r="E3" s="15">
         <f>'Staffing Plan'!E28</f>
-        <v>1231718</v>
+        <v>2042905</v>
       </c>
       <c r="F3" s="15">
         <f>'Staffing Plan'!F28</f>
-        <v>1231718</v>
+        <v>2113443</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2302,23 +2299,23 @@
       </c>
       <c r="B6" s="28">
         <f>SUM(B3:B5)</f>
-        <v>1736256</v>
+        <v>1706865</v>
       </c>
       <c r="C6" s="28">
         <f>SUM(C3:C5)</f>
-        <v>2209403</v>
+        <v>2456286</v>
       </c>
       <c r="D6" s="28">
         <f>SUM(D3:D5)</f>
-        <v>2512064</v>
+        <v>3076368</v>
       </c>
       <c r="E6" s="28">
         <f>SUM(E3:E5)</f>
-        <v>2745632</v>
+        <v>3556819</v>
       </c>
       <c r="F6" s="28">
         <f>SUM(F3:F5)</f>
-        <v>2856467</v>
+        <v>3738192</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2327,23 +2324,23 @@
       </c>
       <c r="B7" s="29">
         <f>B2-B6</f>
-        <v>-447923</v>
+        <v>-418532</v>
       </c>
       <c r="C7" s="30">
         <f>C2-C6</f>
-        <v>313398</v>
+        <v>66515</v>
       </c>
       <c r="D7" s="30">
         <f>D2-D6</f>
-        <v>1272536</v>
+        <v>708232</v>
       </c>
       <c r="E7" s="30">
         <f>E2-E6</f>
-        <v>2013494</v>
+        <v>1202307</v>
       </c>
       <c r="F7" s="30">
         <f>F2-F6</f>
-        <v>2327934</v>
+        <v>1446209</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2352,23 +2349,23 @@
       </c>
       <c r="B8" s="14">
         <f>IF(B2=0,0,B7/B2)</f>
-        <v>-0.35</v>
+        <v>-0.32</v>
       </c>
       <c r="C8" s="14">
         <f>IF(C2=0,0,C7/C2)</f>
-        <v>0.12</v>
+        <v>0.03</v>
       </c>
       <c r="D8" s="14">
         <f>IF(D2=0,0,D7/D2)</f>
-        <v>0.34</v>
+        <v>0.19</v>
       </c>
       <c r="E8" s="14">
         <f>IF(E2=0,0,E7/E2)</f>
-        <v>0.42</v>
+        <v>0.25</v>
       </c>
       <c r="F8" s="14">
         <f>IF(F2=0,0,F7/F2)</f>
-        <v>0.45</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2377,23 +2374,23 @@
       </c>
       <c r="B9" s="27">
         <f>B7</f>
-        <v>-447923</v>
+        <v>-418532</v>
       </c>
       <c r="C9" s="27">
         <f>B9+C7</f>
-        <v>-134525</v>
+        <v>-352017</v>
       </c>
       <c r="D9" s="27">
         <f>C9+D7</f>
-        <v>1138011</v>
+        <v>356215</v>
       </c>
       <c r="E9" s="27">
         <f>D9+E7</f>
-        <v>3151505</v>
+        <v>1558522</v>
       </c>
       <c r="F9" s="27">
         <f>E9+F7</f>
-        <v>5479439</v>
+        <v>3004731</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2473,19 +2470,19 @@
         <v>185</v>
       </c>
       <c r="B3" s="15">
-        <v>52077</v>
+        <v>81468</v>
       </c>
       <c r="C3" s="15">
-        <v>365475</v>
+        <v>147983</v>
       </c>
       <c r="D3" s="15">
-        <v>1638011</v>
+        <v>856215</v>
       </c>
       <c r="E3" s="15">
-        <v>3651505</v>
+        <v>2058522</v>
       </c>
       <c r="F3" s="15">
-        <v>5979439</v>
+        <v>3504731</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2514,23 +2511,23 @@
       </c>
       <c r="B5" s="16">
         <f>SUM(B3:B4)</f>
-        <v>52077</v>
+        <v>81468</v>
       </c>
       <c r="C5" s="16">
         <f>SUM(C3:C4)</f>
-        <v>365475</v>
+        <v>147983</v>
       </c>
       <c r="D5" s="16">
         <f>SUM(D3:D4)</f>
-        <v>1638011</v>
+        <v>856215</v>
       </c>
       <c r="E5" s="16">
         <f>SUM(E3:E4)</f>
-        <v>3651505</v>
+        <v>2058522</v>
       </c>
       <c r="F5" s="16">
         <f>SUM(F3:F4)</f>
-        <v>5979439</v>
+        <v>3504731</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2626,16 +2623,16 @@
         <v>0</v>
       </c>
       <c r="C13" s="15">
-        <v>-426848</v>
+        <v>-397457</v>
       </c>
       <c r="D13" s="15">
-        <v>-91164</v>
+        <v>-308656</v>
       </c>
       <c r="E13" s="15">
-        <v>1204940</v>
+        <v>423144</v>
       </c>
       <c r="F13" s="15">
-        <v>3243357</v>
+        <v>1650374</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2643,19 +2640,19 @@
         <v>194</v>
       </c>
       <c r="B14" s="15">
-        <v>-426848</v>
+        <v>-397457</v>
       </c>
       <c r="C14" s="15">
-        <v>335684</v>
+        <v>88801</v>
       </c>
       <c r="D14" s="15">
-        <v>1296104</v>
+        <v>731800</v>
       </c>
       <c r="E14" s="15">
-        <v>2038417</v>
+        <v>1227230</v>
       </c>
       <c r="F14" s="15">
-        <v>2354290</v>
+        <v>1472565</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2664,23 +2661,23 @@
       </c>
       <c r="B15" s="16">
         <f>B5-B10</f>
-        <v>-426848</v>
+        <v>-397457</v>
       </c>
       <c r="C15" s="16">
         <f>C5-C10</f>
-        <v>-91164</v>
+        <v>-308656</v>
       </c>
       <c r="D15" s="16">
         <f>D5-D10</f>
-        <v>1204940</v>
+        <v>423144</v>
       </c>
       <c r="E15" s="16">
         <f>E5-E10</f>
-        <v>3243357</v>
+        <v>1650374</v>
       </c>
       <c r="F15" s="16">
         <f>F5-F10</f>
-        <v>5597647</v>
+        <v>3122939</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -2765,19 +2762,19 @@
         <v>198</v>
       </c>
       <c r="B3" s="15">
-        <v>-283098</v>
+        <v>-253707</v>
       </c>
       <c r="C3" s="15">
-        <v>403222</v>
+        <v>156339</v>
       </c>
       <c r="D3" s="15">
-        <v>1362361</v>
+        <v>798057</v>
       </c>
       <c r="E3" s="15">
-        <v>2088318</v>
+        <v>1277131</v>
       </c>
       <c r="F3" s="15">
-        <v>2397758</v>
+        <v>1516033</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2806,23 +2803,23 @@
       </c>
       <c r="B5" s="33">
         <f>IF(B4=0,"N/A",B3/B4)</f>
-        <v>-5.68</v>
+        <v>-5.09</v>
       </c>
       <c r="C5" s="33">
         <f>IF(C4=0,"N/A",C3/C4)</f>
-        <v>8.09</v>
+        <v>3.14</v>
       </c>
       <c r="D5" s="33">
         <f>IF(D4=0,"N/A",D3/D4)</f>
-        <v>27.34</v>
+        <v>16.02</v>
       </c>
       <c r="E5" s="33">
         <f>IF(E4=0,"N/A",E3/E4)</f>
-        <v>41.91</v>
+        <v>25.63</v>
       </c>
       <c r="F5" s="33">
         <f>IF(F4=0,"N/A",F3/F4)</f>
-        <v>48.12</v>
+        <v>30.43</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2840,19 +2837,19 @@
         <v>201</v>
       </c>
       <c r="B8" s="15">
-        <v>52077</v>
+        <v>81468</v>
       </c>
       <c r="C8" s="15">
-        <v>365475</v>
+        <v>147983</v>
       </c>
       <c r="D8" s="15">
-        <v>1638011</v>
+        <v>856215</v>
       </c>
       <c r="E8" s="15">
-        <v>3651505</v>
+        <v>2058522</v>
       </c>
       <c r="F8" s="15">
-        <v>5979439</v>
+        <v>3504731</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2860,19 +2857,19 @@
         <v>202</v>
       </c>
       <c r="B9" s="15">
-        <v>130953</v>
+        <v>128503</v>
       </c>
       <c r="C9" s="15">
-        <v>176632</v>
+        <v>197205</v>
       </c>
       <c r="D9" s="15">
-        <v>201853</v>
+        <v>248879</v>
       </c>
       <c r="E9" s="15">
-        <v>222567</v>
+        <v>290166</v>
       </c>
       <c r="F9" s="15">
-        <v>232220</v>
+        <v>305697</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2881,23 +2878,23 @@
       </c>
       <c r="B10" s="34">
         <f>IF(B9=0,0,B8/B9)</f>
-        <v>0.4</v>
+        <v>0.63</v>
       </c>
       <c r="C10" s="34">
         <f>IF(C9=0,0,C8/C9)</f>
-        <v>2.07</v>
+        <v>0.75</v>
       </c>
       <c r="D10" s="34">
         <f>IF(D9=0,0,D8/D9)</f>
-        <v>8.11</v>
+        <v>3.44</v>
       </c>
       <c r="E10" s="34">
         <f>IF(E9=0,0,E8/E9)</f>
-        <v>16.41</v>
+        <v>7.09</v>
       </c>
       <c r="F10" s="34">
         <f>IF(F9=0,0,F8/F9)</f>
-        <v>25.75</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2905,19 +2902,19 @@
         <v>204</v>
       </c>
       <c r="B11" s="35">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C11" s="35">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="D11" s="35">
-        <v>247</v>
+        <v>105</v>
       </c>
       <c r="E11" s="35">
-        <v>499</v>
+        <v>216</v>
       </c>
       <c r="F11" s="35">
-        <v>783</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2963,9 +2960,9 @@
         <f>IF(B10&gt;=2,"PASS","FAIL")</f>
         <v>FAIL</v>
       </c>
-      <c r="C15" s="37" t="str">
+      <c r="C15" s="36" t="str">
         <f>IF(C10&gt;=2,"PASS","FAIL")</f>
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="D15" s="37" t="str">
         <f>IF(D10&gt;=2,"PASS","FAIL")</f>
@@ -3173,7 +3170,7 @@
         <v>233</v>
       </c>
       <c r="B18" s="18">
-        <v>1736256</v>
+        <v>1706865</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -3181,7 +3178,7 @@
         <v>234</v>
       </c>
       <c r="B19" s="18">
-        <v>-447923</v>
+        <v>-418532</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -3189,7 +3186,7 @@
         <v>235</v>
       </c>
       <c r="B20" s="41">
-        <v>-0.34767641595767557</v>
+        <v>-0.32486321471234536</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -3205,7 +3202,7 @@
         <v>236</v>
       </c>
       <c r="B22" s="18">
-        <v>52077</v>
+        <v>81468</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -3253,7 +3250,7 @@
         <v>243</v>
       </c>
       <c r="B28" s="18">
-        <v>14469</v>
+        <v>14224</v>
       </c>
     </row>
   </sheetData>
@@ -3398,23 +3395,23 @@
       </c>
       <c r="B9" s="15">
         <f>'5-Year P&amp;L'!B6</f>
-        <v>1736256</v>
+        <v>1706865</v>
       </c>
       <c r="C9" s="15">
         <f>'5-Year P&amp;L'!C6</f>
-        <v>2209403</v>
+        <v>2456286</v>
       </c>
       <c r="D9" s="15">
         <f>'5-Year P&amp;L'!D6</f>
-        <v>2512064</v>
+        <v>3076368</v>
       </c>
       <c r="E9" s="15">
         <f>'5-Year P&amp;L'!E6</f>
-        <v>2745632</v>
+        <v>3556819</v>
       </c>
       <c r="F9" s="15">
         <f>'5-Year P&amp;L'!F6</f>
-        <v>2856467</v>
+        <v>3738192</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3423,23 +3420,23 @@
       </c>
       <c r="B10" s="23">
         <f>'5-Year P&amp;L'!B7</f>
-        <v>-447923</v>
+        <v>-418532</v>
       </c>
       <c r="C10" s="23">
         <f>'5-Year P&amp;L'!C7</f>
-        <v>313398</v>
+        <v>66515</v>
       </c>
       <c r="D10" s="23">
         <f>'5-Year P&amp;L'!D7</f>
-        <v>1272536</v>
+        <v>708232</v>
       </c>
       <c r="E10" s="23">
         <f>'5-Year P&amp;L'!E7</f>
-        <v>2013494</v>
+        <v>1202307</v>
       </c>
       <c r="F10" s="23">
         <f>'5-Year P&amp;L'!F7</f>
-        <v>2327934</v>
+        <v>1446209</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -3448,23 +3445,23 @@
       </c>
       <c r="B11" s="14">
         <f>IF(B8=0,0,B10/B8)</f>
-        <v>-0.35</v>
+        <v>-0.32</v>
       </c>
       <c r="C11" s="14">
         <f>IF(C8=0,0,C10/C8)</f>
-        <v>0.12</v>
+        <v>0.03</v>
       </c>
       <c r="D11" s="14">
         <f>IF(D8=0,0,D10/D8)</f>
-        <v>0.34</v>
+        <v>0.19</v>
       </c>
       <c r="E11" s="14">
         <f>IF(E8=0,0,E10/E8)</f>
-        <v>0.42</v>
+        <v>0.25</v>
       </c>
       <c r="F11" s="14">
         <f>IF(F8=0,0,F10/F8)</f>
-        <v>0.45</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -3473,23 +3470,23 @@
       </c>
       <c r="B12" s="27">
         <f>B10</f>
-        <v>-447923</v>
+        <v>-418532</v>
       </c>
       <c r="C12" s="27">
         <f>B12+C10</f>
-        <v>-134525</v>
+        <v>-352017</v>
       </c>
       <c r="D12" s="27">
         <f>C12+D10</f>
-        <v>1138011</v>
+        <v>356215</v>
       </c>
       <c r="E12" s="27">
         <f>D12+E10</f>
-        <v>3151505</v>
+        <v>1558522</v>
       </c>
       <c r="F12" s="27">
         <f>E12+F10</f>
-        <v>5479439</v>
+        <v>3004731</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -3497,19 +3494,19 @@
         <v>247</v>
       </c>
       <c r="B13" s="27">
-        <v>52077</v>
+        <v>81468</v>
       </c>
       <c r="C13" s="27">
-        <v>365475</v>
+        <v>147983</v>
       </c>
       <c r="D13" s="27">
-        <v>1638011</v>
+        <v>856215</v>
       </c>
       <c r="E13" s="27">
-        <v>3651505</v>
+        <v>2058522</v>
       </c>
       <c r="F13" s="27">
-        <v>5979439</v>
+        <v>3504731</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -3537,19 +3534,19 @@
         <v>122</v>
       </c>
       <c r="B15" s="15">
-        <v>14469</v>
+        <v>14224</v>
       </c>
       <c r="C15" s="15">
-        <v>11047</v>
+        <v>12281</v>
       </c>
       <c r="D15" s="15">
-        <v>8374</v>
+        <v>10255</v>
       </c>
       <c r="E15" s="15">
-        <v>7322</v>
+        <v>9485</v>
       </c>
       <c r="F15" s="15">
-        <v>7141</v>
+        <v>9345</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -3557,19 +3554,19 @@
         <v>199</v>
       </c>
       <c r="B16" s="33">
-        <v>-5.68</v>
+        <v>-5.09</v>
       </c>
       <c r="C16" s="33">
-        <v>8.09</v>
+        <v>3.14</v>
       </c>
       <c r="D16" s="33">
-        <v>27.34</v>
+        <v>16.02</v>
       </c>
       <c r="E16" s="33">
-        <v>41.91</v>
+        <v>25.63</v>
       </c>
       <c r="F16" s="33">
-        <v>48.12</v>
+        <v>30.43</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -3676,7 +3673,7 @@
         <v>258</v>
       </c>
       <c r="C17" s="27">
-        <v>2327934</v>
+        <v>1446209</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
@@ -3684,7 +3681,7 @@
         <v>201</v>
       </c>
       <c r="C18" s="27">
-        <v>5479439</v>
+        <v>3004731</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
@@ -3938,19 +3935,19 @@
         <v>167</v>
       </c>
       <c r="C9" s="61">
-        <v>1026431</v>
+        <v>997040</v>
       </c>
       <c r="D9" s="61">
-        <v>1231718</v>
+        <v>1478601</v>
       </c>
       <c r="E9" s="61">
-        <v>1231718</v>
+        <v>1796022</v>
       </c>
       <c r="F9" s="61">
-        <v>1231718</v>
+        <v>2042905</v>
       </c>
       <c r="G9" s="61">
-        <v>1231718</v>
+        <v>2113443</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -3998,19 +3995,19 @@
         <v>179</v>
       </c>
       <c r="C12" s="63">
-        <v>-447923</v>
+        <v>-418532</v>
       </c>
       <c r="D12" s="64">
-        <v>313398</v>
+        <v>66515</v>
       </c>
       <c r="E12" s="64">
-        <v>1272536</v>
+        <v>708232</v>
       </c>
       <c r="F12" s="64">
-        <v>2013494</v>
+        <v>1202307</v>
       </c>
       <c r="G12" s="64">
-        <v>2327934</v>
+        <v>1446209</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
@@ -4018,19 +4015,19 @@
         <v>282</v>
       </c>
       <c r="C13" s="64">
-        <v>52077</v>
+        <v>81468</v>
       </c>
       <c r="D13" s="64">
-        <v>365475</v>
+        <v>147983</v>
       </c>
       <c r="E13" s="64">
-        <v>1638011</v>
+        <v>856215</v>
       </c>
       <c r="F13" s="64">
-        <v>3651505</v>
+        <v>2058522</v>
       </c>
       <c r="G13" s="64">
-        <v>5979439</v>
+        <v>3504731</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
@@ -4038,41 +4035,41 @@
         <v>283</v>
       </c>
       <c r="C14" s="65">
-        <v>-0.34767641595767557</v>
+        <v>-0.32486321471234536</v>
       </c>
       <c r="D14" s="66">
-        <v>0.12422625654035199</v>
-      </c>
-      <c r="E14" s="66">
-        <v>0.3362405538233895</v>
-      </c>
-      <c r="F14" s="66">
-        <v>0.42308071336642766</v>
-      </c>
-      <c r="G14" s="66">
-        <v>0.44902669547102847</v>
+        <v>0.026365546218487395</v>
+      </c>
+      <c r="E14" s="67">
+        <v>0.1871352322570417</v>
+      </c>
+      <c r="F14" s="67">
+        <v>0.25263194389725</v>
+      </c>
+      <c r="G14" s="67">
+        <v>0.27895397731656507</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="62" t="s">
         <v>248</v>
       </c>
-      <c r="C15" s="67">
+      <c r="C15" s="68">
         <v>10736.108333333334</v>
       </c>
-      <c r="D15" s="67">
+      <c r="D15" s="68">
         <v>12614</v>
       </c>
-      <c r="E15" s="67">
+      <c r="E15" s="68">
         <v>12615.333333333334</v>
       </c>
-      <c r="F15" s="67">
+      <c r="F15" s="68">
         <v>12691</v>
       </c>
-      <c r="G15" s="67">
+      <c r="G15" s="68">
         <v>12961</v>
       </c>
-      <c r="H15" s="68" t="s">
+      <c r="H15" s="69" t="s">
         <v>284</v>
       </c>
     </row>
@@ -4081,21 +4078,21 @@
         <v>285</v>
       </c>
       <c r="C16" s="65">
-        <v>0.7967124959152642</v>
+        <v>0.7738992946699339</v>
       </c>
       <c r="D16" s="66">
-        <v>0.4882345013477089</v>
-      </c>
-      <c r="E16" s="66">
-        <v>0.3254552660783174</v>
-      </c>
-      <c r="F16" s="66">
-        <v>0.25881186142410634</v>
-      </c>
-      <c r="G16" s="66">
-        <v>0.23758159092662604</v>
-      </c>
-      <c r="H16" s="68" t="s">
+        <v>0.5860952116695735</v>
+      </c>
+      <c r="E16" s="67">
+        <v>0.47456058764466524</v>
+      </c>
+      <c r="F16" s="67">
+        <v>0.429260630893284</v>
+      </c>
+      <c r="G16" s="67">
+        <v>0.4076543090810894</v>
+      </c>
+      <c r="H16" s="69" t="s">
         <v>286</v>
       </c>
     </row>
@@ -4103,22 +4100,22 @@
       <c r="B17" s="62" t="s">
         <v>287</v>
       </c>
-      <c r="C17" s="69">
+      <c r="C17" s="66">
         <v>0.21888750812095942</v>
       </c>
-      <c r="D17" s="66">
+      <c r="D17" s="67">
         <v>0.1151339781195497</v>
       </c>
-      <c r="E17" s="66">
+      <c r="E17" s="67">
         <v>0.07904835385509698</v>
       </c>
-      <c r="F17" s="66">
+      <c r="F17" s="67">
         <v>0.06474930412628371</v>
       </c>
-      <c r="G17" s="66">
+      <c r="G17" s="67">
         <v>0.06122075900007716</v>
       </c>
-      <c r="H17" s="68" t="s">
+      <c r="H17" s="69" t="s">
         <v>288</v>
       </c>
     </row>
@@ -4127,21 +4124,21 @@
         <v>289</v>
       </c>
       <c r="C18" s="65">
-        <v>-0.219739772248324</v>
+        <v>-0.1969265710029938</v>
       </c>
       <c r="D18" s="66">
-        <v>0.15983114000317108</v>
-      </c>
-      <c r="E18" s="66">
-        <v>0.3599748982719442</v>
-      </c>
-      <c r="F18" s="66">
-        <v>0.4388029312110945</v>
-      </c>
-      <c r="G18" s="66">
-        <v>0.46249479206851324</v>
-      </c>
-      <c r="H18" s="68" t="s">
+        <v>0.061970429681306484</v>
+      </c>
+      <c r="E18" s="67">
+        <v>0.21086957670559636</v>
+      </c>
+      <c r="F18" s="67">
+        <v>0.26835416174191684</v>
+      </c>
+      <c r="G18" s="67">
+        <v>0.29242207391404984</v>
+      </c>
+      <c r="H18" s="69" t="s">
         <v>290</v>
       </c>
     </row>
@@ -4164,7 +4161,7 @@
       <c r="G19" s="70">
         <v>3</v>
       </c>
-      <c r="H19" s="68" t="s">
+      <c r="H19" s="69" t="s">
         <v>292</v>
       </c>
     </row>
@@ -4173,21 +4170,21 @@
         <v>199</v>
       </c>
       <c r="C20" s="71">
-        <v>-5.681846462619167</v>
+        <v>-5.091961866532865</v>
       </c>
       <c r="D20" s="72">
-        <v>8.092764676367285</v>
+        <v>3.137762167586553</v>
       </c>
       <c r="E20" s="72">
-        <v>27.342920220772704</v>
+        <v>16.017200200702458</v>
       </c>
       <c r="F20" s="72">
-        <v>41.91305569493226</v>
+        <v>25.632333166081285</v>
       </c>
       <c r="G20" s="72">
-        <v>48.12359257400903</v>
-      </c>
-      <c r="H20" s="68" t="s">
+        <v>30.42715504264927</v>
+      </c>
+      <c r="H20" s="69" t="s">
         <v>293</v>
       </c>
     </row>
@@ -4215,7 +4212,7 @@
         <f>IF(AND('5-Year P&amp;L'!F9&gt;=0,'5-Year P&amp;L'!E9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="68" t="s">
+      <c r="H21" s="69" t="s">
         <v>23</v>
       </c>
     </row>
@@ -4224,21 +4221,21 @@
         <v>295</v>
       </c>
       <c r="C22" s="74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" s="74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="74">
-        <v>8</v>
-      </c>
-      <c r="F22" s="75">
-        <v>16</v>
-      </c>
-      <c r="G22" s="70">
-        <v>25</v>
-      </c>
-      <c r="H22" s="68" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="74">
+        <v>7</v>
+      </c>
+      <c r="G22" s="74">
+        <v>11</v>
+      </c>
+      <c r="H22" s="69" t="s">
         <v>296</v>
       </c>
     </row>
@@ -4260,126 +4257,126 @@
       <c r="H24" s="5"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="76" t="s">
+      <c r="B25" s="75" t="s">
         <v>301</v>
       </c>
-      <c r="C25" s="77" t="s">
+      <c r="C25" s="76" t="s">
         <v>302</v>
       </c>
-      <c r="D25" s="78" t="s">
+      <c r="D25" s="77" t="s">
         <v>303</v>
       </c>
-      <c r="E25" s="78"/>
-      <c r="F25" s="79" t="s">
+      <c r="E25" s="77"/>
+      <c r="F25" s="78" t="s">
         <v>304</v>
       </c>
-      <c r="G25" s="79"/>
-      <c r="H25" s="79"/>
+      <c r="G25" s="78"/>
+      <c r="H25" s="78"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="76" t="s">
+      <c r="B26" s="75" t="s">
         <v>305</v>
       </c>
       <c r="C26" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="D26" s="78" t="s">
+      <c r="D26" s="77" t="s">
         <v>307</v>
       </c>
-      <c r="E26" s="78"/>
-      <c r="F26" s="79" t="s">
+      <c r="E26" s="77"/>
+      <c r="F26" s="78" t="s">
         <v>308</v>
       </c>
-      <c r="G26" s="79"/>
-      <c r="H26" s="79"/>
+      <c r="G26" s="78"/>
+      <c r="H26" s="78"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="76" t="s">
+      <c r="B27" s="75" t="s">
         <v>309</v>
       </c>
       <c r="C27" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="D27" s="78" t="s">
+      <c r="D27" s="77" t="s">
         <v>310</v>
       </c>
-      <c r="E27" s="78"/>
-      <c r="F27" s="79" t="s">
+      <c r="E27" s="77"/>
+      <c r="F27" s="78" t="s">
         <v>311</v>
       </c>
-      <c r="G27" s="79"/>
-      <c r="H27" s="79"/>
+      <c r="G27" s="78"/>
+      <c r="H27" s="78"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="76" t="s">
+      <c r="B28" s="75" t="s">
         <v>312</v>
       </c>
       <c r="C28" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="D28" s="78" t="s">
+      <c r="D28" s="77" t="s">
         <v>313</v>
       </c>
-      <c r="E28" s="78"/>
-      <c r="F28" s="79" t="s">
+      <c r="E28" s="77"/>
+      <c r="F28" s="78" t="s">
         <v>314</v>
       </c>
-      <c r="G28" s="79"/>
-      <c r="H28" s="79"/>
+      <c r="G28" s="78"/>
+      <c r="H28" s="78"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="76" t="s">
+      <c r="B29" s="75" t="s">
         <v>315</v>
       </c>
       <c r="C29" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="D29" s="78" t="s">
+      <c r="D29" s="77" t="s">
         <v>316</v>
       </c>
-      <c r="E29" s="78"/>
-      <c r="F29" s="79" t="s">
+      <c r="E29" s="77"/>
+      <c r="F29" s="78" t="s">
         <v>317</v>
       </c>
-      <c r="G29" s="79"/>
-      <c r="H29" s="79"/>
+      <c r="G29" s="78"/>
+      <c r="H29" s="78"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="76" t="s">
+      <c r="B30" s="75" t="s">
         <v>318</v>
       </c>
       <c r="C30" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="D30" s="78" t="s">
+      <c r="D30" s="77" t="s">
         <v>319</v>
       </c>
-      <c r="E30" s="78"/>
-      <c r="F30" s="79" t="s">
+      <c r="E30" s="77"/>
+      <c r="F30" s="78" t="s">
         <v>320</v>
       </c>
-      <c r="G30" s="79"/>
-      <c r="H30" s="79"/>
+      <c r="G30" s="78"/>
+      <c r="H30" s="78"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="76" t="s">
+      <c r="B31" s="75" t="s">
         <v>321</v>
       </c>
       <c r="C31" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="D31" s="78" t="s">
+      <c r="D31" s="77" t="s">
         <v>322</v>
       </c>
-      <c r="E31" s="78"/>
-      <c r="F31" s="79" t="s">
+      <c r="E31" s="77"/>
+      <c r="F31" s="78" t="s">
         <v>323</v>
       </c>
-      <c r="G31" s="79"/>
-      <c r="H31" s="79"/>
+      <c r="G31" s="78"/>
+      <c r="H31" s="78"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="76" t="s">
+      <c r="B33" s="75" t="s">
         <v>273</v>
       </c>
       <c r="C33" s="62" t="s">
@@ -4390,15 +4387,15 @@
       <c r="F33" s="62"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="80" t="s">
+      <c r="B35" s="79" t="s">
         <v>325</v>
       </c>
-      <c r="C35" s="80"/>
-      <c r="D35" s="80"/>
-      <c r="E35" s="80"/>
-      <c r="F35" s="80"/>
-      <c r="G35" s="80"/>
-      <c r="H35" s="80"/>
+      <c r="C35" s="79"/>
+      <c r="D35" s="79"/>
+      <c r="E35" s="79"/>
+      <c r="F35" s="79"/>
+      <c r="G35" s="79"/>
+      <c r="H35" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -6238,7 +6235,7 @@
         <v>135</v>
       </c>
       <c r="B14" s="22">
-        <v>261905</v>
+        <v>257007</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -6246,7 +6243,7 @@
         <v>136</v>
       </c>
       <c r="B15" s="22">
-        <v>26895</v>
+        <v>26650</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -6255,7 +6252,7 @@
       </c>
       <c r="B16" s="23">
         <f>SUM(B9:B15)</f>
-        <v>564800</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -6264,7 +6261,7 @@
       </c>
       <c r="B18" s="24">
         <f>B6-B16</f>
-        <v>-64800</v>
+        <v>-59657</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
@@ -6562,34 +6559,34 @@
         <v>167</v>
       </c>
       <c r="B3" s="15">
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="C3" s="15">
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="D3" s="15">
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="E3" s="15">
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="F3" s="15">
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="G3" s="15">
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="H3" s="15">
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="I3" s="15">
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="J3" s="15">
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="K3" s="15">
-        <v>102644</v>
+        <v>99704</v>
       </c>
       <c r="L3" s="15">
         <v>0</v>
@@ -6599,7 +6596,7 @@
       </c>
       <c r="N3" s="15">
         <f>SUM(B3:M3)</f>
-        <v>1026431</v>
+        <v>997040</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -6698,43 +6695,43 @@
       </c>
       <c r="B6" s="23">
         <f>SUM(B3:B5)</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="C6" s="23">
         <f>SUM(C3:C5)</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="D6" s="23">
         <f>SUM(D3:D5)</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="E6" s="23">
         <f>SUM(E3:E5)</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="F6" s="23">
         <f>SUM(F3:F5)</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="G6" s="23">
         <f>SUM(G3:G5)</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="H6" s="23">
         <f>SUM(H3:H5)</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="I6" s="23">
         <f>SUM(I3:I5)</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="J6" s="23">
         <f>SUM(J3:J5)</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="K6" s="23">
         <f>SUM(K3:K5)</f>
-        <v>170879</v>
+        <v>167939</v>
       </c>
       <c r="L6" s="23">
         <f>SUM(L3:L5)</f>
@@ -6746,7 +6743,7 @@
       </c>
       <c r="N6" s="23">
         <f>SUM(B6:M6)</f>
-        <v>1736256</v>
+        <v>1706865</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -6755,43 +6752,43 @@
       </c>
       <c r="B7" s="27">
         <f>B2-B6</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="C7" s="27">
         <f>C2-C6</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="D7" s="27">
         <f>D2-D6</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="E7" s="27">
         <f>E2-E6</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="F7" s="27">
         <f>F2-F6</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="G7" s="27">
         <f>G2-G6</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="H7" s="27">
         <f>H2-H6</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="I7" s="27">
         <f>I2-I6</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="J7" s="27">
         <f>J2-J6</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="K7" s="27">
         <f>K2-K6</f>
-        <v>-273946</v>
+        <v>-271006</v>
       </c>
       <c r="L7" s="27">
         <f>L2-L6</f>
@@ -6803,7 +6800,7 @@
       </c>
       <c r="N7" s="27">
         <f>SUM(B7:M7)</f>
-        <v>-447923</v>
+        <v>-418532</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -6812,55 +6809,55 @@
       </c>
       <c r="B8" s="27">
         <f>500000+B7</f>
-        <v>483722</v>
+        <v>486661</v>
       </c>
       <c r="C8" s="27">
         <f>B8+C7</f>
-        <v>467444</v>
+        <v>473322</v>
       </c>
       <c r="D8" s="27">
         <f>C8+D7</f>
-        <v>451166</v>
+        <v>459983</v>
       </c>
       <c r="E8" s="27">
         <f>D8+E7</f>
-        <v>434888</v>
+        <v>446644</v>
       </c>
       <c r="F8" s="27">
         <f>E8+F7</f>
-        <v>418610</v>
+        <v>433305</v>
       </c>
       <c r="G8" s="27">
         <f>F8+G7</f>
-        <v>402332</v>
+        <v>419966</v>
       </c>
       <c r="H8" s="27">
         <f>G8+H7</f>
-        <v>386054</v>
+        <v>406627</v>
       </c>
       <c r="I8" s="27">
         <f>H8+I7</f>
-        <v>369776</v>
+        <v>393288</v>
       </c>
       <c r="J8" s="27">
         <f>I8+J7</f>
-        <v>353498</v>
+        <v>379949</v>
       </c>
       <c r="K8" s="27">
         <f>J8+K7</f>
-        <v>79552</v>
+        <v>108943</v>
       </c>
       <c r="L8" s="27">
         <f>K8+L7</f>
-        <v>65817</v>
+        <v>95208</v>
       </c>
       <c r="M8" s="27">
         <f>L8+M7</f>
-        <v>52077</v>
+        <v>81468</v>
       </c>
       <c r="N8" s="27">
         <f>M8</f>
-        <v>52077</v>
+        <v>81468</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -6895,7 +6892,7 @@
       </c>
       <c r="B12" s="18">
         <f>M8</f>
-        <v>52077</v>
+        <v>81468</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -6904,7 +6901,7 @@
       </c>
       <c r="B13" s="19">
         <f>MIN(B8:M8)</f>
-        <v>52077</v>
+        <v>81468</v>
       </c>
     </row>
   </sheetData>

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
@@ -50,7 +50,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'Underwriting Snapshot'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'Summary'!$A1:$F18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="13">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="15">'Financial Health'!$A1:$H35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'Financial Health'!$A1:$H36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="15">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="327">
   <si>
     <t>SchoolStack - Assumptions &amp; Drivers</t>
   </si>
@@ -949,6 +949,9 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -3824,7 +3827,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -4239,170 +4242,191 @@
         <v>296</v>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="5" t="s">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="62" t="s">
+        <v>204</v>
+      </c>
+      <c r="C23" s="74">
+        <v>19</v>
+      </c>
+      <c r="D23" s="74">
+        <v>22</v>
+      </c>
+      <c r="E23" s="70">
+        <v>103</v>
+      </c>
+      <c r="F23" s="70">
+        <v>213</v>
+      </c>
+      <c r="G23" s="70">
+        <v>344</v>
+      </c>
+      <c r="H23" s="69" t="s">
         <v>297</v>
       </c>
-      <c r="C24" s="5" t="s">
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="C25" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5" t="s">
+      <c r="D25" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="75" t="s">
+      <c r="E25" s="5"/>
+      <c r="F25" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="C25" s="76" t="s">
-        <v>302</v>
-      </c>
-      <c r="D25" s="77" t="s">
-        <v>303</v>
-      </c>
-      <c r="E25" s="77"/>
-      <c r="F25" s="78" t="s">
-        <v>304</v>
-      </c>
-      <c r="G25" s="78"/>
-      <c r="H25" s="78"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="75" t="s">
-        <v>305</v>
-      </c>
-      <c r="C26" s="32" t="s">
-        <v>306</v>
+        <v>302</v>
+      </c>
+      <c r="C26" s="76" t="s">
+        <v>303</v>
       </c>
       <c r="D26" s="77" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="E26" s="77"/>
       <c r="F26" s="78" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="G26" s="78"/>
       <c r="H26" s="78"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="75" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C27" s="32" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D27" s="77" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E27" s="77"/>
       <c r="F27" s="78" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G27" s="78"/>
       <c r="H27" s="78"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="75" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C28" s="32" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D28" s="77" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E28" s="77"/>
       <c r="F28" s="78" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G28" s="78"/>
       <c r="H28" s="78"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="75" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C29" s="32" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D29" s="77" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E29" s="77"/>
       <c r="F29" s="78" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="G29" s="78"/>
       <c r="H29" s="78"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="75" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C30" s="32" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D30" s="77" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E30" s="77"/>
       <c r="F30" s="78" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="G30" s="78"/>
       <c r="H30" s="78"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="75" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C31" s="32" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D31" s="77" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E31" s="77"/>
       <c r="F31" s="78" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G31" s="78"/>
       <c r="H31" s="78"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="75" t="s">
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="75" t="s">
+        <v>322</v>
+      </c>
+      <c r="C32" s="32" t="s">
+        <v>307</v>
+      </c>
+      <c r="D32" s="77" t="s">
+        <v>323</v>
+      </c>
+      <c r="E32" s="77"/>
+      <c r="F32" s="78" t="s">
+        <v>324</v>
+      </c>
+      <c r="G32" s="78"/>
+      <c r="H32" s="78"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B34" s="75" t="s">
         <v>273</v>
       </c>
-      <c r="C33" s="62" t="s">
-        <v>324</v>
-      </c>
-      <c r="D33" s="62"/>
-      <c r="E33" s="62"/>
-      <c r="F33" s="62"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="79" t="s">
+      <c r="C34" s="62" t="s">
         <v>325</v>
       </c>
-      <c r="C35" s="79"/>
-      <c r="D35" s="79"/>
-      <c r="E35" s="79"/>
-      <c r="F35" s="79"/>
-      <c r="G35" s="79"/>
-      <c r="H35" s="79"/>
+      <c r="D34" s="62"/>
+      <c r="E34" s="62"/>
+      <c r="F34" s="62"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="79" t="s">
+        <v>326</v>
+      </c>
+      <c r="C36" s="79"/>
+      <c r="D36" s="79"/>
+      <c r="E36" s="79"/>
+      <c r="F36" s="79"/>
+      <c r="G36" s="79"/>
+      <c r="H36" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:H25"/>
     <mergeCell ref="D26:E26"/>
@@ -4417,8 +4441,10 @@
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="B36:H36"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
@@ -50,7 +50,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'Underwriting Snapshot'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'Summary'!$A1:$F18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="13">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="15">'Financial Health'!$A1:$H36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'Financial Health'!$A1:$H40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="15">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="331">
   <si>
     <t>SchoolStack - Assumptions &amp; Drivers</t>
   </si>
@@ -913,6 +913,18 @@
   </si>
   <si>
     <t>≥ $10,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
   </si>
   <si>
     <t>Payroll %</t>
@@ -1305,7 +1317,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1404,6 +1416,18 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3827,7 +3851,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H36"/>
+  <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -4076,365 +4100,440 @@
         <v>284</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="62" t="s">
+        <v>122</v>
+      </c>
+      <c r="C16" s="70">
+        <v>13265.541666666666</v>
+      </c>
+      <c r="D16" s="70">
+        <v>12081.43</v>
+      </c>
+      <c r="E16" s="70">
+        <v>10121.226666666667</v>
+      </c>
+      <c r="F16" s="70">
+        <v>9418.184</v>
+      </c>
+      <c r="G16" s="70">
+        <v>9295.48</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="13" t="s">
         <v>285</v>
       </c>
-      <c r="C16" s="65">
-        <v>0.7738992946699339</v>
-      </c>
-      <c r="D16" s="66">
-        <v>0.5860952116695735</v>
-      </c>
-      <c r="E16" s="67">
-        <v>0.47456058764466524</v>
-      </c>
-      <c r="F16" s="67">
-        <v>0.429260630893284</v>
-      </c>
-      <c r="G16" s="67">
-        <v>0.4076543090810894</v>
-      </c>
-      <c r="H16" s="69" t="s">
+      <c r="C17" s="61">
+        <v>0</v>
+      </c>
+      <c r="D17" s="61">
+        <v>0</v>
+      </c>
+      <c r="E17" s="61">
+        <v>0</v>
+      </c>
+      <c r="F17" s="61">
+        <v>0</v>
+      </c>
+      <c r="G17" s="61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="13" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="62" t="s">
+      <c r="C18" s="71">
+        <v>2350</v>
+      </c>
+      <c r="D18" s="68">
+        <v>1452.3</v>
+      </c>
+      <c r="E18" s="68">
+        <v>997.2213333333334</v>
+      </c>
+      <c r="F18" s="68">
+        <v>821.7334186666667</v>
+      </c>
+      <c r="G18" s="68">
+        <v>793.4822574000001</v>
+      </c>
+      <c r="H18" s="69" t="s">
         <v>287</v>
       </c>
-      <c r="C17" s="66">
-        <v>0.21888750812095942</v>
-      </c>
-      <c r="D17" s="67">
-        <v>0.1151339781195497</v>
-      </c>
-      <c r="E17" s="67">
-        <v>0.07904835385509698</v>
-      </c>
-      <c r="F17" s="67">
-        <v>0.06474930412628371</v>
-      </c>
-      <c r="G17" s="67">
-        <v>0.06122075900007716</v>
-      </c>
-      <c r="H17" s="69" t="s">
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="62" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="62" t="s">
-        <v>289</v>
-      </c>
-      <c r="C18" s="65">
-        <v>-0.1969265710029938</v>
-      </c>
-      <c r="D18" s="66">
-        <v>0.061970429681306484</v>
-      </c>
-      <c r="E18" s="67">
-        <v>0.21086957670559636</v>
-      </c>
-      <c r="F18" s="67">
-        <v>0.26835416174191684</v>
-      </c>
-      <c r="G18" s="67">
-        <v>0.29242207391404984</v>
-      </c>
-      <c r="H18" s="69" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="62" t="s">
-        <v>291</v>
-      </c>
-      <c r="C19" s="70">
-        <v>3</v>
-      </c>
-      <c r="D19" s="70">
-        <v>3</v>
-      </c>
-      <c r="E19" s="70">
-        <v>3</v>
-      </c>
-      <c r="F19" s="70">
-        <v>3</v>
-      </c>
-      <c r="G19" s="70">
-        <v>3</v>
-      </c>
-      <c r="H19" s="69" t="s">
-        <v>292</v>
+      <c r="C19" s="72">
+        <v>-3487.766666666667</v>
+      </c>
+      <c r="D19" s="73">
+        <v>332.575</v>
+      </c>
+      <c r="E19" s="73">
+        <v>2360.7733333333335</v>
+      </c>
+      <c r="F19" s="73">
+        <v>3206.152</v>
+      </c>
+      <c r="G19" s="73">
+        <v>3615.5225</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="62" t="s">
-        <v>199</v>
-      </c>
-      <c r="C20" s="71">
-        <v>-5.091961866532865</v>
-      </c>
-      <c r="D20" s="72">
-        <v>3.137762167586553</v>
-      </c>
-      <c r="E20" s="72">
-        <v>16.017200200702458</v>
-      </c>
-      <c r="F20" s="72">
-        <v>25.632333166081285</v>
-      </c>
-      <c r="G20" s="72">
-        <v>30.42715504264927</v>
+        <v>289</v>
+      </c>
+      <c r="C20" s="65">
+        <v>0.7738992946699339</v>
+      </c>
+      <c r="D20" s="66">
+        <v>0.5860952116695735</v>
+      </c>
+      <c r="E20" s="67">
+        <v>0.47456058764466524</v>
+      </c>
+      <c r="F20" s="67">
+        <v>0.429260630893284</v>
+      </c>
+      <c r="G20" s="67">
+        <v>0.4076543090810894</v>
       </c>
       <c r="H20" s="69" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="62" t="s">
+        <v>291</v>
+      </c>
+      <c r="C21" s="66">
+        <v>0.21888750812095942</v>
+      </c>
+      <c r="D21" s="67">
+        <v>0.1151339781195497</v>
+      </c>
+      <c r="E21" s="67">
+        <v>0.07904835385509698</v>
+      </c>
+      <c r="F21" s="67">
+        <v>0.06474930412628371</v>
+      </c>
+      <c r="G21" s="67">
+        <v>0.06122075900007716</v>
+      </c>
+      <c r="H21" s="69" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="62" t="s">
+        <v>293</v>
+      </c>
+      <c r="C22" s="65">
+        <v>-0.1969265710029938</v>
+      </c>
+      <c r="D22" s="66">
+        <v>0.061970429681306484</v>
+      </c>
+      <c r="E22" s="67">
+        <v>0.21086957670559636</v>
+      </c>
+      <c r="F22" s="67">
+        <v>0.26835416174191684</v>
+      </c>
+      <c r="G22" s="67">
+        <v>0.29242207391404984</v>
+      </c>
+      <c r="H22" s="69" t="s">
         <v>294</v>
       </c>
-      <c r="C21" s="73" t="str">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="62" t="s">
+        <v>295</v>
+      </c>
+      <c r="C23" s="74">
+        <v>3</v>
+      </c>
+      <c r="D23" s="74">
+        <v>3</v>
+      </c>
+      <c r="E23" s="74">
+        <v>3</v>
+      </c>
+      <c r="F23" s="74">
+        <v>3</v>
+      </c>
+      <c r="G23" s="74">
+        <v>3</v>
+      </c>
+      <c r="H23" s="69" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="62" t="s">
+        <v>199</v>
+      </c>
+      <c r="C24" s="75">
+        <v>-5.091961866532865</v>
+      </c>
+      <c r="D24" s="76">
+        <v>3.137762167586553</v>
+      </c>
+      <c r="E24" s="76">
+        <v>16.017200200702458</v>
+      </c>
+      <c r="F24" s="76">
+        <v>25.632333166081285</v>
+      </c>
+      <c r="G24" s="76">
+        <v>30.42715504264927</v>
+      </c>
+      <c r="H24" s="69" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="62" t="s">
+        <v>298</v>
+      </c>
+      <c r="C25" s="77" t="str">
         <f>IF('5-Year P&amp;L'!B9&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="73" t="str">
+      <c r="D25" s="77" t="str">
         <f>IF(AND('5-Year P&amp;L'!C9&gt;=0,'5-Year P&amp;L'!B9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="32" t="str">
+      <c r="E25" s="32" t="str">
         <f>IF(AND('5-Year P&amp;L'!D9&gt;=0,'5-Year P&amp;L'!C9&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="F21" s="73" t="str">
+      <c r="F25" s="77" t="str">
         <f>IF(AND('5-Year P&amp;L'!E9&gt;=0,'5-Year P&amp;L'!D9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="73" t="str">
+      <c r="G25" s="77" t="str">
         <f>IF(AND('5-Year P&amp;L'!F9&gt;=0,'5-Year P&amp;L'!E9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="69" t="s">
+      <c r="H25" s="69" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="62" t="s">
-        <v>295</v>
-      </c>
-      <c r="C22" s="74">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="62" t="s">
+        <v>299</v>
+      </c>
+      <c r="C26" s="78">
         <v>1</v>
       </c>
-      <c r="D22" s="74">
+      <c r="D26" s="78">
         <v>1</v>
       </c>
-      <c r="E22" s="74">
+      <c r="E26" s="78">
         <v>3</v>
       </c>
-      <c r="F22" s="74">
+      <c r="F26" s="78">
         <v>7</v>
       </c>
-      <c r="G22" s="74">
+      <c r="G26" s="78">
         <v>11</v>
       </c>
-      <c r="H22" s="69" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="62" t="s">
+      <c r="H26" s="69" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="62" t="s">
         <v>204</v>
       </c>
-      <c r="C23" s="74">
+      <c r="C27" s="78">
         <v>19</v>
       </c>
-      <c r="D23" s="74">
+      <c r="D27" s="78">
         <v>22</v>
       </c>
-      <c r="E23" s="70">
+      <c r="E27" s="74">
         <v>103</v>
       </c>
-      <c r="F23" s="70">
+      <c r="F27" s="74">
         <v>213</v>
       </c>
-      <c r="G23" s="70">
+      <c r="G27" s="74">
         <v>344</v>
       </c>
-      <c r="H23" s="69" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5" t="s">
+      <c r="H27" s="69" t="s">
         <v>301</v>
       </c>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="75" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="C26" s="76" t="s">
+      <c r="C29" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="D26" s="77" t="s">
+      <c r="D29" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="E26" s="77"/>
-      <c r="F26" s="78" t="s">
+      <c r="E29" s="5"/>
+      <c r="F29" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="G26" s="78"/>
-      <c r="H26" s="78"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="75" t="s">
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="79" t="s">
         <v>306</v>
       </c>
-      <c r="C27" s="32" t="s">
+      <c r="C30" s="80" t="s">
         <v>307</v>
       </c>
-      <c r="D27" s="77" t="s">
+      <c r="D30" s="81" t="s">
         <v>308</v>
       </c>
-      <c r="E27" s="77"/>
-      <c r="F27" s="78" t="s">
+      <c r="E30" s="81"/>
+      <c r="F30" s="82" t="s">
         <v>309</v>
       </c>
-      <c r="G27" s="78"/>
-      <c r="H27" s="78"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="75" t="s">
+      <c r="G30" s="82"/>
+      <c r="H30" s="82"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="79" t="s">
         <v>310</v>
       </c>
-      <c r="C28" s="32" t="s">
-        <v>307</v>
-      </c>
-      <c r="D28" s="77" t="s">
+      <c r="C31" s="32" t="s">
         <v>311</v>
       </c>
-      <c r="E28" s="77"/>
-      <c r="F28" s="78" t="s">
+      <c r="D31" s="81" t="s">
         <v>312</v>
       </c>
-      <c r="G28" s="78"/>
-      <c r="H28" s="78"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="75" t="s">
+      <c r="E31" s="81"/>
+      <c r="F31" s="82" t="s">
         <v>313</v>
       </c>
-      <c r="C29" s="32" t="s">
-        <v>307</v>
-      </c>
-      <c r="D29" s="77" t="s">
+      <c r="G31" s="82"/>
+      <c r="H31" s="82"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="79" t="s">
         <v>314</v>
       </c>
-      <c r="E29" s="77"/>
-      <c r="F29" s="78" t="s">
+      <c r="C32" s="32" t="s">
+        <v>311</v>
+      </c>
+      <c r="D32" s="81" t="s">
         <v>315</v>
       </c>
-      <c r="G29" s="78"/>
-      <c r="H29" s="78"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="75" t="s">
+      <c r="E32" s="81"/>
+      <c r="F32" s="82" t="s">
         <v>316</v>
       </c>
-      <c r="C30" s="32" t="s">
-        <v>307</v>
-      </c>
-      <c r="D30" s="77" t="s">
+      <c r="G32" s="82"/>
+      <c r="H32" s="82"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="79" t="s">
         <v>317</v>
       </c>
-      <c r="E30" s="77"/>
-      <c r="F30" s="78" t="s">
+      <c r="C33" s="32" t="s">
+        <v>311</v>
+      </c>
+      <c r="D33" s="81" t="s">
         <v>318</v>
       </c>
-      <c r="G30" s="78"/>
-      <c r="H30" s="78"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="75" t="s">
+      <c r="E33" s="81"/>
+      <c r="F33" s="82" t="s">
         <v>319</v>
       </c>
-      <c r="C31" s="32" t="s">
-        <v>307</v>
-      </c>
-      <c r="D31" s="77" t="s">
+      <c r="G33" s="82"/>
+      <c r="H33" s="82"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="79" t="s">
         <v>320</v>
       </c>
-      <c r="E31" s="77"/>
-      <c r="F31" s="78" t="s">
+      <c r="C34" s="32" t="s">
+        <v>311</v>
+      </c>
+      <c r="D34" s="81" t="s">
         <v>321</v>
       </c>
-      <c r="G31" s="78"/>
-      <c r="H31" s="78"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="75" t="s">
+      <c r="E34" s="81"/>
+      <c r="F34" s="82" t="s">
         <v>322</v>
       </c>
-      <c r="C32" s="32" t="s">
-        <v>307</v>
-      </c>
-      <c r="D32" s="77" t="s">
+      <c r="G34" s="82"/>
+      <c r="H34" s="82"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="79" t="s">
         <v>323</v>
       </c>
-      <c r="E32" s="77"/>
-      <c r="F32" s="78" t="s">
+      <c r="C35" s="32" t="s">
+        <v>311</v>
+      </c>
+      <c r="D35" s="81" t="s">
         <v>324</v>
       </c>
-      <c r="G32" s="78"/>
-      <c r="H32" s="78"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B34" s="75" t="s">
-        <v>273</v>
-      </c>
-      <c r="C34" s="62" t="s">
+      <c r="E35" s="81"/>
+      <c r="F35" s="82" t="s">
         <v>325</v>
       </c>
-      <c r="D34" s="62"/>
-      <c r="E34" s="62"/>
-      <c r="F34" s="62"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G35" s="82"/>
+      <c r="H35" s="82"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="79" t="s">
         <v>326</v>
       </c>
-      <c r="C36" s="79"/>
-      <c r="D36" s="79"/>
-      <c r="E36" s="79"/>
-      <c r="F36" s="79"/>
-      <c r="G36" s="79"/>
-      <c r="H36" s="79"/>
+      <c r="C36" s="32" t="s">
+        <v>311</v>
+      </c>
+      <c r="D36" s="81" t="s">
+        <v>327</v>
+      </c>
+      <c r="E36" s="81"/>
+      <c r="F36" s="82" t="s">
+        <v>328</v>
+      </c>
+      <c r="G36" s="82"/>
+      <c r="H36" s="82"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="79" t="s">
+        <v>273</v>
+      </c>
+      <c r="C38" s="62" t="s">
+        <v>329</v>
+      </c>
+      <c r="D38" s="62"/>
+      <c r="E38" s="62"/>
+      <c r="F38" s="62"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="83" t="s">
+        <v>330</v>
+      </c>
+      <c r="C40" s="83"/>
+      <c r="D40" s="83"/>
+      <c r="E40" s="83"/>
+      <c r="F40" s="83"/>
+      <c r="G40" s="83"/>
+      <c r="H40" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
@@ -4443,8 +4542,16 @@
     <mergeCell ref="F31:H31"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="F32:H32"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -4490,48 +4597,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C24:G24">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C20&gt;=1.25</formula>
+      <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1</formula>
+      <formula>C24&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1</formula>
+      <formula>C24&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
@@ -50,7 +50,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'Underwriting Snapshot'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'Summary'!$A1:$F18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="13">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="15">'Financial Health'!$A1:$H40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'Financial Health'!$A1:$H35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="15">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="326">
   <si>
     <t>SchoolStack - Assumptions &amp; Drivers</t>
   </si>
@@ -708,13 +708,13 @@
     <t>DSCR ≥ 1.20x (2026-27)</t>
   </si>
   <si>
-    <t>-5.09x</t>
+    <t>-5.68x</t>
   </si>
   <si>
     <t>Min 2 Months Cash Reserve (2026-27)</t>
   </si>
   <si>
-    <t>0.6 months</t>
+    <t>0.4 months</t>
   </si>
   <si>
     <t>Positive Net Income (2026-27)</t>
@@ -780,7 +780,7 @@
     <t>2026-27 Cash Reserve (Months)</t>
   </si>
   <si>
-    <t>0.6</t>
+    <t>0.4</t>
   </si>
   <si>
     <t>Break-Even Year</t>
@@ -915,18 +915,6 @@
     <t>≥ $10,000</t>
   </si>
   <si>
-    <t xml:space="preserve">  Instructional / Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Facility / Student</t>
-  </si>
-  <si>
-    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
-  </si>
-  <si>
-    <t>Surplus per Student</t>
-  </si>
-  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -963,9 +951,6 @@
     <t>≥ 24 months</t>
   </si>
   <si>
-    <t>≥ 90 days</t>
-  </si>
-  <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
   </si>
   <si>
@@ -1005,7 +990,7 @@
     <t>Staffing Burden</t>
   </si>
   <si>
-    <t>Staffing at 41% of revenue leaves room for facilities, programs, and reserves.</t>
+    <t>Staffing at 24% of revenue leaves room for facilities, programs, and reserves.</t>
   </si>
   <si>
     <t>As you add staff, ensure staffing stays below 60% of revenue.</t>
@@ -1023,7 +1008,7 @@
     <t>Debt Affordability</t>
   </si>
   <si>
-    <t>DSCR of 30.43x provides comfortable coverage of debt payments with room to spare.</t>
+    <t>DSCR of 48.12x provides comfortable coverage of debt payments with room to spare.</t>
   </si>
   <si>
     <t>Maintain this ratio as you take on any additional debt.</t>
@@ -1041,7 +1026,7 @@
     <t>Reserve Strength</t>
   </si>
   <si>
-    <t>11.3 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+    <t>25.3 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
   </si>
   <si>
     <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
@@ -1317,7 +1302,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1406,9 +1391,6 @@
     <xf numFmtId="165" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="165" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1416,16 +1398,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1441,6 +1414,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2256,23 +2232,23 @@
       </c>
       <c r="B3" s="15">
         <f>'Staffing Plan'!B28</f>
-        <v>997040</v>
+        <v>1026431</v>
       </c>
       <c r="C3" s="15">
         <f>'Staffing Plan'!C28</f>
-        <v>1478601</v>
+        <v>1231718</v>
       </c>
       <c r="D3" s="15">
         <f>'Staffing Plan'!D28</f>
-        <v>1796022</v>
+        <v>1231718</v>
       </c>
       <c r="E3" s="15">
         <f>'Staffing Plan'!E28</f>
-        <v>2042905</v>
+        <v>1231718</v>
       </c>
       <c r="F3" s="15">
         <f>'Staffing Plan'!F28</f>
-        <v>2113443</v>
+        <v>1231718</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2326,23 +2302,23 @@
       </c>
       <c r="B6" s="28">
         <f>SUM(B3:B5)</f>
-        <v>1706865</v>
+        <v>1736256</v>
       </c>
       <c r="C6" s="28">
         <f>SUM(C3:C5)</f>
-        <v>2456286</v>
+        <v>2209403</v>
       </c>
       <c r="D6" s="28">
         <f>SUM(D3:D5)</f>
-        <v>3076368</v>
+        <v>2512064</v>
       </c>
       <c r="E6" s="28">
         <f>SUM(E3:E5)</f>
-        <v>3556819</v>
+        <v>2745632</v>
       </c>
       <c r="F6" s="28">
         <f>SUM(F3:F5)</f>
-        <v>3738192</v>
+        <v>2856467</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2351,23 +2327,23 @@
       </c>
       <c r="B7" s="29">
         <f>B2-B6</f>
-        <v>-418532</v>
+        <v>-447923</v>
       </c>
       <c r="C7" s="30">
         <f>C2-C6</f>
-        <v>66515</v>
+        <v>313398</v>
       </c>
       <c r="D7" s="30">
         <f>D2-D6</f>
-        <v>708232</v>
+        <v>1272536</v>
       </c>
       <c r="E7" s="30">
         <f>E2-E6</f>
-        <v>1202307</v>
+        <v>2013494</v>
       </c>
       <c r="F7" s="30">
         <f>F2-F6</f>
-        <v>1446209</v>
+        <v>2327934</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2376,23 +2352,23 @@
       </c>
       <c r="B8" s="14">
         <f>IF(B2=0,0,B7/B2)</f>
-        <v>-0.32</v>
+        <v>-0.35</v>
       </c>
       <c r="C8" s="14">
         <f>IF(C2=0,0,C7/C2)</f>
-        <v>0.03</v>
+        <v>0.12</v>
       </c>
       <c r="D8" s="14">
         <f>IF(D2=0,0,D7/D2)</f>
-        <v>0.19</v>
+        <v>0.34</v>
       </c>
       <c r="E8" s="14">
         <f>IF(E2=0,0,E7/E2)</f>
-        <v>0.25</v>
+        <v>0.42</v>
       </c>
       <c r="F8" s="14">
         <f>IF(F2=0,0,F7/F2)</f>
-        <v>0.28</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2401,23 +2377,23 @@
       </c>
       <c r="B9" s="27">
         <f>B7</f>
-        <v>-418532</v>
+        <v>-447923</v>
       </c>
       <c r="C9" s="27">
         <f>B9+C7</f>
-        <v>-352017</v>
+        <v>-134525</v>
       </c>
       <c r="D9" s="27">
         <f>C9+D7</f>
-        <v>356215</v>
+        <v>1138011</v>
       </c>
       <c r="E9" s="27">
         <f>D9+E7</f>
-        <v>1558522</v>
+        <v>3151505</v>
       </c>
       <c r="F9" s="27">
         <f>E9+F7</f>
-        <v>3004731</v>
+        <v>5479439</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2497,19 +2473,19 @@
         <v>185</v>
       </c>
       <c r="B3" s="15">
-        <v>81468</v>
+        <v>52077</v>
       </c>
       <c r="C3" s="15">
-        <v>147983</v>
+        <v>365475</v>
       </c>
       <c r="D3" s="15">
-        <v>856215</v>
+        <v>1638011</v>
       </c>
       <c r="E3" s="15">
-        <v>2058522</v>
+        <v>3651505</v>
       </c>
       <c r="F3" s="15">
-        <v>3504731</v>
+        <v>5979439</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2538,23 +2514,23 @@
       </c>
       <c r="B5" s="16">
         <f>SUM(B3:B4)</f>
-        <v>81468</v>
+        <v>52077</v>
       </c>
       <c r="C5" s="16">
         <f>SUM(C3:C4)</f>
-        <v>147983</v>
+        <v>365475</v>
       </c>
       <c r="D5" s="16">
         <f>SUM(D3:D4)</f>
-        <v>856215</v>
+        <v>1638011</v>
       </c>
       <c r="E5" s="16">
         <f>SUM(E3:E4)</f>
-        <v>2058522</v>
+        <v>3651505</v>
       </c>
       <c r="F5" s="16">
         <f>SUM(F3:F4)</f>
-        <v>3504731</v>
+        <v>5979439</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2650,16 +2626,16 @@
         <v>0</v>
       </c>
       <c r="C13" s="15">
-        <v>-397457</v>
+        <v>-426848</v>
       </c>
       <c r="D13" s="15">
-        <v>-308656</v>
+        <v>-91164</v>
       </c>
       <c r="E13" s="15">
-        <v>423144</v>
+        <v>1204940</v>
       </c>
       <c r="F13" s="15">
-        <v>1650374</v>
+        <v>3243357</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2667,19 +2643,19 @@
         <v>194</v>
       </c>
       <c r="B14" s="15">
-        <v>-397457</v>
+        <v>-426848</v>
       </c>
       <c r="C14" s="15">
-        <v>88801</v>
+        <v>335684</v>
       </c>
       <c r="D14" s="15">
-        <v>731800</v>
+        <v>1296104</v>
       </c>
       <c r="E14" s="15">
-        <v>1227230</v>
+        <v>2038417</v>
       </c>
       <c r="F14" s="15">
-        <v>1472565</v>
+        <v>2354290</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2688,23 +2664,23 @@
       </c>
       <c r="B15" s="16">
         <f>B5-B10</f>
-        <v>-397457</v>
+        <v>-426848</v>
       </c>
       <c r="C15" s="16">
         <f>C5-C10</f>
-        <v>-308656</v>
+        <v>-91164</v>
       </c>
       <c r="D15" s="16">
         <f>D5-D10</f>
-        <v>423144</v>
+        <v>1204940</v>
       </c>
       <c r="E15" s="16">
         <f>E5-E10</f>
-        <v>1650374</v>
+        <v>3243357</v>
       </c>
       <c r="F15" s="16">
         <f>F5-F10</f>
-        <v>3122939</v>
+        <v>5597647</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -2789,19 +2765,19 @@
         <v>198</v>
       </c>
       <c r="B3" s="15">
-        <v>-253707</v>
+        <v>-283098</v>
       </c>
       <c r="C3" s="15">
-        <v>156339</v>
+        <v>403222</v>
       </c>
       <c r="D3" s="15">
-        <v>798057</v>
+        <v>1362361</v>
       </c>
       <c r="E3" s="15">
-        <v>1277131</v>
+        <v>2088318</v>
       </c>
       <c r="F3" s="15">
-        <v>1516033</v>
+        <v>2397758</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2830,23 +2806,23 @@
       </c>
       <c r="B5" s="33">
         <f>IF(B4=0,"N/A",B3/B4)</f>
-        <v>-5.09</v>
+        <v>-5.68</v>
       </c>
       <c r="C5" s="33">
         <f>IF(C4=0,"N/A",C3/C4)</f>
-        <v>3.14</v>
+        <v>8.09</v>
       </c>
       <c r="D5" s="33">
         <f>IF(D4=0,"N/A",D3/D4)</f>
-        <v>16.02</v>
+        <v>27.34</v>
       </c>
       <c r="E5" s="33">
         <f>IF(E4=0,"N/A",E3/E4)</f>
-        <v>25.63</v>
+        <v>41.91</v>
       </c>
       <c r="F5" s="33">
         <f>IF(F4=0,"N/A",F3/F4)</f>
-        <v>30.43</v>
+        <v>48.12</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2864,19 +2840,19 @@
         <v>201</v>
       </c>
       <c r="B8" s="15">
-        <v>81468</v>
+        <v>52077</v>
       </c>
       <c r="C8" s="15">
-        <v>147983</v>
+        <v>365475</v>
       </c>
       <c r="D8" s="15">
-        <v>856215</v>
+        <v>1638011</v>
       </c>
       <c r="E8" s="15">
-        <v>2058522</v>
+        <v>3651505</v>
       </c>
       <c r="F8" s="15">
-        <v>3504731</v>
+        <v>5979439</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2884,19 +2860,19 @@
         <v>202</v>
       </c>
       <c r="B9" s="15">
-        <v>128503</v>
+        <v>130953</v>
       </c>
       <c r="C9" s="15">
-        <v>197205</v>
+        <v>176632</v>
       </c>
       <c r="D9" s="15">
-        <v>248879</v>
+        <v>201853</v>
       </c>
       <c r="E9" s="15">
-        <v>290166</v>
+        <v>222567</v>
       </c>
       <c r="F9" s="15">
-        <v>305697</v>
+        <v>232220</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2905,23 +2881,23 @@
       </c>
       <c r="B10" s="34">
         <f>IF(B9=0,0,B8/B9)</f>
-        <v>0.63</v>
+        <v>0.4</v>
       </c>
       <c r="C10" s="34">
         <f>IF(C9=0,0,C8/C9)</f>
-        <v>0.75</v>
+        <v>2.07</v>
       </c>
       <c r="D10" s="34">
         <f>IF(D9=0,0,D8/D9)</f>
-        <v>3.44</v>
+        <v>8.11</v>
       </c>
       <c r="E10" s="34">
         <f>IF(E9=0,0,E8/E9)</f>
-        <v>7.09</v>
+        <v>16.41</v>
       </c>
       <c r="F10" s="34">
         <f>IF(F9=0,0,F8/F9)</f>
-        <v>11.46</v>
+        <v>25.75</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2929,19 +2905,19 @@
         <v>204</v>
       </c>
       <c r="B11" s="35">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C11" s="35">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="D11" s="35">
-        <v>105</v>
+        <v>247</v>
       </c>
       <c r="E11" s="35">
-        <v>216</v>
+        <v>499</v>
       </c>
       <c r="F11" s="35">
-        <v>349</v>
+        <v>783</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2987,9 +2963,9 @@
         <f>IF(B10&gt;=2,"PASS","FAIL")</f>
         <v>FAIL</v>
       </c>
-      <c r="C15" s="36" t="str">
+      <c r="C15" s="37" t="str">
         <f>IF(C10&gt;=2,"PASS","FAIL")</f>
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="D15" s="37" t="str">
         <f>IF(D10&gt;=2,"PASS","FAIL")</f>
@@ -3197,7 +3173,7 @@
         <v>233</v>
       </c>
       <c r="B18" s="18">
-        <v>1706865</v>
+        <v>1736256</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -3205,7 +3181,7 @@
         <v>234</v>
       </c>
       <c r="B19" s="18">
-        <v>-418532</v>
+        <v>-447923</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -3213,7 +3189,7 @@
         <v>235</v>
       </c>
       <c r="B20" s="41">
-        <v>-0.32486321471234536</v>
+        <v>-0.34767641595767557</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -3229,7 +3205,7 @@
         <v>236</v>
       </c>
       <c r="B22" s="18">
-        <v>81468</v>
+        <v>52077</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -3277,7 +3253,7 @@
         <v>243</v>
       </c>
       <c r="B28" s="18">
-        <v>14224</v>
+        <v>14469</v>
       </c>
     </row>
   </sheetData>
@@ -3422,23 +3398,23 @@
       </c>
       <c r="B9" s="15">
         <f>'5-Year P&amp;L'!B6</f>
-        <v>1706865</v>
+        <v>1736256</v>
       </c>
       <c r="C9" s="15">
         <f>'5-Year P&amp;L'!C6</f>
-        <v>2456286</v>
+        <v>2209403</v>
       </c>
       <c r="D9" s="15">
         <f>'5-Year P&amp;L'!D6</f>
-        <v>3076368</v>
+        <v>2512064</v>
       </c>
       <c r="E9" s="15">
         <f>'5-Year P&amp;L'!E6</f>
-        <v>3556819</v>
+        <v>2745632</v>
       </c>
       <c r="F9" s="15">
         <f>'5-Year P&amp;L'!F6</f>
-        <v>3738192</v>
+        <v>2856467</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3447,23 +3423,23 @@
       </c>
       <c r="B10" s="23">
         <f>'5-Year P&amp;L'!B7</f>
-        <v>-418532</v>
+        <v>-447923</v>
       </c>
       <c r="C10" s="23">
         <f>'5-Year P&amp;L'!C7</f>
-        <v>66515</v>
+        <v>313398</v>
       </c>
       <c r="D10" s="23">
         <f>'5-Year P&amp;L'!D7</f>
-        <v>708232</v>
+        <v>1272536</v>
       </c>
       <c r="E10" s="23">
         <f>'5-Year P&amp;L'!E7</f>
-        <v>1202307</v>
+        <v>2013494</v>
       </c>
       <c r="F10" s="23">
         <f>'5-Year P&amp;L'!F7</f>
-        <v>1446209</v>
+        <v>2327934</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -3472,23 +3448,23 @@
       </c>
       <c r="B11" s="14">
         <f>IF(B8=0,0,B10/B8)</f>
-        <v>-0.32</v>
+        <v>-0.35</v>
       </c>
       <c r="C11" s="14">
         <f>IF(C8=0,0,C10/C8)</f>
-        <v>0.03</v>
+        <v>0.12</v>
       </c>
       <c r="D11" s="14">
         <f>IF(D8=0,0,D10/D8)</f>
-        <v>0.19</v>
+        <v>0.34</v>
       </c>
       <c r="E11" s="14">
         <f>IF(E8=0,0,E10/E8)</f>
-        <v>0.25</v>
+        <v>0.42</v>
       </c>
       <c r="F11" s="14">
         <f>IF(F8=0,0,F10/F8)</f>
-        <v>0.28</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -3497,23 +3473,23 @@
       </c>
       <c r="B12" s="27">
         <f>B10</f>
-        <v>-418532</v>
+        <v>-447923</v>
       </c>
       <c r="C12" s="27">
         <f>B12+C10</f>
-        <v>-352017</v>
+        <v>-134525</v>
       </c>
       <c r="D12" s="27">
         <f>C12+D10</f>
-        <v>356215</v>
+        <v>1138011</v>
       </c>
       <c r="E12" s="27">
         <f>D12+E10</f>
-        <v>1558522</v>
+        <v>3151505</v>
       </c>
       <c r="F12" s="27">
         <f>E12+F10</f>
-        <v>3004731</v>
+        <v>5479439</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -3521,19 +3497,19 @@
         <v>247</v>
       </c>
       <c r="B13" s="27">
-        <v>81468</v>
+        <v>52077</v>
       </c>
       <c r="C13" s="27">
-        <v>147983</v>
+        <v>365475</v>
       </c>
       <c r="D13" s="27">
-        <v>856215</v>
+        <v>1638011</v>
       </c>
       <c r="E13" s="27">
-        <v>2058522</v>
+        <v>3651505</v>
       </c>
       <c r="F13" s="27">
-        <v>3504731</v>
+        <v>5979439</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -3561,19 +3537,19 @@
         <v>122</v>
       </c>
       <c r="B15" s="15">
-        <v>14224</v>
+        <v>14469</v>
       </c>
       <c r="C15" s="15">
-        <v>12281</v>
+        <v>11047</v>
       </c>
       <c r="D15" s="15">
-        <v>10255</v>
+        <v>8374</v>
       </c>
       <c r="E15" s="15">
-        <v>9485</v>
+        <v>7322</v>
       </c>
       <c r="F15" s="15">
-        <v>9345</v>
+        <v>7141</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -3581,19 +3557,19 @@
         <v>199</v>
       </c>
       <c r="B16" s="33">
-        <v>-5.09</v>
+        <v>-5.68</v>
       </c>
       <c r="C16" s="33">
-        <v>3.14</v>
+        <v>8.09</v>
       </c>
       <c r="D16" s="33">
-        <v>16.02</v>
+        <v>27.34</v>
       </c>
       <c r="E16" s="33">
-        <v>25.63</v>
+        <v>41.91</v>
       </c>
       <c r="F16" s="33">
-        <v>30.43</v>
+        <v>48.12</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -3700,7 +3676,7 @@
         <v>258</v>
       </c>
       <c r="C17" s="27">
-        <v>1446209</v>
+        <v>2327934</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
@@ -3708,7 +3684,7 @@
         <v>201</v>
       </c>
       <c r="C18" s="27">
-        <v>3004731</v>
+        <v>5479439</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
@@ -3851,7 +3827,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H40"/>
+  <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -3962,19 +3938,19 @@
         <v>167</v>
       </c>
       <c r="C9" s="61">
-        <v>997040</v>
+        <v>1026431</v>
       </c>
       <c r="D9" s="61">
-        <v>1478601</v>
+        <v>1231718</v>
       </c>
       <c r="E9" s="61">
-        <v>1796022</v>
+        <v>1231718</v>
       </c>
       <c r="F9" s="61">
-        <v>2042905</v>
+        <v>1231718</v>
       </c>
       <c r="G9" s="61">
-        <v>2113443</v>
+        <v>1231718</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -4022,19 +3998,19 @@
         <v>179</v>
       </c>
       <c r="C12" s="63">
-        <v>-418532</v>
+        <v>-447923</v>
       </c>
       <c r="D12" s="64">
-        <v>66515</v>
+        <v>313398</v>
       </c>
       <c r="E12" s="64">
-        <v>708232</v>
+        <v>1272536</v>
       </c>
       <c r="F12" s="64">
-        <v>1202307</v>
+        <v>2013494</v>
       </c>
       <c r="G12" s="64">
-        <v>1446209</v>
+        <v>2327934</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
@@ -4042,19 +4018,19 @@
         <v>282</v>
       </c>
       <c r="C13" s="64">
-        <v>81468</v>
+        <v>52077</v>
       </c>
       <c r="D13" s="64">
-        <v>147983</v>
+        <v>365475</v>
       </c>
       <c r="E13" s="64">
-        <v>856215</v>
+        <v>1638011</v>
       </c>
       <c r="F13" s="64">
-        <v>2058522</v>
+        <v>3651505</v>
       </c>
       <c r="G13" s="64">
-        <v>3504731</v>
+        <v>5979439</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
@@ -4062,496 +4038,390 @@
         <v>283</v>
       </c>
       <c r="C14" s="65">
-        <v>-0.32486321471234536</v>
+        <v>-0.34767641595767557</v>
       </c>
       <c r="D14" s="66">
-        <v>0.026365546218487395</v>
-      </c>
-      <c r="E14" s="67">
-        <v>0.1871352322570417</v>
-      </c>
-      <c r="F14" s="67">
-        <v>0.25263194389725</v>
-      </c>
-      <c r="G14" s="67">
-        <v>0.27895397731656507</v>
+        <v>0.12422625654035199</v>
+      </c>
+      <c r="E14" s="66">
+        <v>0.3362405538233895</v>
+      </c>
+      <c r="F14" s="66">
+        <v>0.42308071336642766</v>
+      </c>
+      <c r="G14" s="66">
+        <v>0.44902669547102847</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="62" t="s">
         <v>248</v>
       </c>
-      <c r="C15" s="68">
+      <c r="C15" s="67">
         <v>10736.108333333334</v>
       </c>
-      <c r="D15" s="68">
+      <c r="D15" s="67">
         <v>12614</v>
       </c>
-      <c r="E15" s="68">
+      <c r="E15" s="67">
         <v>12615.333333333334</v>
       </c>
-      <c r="F15" s="68">
+      <c r="F15" s="67">
         <v>12691</v>
       </c>
-      <c r="G15" s="68">
+      <c r="G15" s="67">
         <v>12961</v>
       </c>
-      <c r="H15" s="69" t="s">
+      <c r="H15" s="68" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="62" t="s">
-        <v>122</v>
-      </c>
-      <c r="C16" s="70">
-        <v>13265.541666666666</v>
-      </c>
-      <c r="D16" s="70">
-        <v>12081.43</v>
-      </c>
-      <c r="E16" s="70">
-        <v>10121.226666666667</v>
-      </c>
-      <c r="F16" s="70">
-        <v>9418.184</v>
-      </c>
-      <c r="G16" s="70">
-        <v>9295.48</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="13" t="s">
         <v>285</v>
       </c>
-      <c r="C17" s="61">
-        <v>0</v>
-      </c>
-      <c r="D17" s="61">
-        <v>0</v>
-      </c>
-      <c r="E17" s="61">
-        <v>0</v>
-      </c>
-      <c r="F17" s="61">
-        <v>0</v>
-      </c>
-      <c r="G17" s="61">
-        <v>0</v>
+      <c r="C16" s="65">
+        <v>0.7967124959152642</v>
+      </c>
+      <c r="D16" s="66">
+        <v>0.4882345013477089</v>
+      </c>
+      <c r="E16" s="66">
+        <v>0.3254552660783174</v>
+      </c>
+      <c r="F16" s="66">
+        <v>0.25881186142410634</v>
+      </c>
+      <c r="G16" s="66">
+        <v>0.23758159092662604</v>
+      </c>
+      <c r="H16" s="68" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="62" t="s">
+        <v>287</v>
+      </c>
+      <c r="C17" s="69">
+        <v>0.21888750812095942</v>
+      </c>
+      <c r="D17" s="66">
+        <v>0.1151339781195497</v>
+      </c>
+      <c r="E17" s="66">
+        <v>0.07904835385509698</v>
+      </c>
+      <c r="F17" s="66">
+        <v>0.06474930412628371</v>
+      </c>
+      <c r="G17" s="66">
+        <v>0.06122075900007716</v>
+      </c>
+      <c r="H17" s="68" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="13" t="s">
-        <v>286</v>
-      </c>
-      <c r="C18" s="71">
-        <v>2350</v>
-      </c>
-      <c r="D18" s="68">
-        <v>1452.3</v>
-      </c>
-      <c r="E18" s="68">
-        <v>997.2213333333334</v>
-      </c>
-      <c r="F18" s="68">
-        <v>821.7334186666667</v>
-      </c>
-      <c r="G18" s="68">
-        <v>793.4822574000001</v>
-      </c>
-      <c r="H18" s="69" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="62" t="s">
+        <v>289</v>
+      </c>
+      <c r="C18" s="65">
+        <v>-0.219739772248324</v>
+      </c>
+      <c r="D18" s="66">
+        <v>0.15983114000317108</v>
+      </c>
+      <c r="E18" s="66">
+        <v>0.3599748982719442</v>
+      </c>
+      <c r="F18" s="66">
+        <v>0.4388029312110945</v>
+      </c>
+      <c r="G18" s="66">
+        <v>0.46249479206851324</v>
+      </c>
+      <c r="H18" s="68" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="62" t="s">
-        <v>288</v>
-      </c>
-      <c r="C19" s="72">
-        <v>-3487.766666666667</v>
-      </c>
-      <c r="D19" s="73">
-        <v>332.575</v>
-      </c>
-      <c r="E19" s="73">
-        <v>2360.7733333333335</v>
-      </c>
-      <c r="F19" s="73">
-        <v>3206.152</v>
-      </c>
-      <c r="G19" s="73">
-        <v>3615.5225</v>
+        <v>291</v>
+      </c>
+      <c r="C19" s="70">
+        <v>3</v>
+      </c>
+      <c r="D19" s="70">
+        <v>3</v>
+      </c>
+      <c r="E19" s="70">
+        <v>3</v>
+      </c>
+      <c r="F19" s="70">
+        <v>3</v>
+      </c>
+      <c r="G19" s="70">
+        <v>3</v>
+      </c>
+      <c r="H19" s="68" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="62" t="s">
-        <v>289</v>
-      </c>
-      <c r="C20" s="65">
-        <v>0.7738992946699339</v>
-      </c>
-      <c r="D20" s="66">
-        <v>0.5860952116695735</v>
-      </c>
-      <c r="E20" s="67">
-        <v>0.47456058764466524</v>
-      </c>
-      <c r="F20" s="67">
-        <v>0.429260630893284</v>
-      </c>
-      <c r="G20" s="67">
-        <v>0.4076543090810894</v>
-      </c>
-      <c r="H20" s="69" t="s">
-        <v>290</v>
+        <v>199</v>
+      </c>
+      <c r="C20" s="71">
+        <v>-5.681846462619167</v>
+      </c>
+      <c r="D20" s="72">
+        <v>8.092764676367285</v>
+      </c>
+      <c r="E20" s="72">
+        <v>27.342920220772704</v>
+      </c>
+      <c r="F20" s="72">
+        <v>41.91305569493226</v>
+      </c>
+      <c r="G20" s="72">
+        <v>48.12359257400903</v>
+      </c>
+      <c r="H20" s="68" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="62" t="s">
-        <v>291</v>
-      </c>
-      <c r="C21" s="66">
-        <v>0.21888750812095942</v>
-      </c>
-      <c r="D21" s="67">
-        <v>0.1151339781195497</v>
-      </c>
-      <c r="E21" s="67">
-        <v>0.07904835385509698</v>
-      </c>
-      <c r="F21" s="67">
-        <v>0.06474930412628371</v>
-      </c>
-      <c r="G21" s="67">
-        <v>0.06122075900007716</v>
-      </c>
-      <c r="H21" s="69" t="s">
-        <v>292</v>
+        <v>294</v>
+      </c>
+      <c r="C21" s="73" t="str">
+        <f>IF('5-Year P&amp;L'!B9&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="73" t="str">
+        <f>IF(AND('5-Year P&amp;L'!C9&gt;=0,'5-Year P&amp;L'!B9&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="32" t="str">
+        <f>IF(AND('5-Year P&amp;L'!D9&gt;=0,'5-Year P&amp;L'!C9&lt;0),"✓ Break-even","")</f>
+        <v>✓ Break-even</v>
+      </c>
+      <c r="F21" s="73" t="str">
+        <f>IF(AND('5-Year P&amp;L'!E9&gt;=0,'5-Year P&amp;L'!D9&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="73" t="str">
+        <f>IF(AND('5-Year P&amp;L'!F9&gt;=0,'5-Year P&amp;L'!E9&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="68" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="62" t="s">
-        <v>293</v>
-      </c>
-      <c r="C22" s="65">
-        <v>-0.1969265710029938</v>
-      </c>
-      <c r="D22" s="66">
-        <v>0.061970429681306484</v>
-      </c>
-      <c r="E22" s="67">
-        <v>0.21086957670559636</v>
-      </c>
-      <c r="F22" s="67">
-        <v>0.26835416174191684</v>
-      </c>
-      <c r="G22" s="67">
-        <v>0.29242207391404984</v>
-      </c>
-      <c r="H22" s="69" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="62" t="s">
         <v>295</v>
       </c>
-      <c r="C23" s="74">
-        <v>3</v>
-      </c>
-      <c r="D23" s="74">
-        <v>3</v>
-      </c>
-      <c r="E23" s="74">
-        <v>3</v>
-      </c>
-      <c r="F23" s="74">
-        <v>3</v>
-      </c>
-      <c r="G23" s="74">
-        <v>3</v>
-      </c>
-      <c r="H23" s="69" t="s">
+      <c r="C22" s="74">
+        <v>0</v>
+      </c>
+      <c r="D22" s="74">
+        <v>2</v>
+      </c>
+      <c r="E22" s="74">
+        <v>8</v>
+      </c>
+      <c r="F22" s="75">
+        <v>16</v>
+      </c>
+      <c r="G22" s="70">
+        <v>25</v>
+      </c>
+      <c r="H22" s="68" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="62" t="s">
-        <v>199</v>
-      </c>
-      <c r="C24" s="75">
-        <v>-5.091961866532865</v>
-      </c>
-      <c r="D24" s="76">
-        <v>3.137762167586553</v>
-      </c>
-      <c r="E24" s="76">
-        <v>16.017200200702458</v>
-      </c>
-      <c r="F24" s="76">
-        <v>25.632333166081285</v>
-      </c>
-      <c r="G24" s="76">
-        <v>30.42715504264927</v>
-      </c>
-      <c r="H24" s="69" t="s">
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="5" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="62" t="s">
+      <c r="C24" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="C25" s="77" t="str">
-        <f>IF('5-Year P&amp;L'!B9&gt;=0,"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="77" t="str">
-        <f>IF(AND('5-Year P&amp;L'!C9&gt;=0,'5-Year P&amp;L'!B9&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="32" t="str">
-        <f>IF(AND('5-Year P&amp;L'!D9&gt;=0,'5-Year P&amp;L'!C9&lt;0),"✓ Break-even","")</f>
-        <v>✓ Break-even</v>
-      </c>
-      <c r="F25" s="77" t="str">
-        <f>IF(AND('5-Year P&amp;L'!E9&gt;=0,'5-Year P&amp;L'!D9&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="77" t="str">
-        <f>IF(AND('5-Year P&amp;L'!F9&gt;=0,'5-Year P&amp;L'!E9&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="69" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="62" t="s">
+      <c r="D24" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="C26" s="78">
-        <v>1</v>
-      </c>
-      <c r="D26" s="78">
-        <v>1</v>
-      </c>
-      <c r="E26" s="78">
-        <v>3</v>
-      </c>
-      <c r="F26" s="78">
-        <v>7</v>
-      </c>
-      <c r="G26" s="78">
-        <v>11</v>
-      </c>
-      <c r="H26" s="69" t="s">
+      <c r="E24" s="5"/>
+      <c r="F24" s="5" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="62" t="s">
-        <v>204</v>
-      </c>
-      <c r="C27" s="78">
-        <v>19</v>
-      </c>
-      <c r="D27" s="78">
-        <v>22</v>
-      </c>
-      <c r="E27" s="74">
-        <v>103</v>
-      </c>
-      <c r="F27" s="74">
-        <v>213</v>
-      </c>
-      <c r="G27" s="74">
-        <v>344</v>
-      </c>
-      <c r="H27" s="69" t="s">
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="76" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="5" t="s">
+      <c r="C25" s="77" t="s">
         <v>302</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="D25" s="78" t="s">
         <v>303</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="E25" s="78"/>
+      <c r="F25" s="79" t="s">
         <v>304</v>
       </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5" t="s">
+      <c r="G25" s="79"/>
+      <c r="H25" s="79"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="76" t="s">
         <v>305</v>
       </c>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
+      <c r="C26" s="32" t="s">
+        <v>306</v>
+      </c>
+      <c r="D26" s="78" t="s">
+        <v>307</v>
+      </c>
+      <c r="E26" s="78"/>
+      <c r="F26" s="79" t="s">
+        <v>308</v>
+      </c>
+      <c r="G26" s="79"/>
+      <c r="H26" s="79"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="76" t="s">
+        <v>309</v>
+      </c>
+      <c r="C27" s="32" t="s">
+        <v>306</v>
+      </c>
+      <c r="D27" s="78" t="s">
+        <v>310</v>
+      </c>
+      <c r="E27" s="78"/>
+      <c r="F27" s="79" t="s">
+        <v>311</v>
+      </c>
+      <c r="G27" s="79"/>
+      <c r="H27" s="79"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="76" t="s">
+        <v>312</v>
+      </c>
+      <c r="C28" s="32" t="s">
+        <v>306</v>
+      </c>
+      <c r="D28" s="78" t="s">
+        <v>313</v>
+      </c>
+      <c r="E28" s="78"/>
+      <c r="F28" s="79" t="s">
+        <v>314</v>
+      </c>
+      <c r="G28" s="79"/>
+      <c r="H28" s="79"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="76" t="s">
+        <v>315</v>
+      </c>
+      <c r="C29" s="32" t="s">
+        <v>306</v>
+      </c>
+      <c r="D29" s="78" t="s">
+        <v>316</v>
+      </c>
+      <c r="E29" s="78"/>
+      <c r="F29" s="79" t="s">
+        <v>317</v>
+      </c>
+      <c r="G29" s="79"/>
+      <c r="H29" s="79"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="79" t="s">
+      <c r="B30" s="76" t="s">
+        <v>318</v>
+      </c>
+      <c r="C30" s="32" t="s">
         <v>306</v>
       </c>
-      <c r="C30" s="80" t="s">
-        <v>307</v>
-      </c>
-      <c r="D30" s="81" t="s">
-        <v>308</v>
-      </c>
-      <c r="E30" s="81"/>
-      <c r="F30" s="82" t="s">
-        <v>309</v>
-      </c>
-      <c r="G30" s="82"/>
-      <c r="H30" s="82"/>
+      <c r="D30" s="78" t="s">
+        <v>319</v>
+      </c>
+      <c r="E30" s="78"/>
+      <c r="F30" s="79" t="s">
+        <v>320</v>
+      </c>
+      <c r="G30" s="79"/>
+      <c r="H30" s="79"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="79" t="s">
-        <v>310</v>
+      <c r="B31" s="76" t="s">
+        <v>321</v>
       </c>
       <c r="C31" s="32" t="s">
-        <v>311</v>
-      </c>
-      <c r="D31" s="81" t="s">
-        <v>312</v>
-      </c>
-      <c r="E31" s="81"/>
-      <c r="F31" s="82" t="s">
-        <v>313</v>
-      </c>
-      <c r="G31" s="82"/>
-      <c r="H31" s="82"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="79" t="s">
-        <v>314</v>
-      </c>
-      <c r="C32" s="32" t="s">
-        <v>311</v>
-      </c>
-      <c r="D32" s="81" t="s">
-        <v>315</v>
-      </c>
-      <c r="E32" s="81"/>
-      <c r="F32" s="82" t="s">
-        <v>316</v>
-      </c>
-      <c r="G32" s="82"/>
-      <c r="H32" s="82"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="79" t="s">
-        <v>317</v>
-      </c>
-      <c r="C33" s="32" t="s">
-        <v>311</v>
-      </c>
-      <c r="D33" s="81" t="s">
-        <v>318</v>
-      </c>
-      <c r="E33" s="81"/>
-      <c r="F33" s="82" t="s">
-        <v>319</v>
-      </c>
-      <c r="G33" s="82"/>
-      <c r="H33" s="82"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="79" t="s">
-        <v>320</v>
-      </c>
-      <c r="C34" s="32" t="s">
-        <v>311</v>
-      </c>
-      <c r="D34" s="81" t="s">
-        <v>321</v>
-      </c>
-      <c r="E34" s="81"/>
-      <c r="F34" s="82" t="s">
+        <v>306</v>
+      </c>
+      <c r="D31" s="78" t="s">
         <v>322</v>
       </c>
-      <c r="G34" s="82"/>
-      <c r="H34" s="82"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="79" t="s">
+      <c r="E31" s="78"/>
+      <c r="F31" s="79" t="s">
         <v>323</v>
       </c>
-      <c r="C35" s="32" t="s">
-        <v>311</v>
-      </c>
-      <c r="D35" s="81" t="s">
+      <c r="G31" s="79"/>
+      <c r="H31" s="79"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="76" t="s">
+        <v>273</v>
+      </c>
+      <c r="C33" s="62" t="s">
         <v>324</v>
       </c>
-      <c r="E35" s="81"/>
-      <c r="F35" s="82" t="s">
+      <c r="D33" s="62"/>
+      <c r="E33" s="62"/>
+      <c r="F33" s="62"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="80" t="s">
         <v>325</v>
       </c>
-      <c r="G35" s="82"/>
-      <c r="H35" s="82"/>
-    </row>
-    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="79" t="s">
-        <v>326</v>
-      </c>
-      <c r="C36" s="32" t="s">
-        <v>311</v>
-      </c>
-      <c r="D36" s="81" t="s">
-        <v>327</v>
-      </c>
-      <c r="E36" s="81"/>
-      <c r="F36" s="82" t="s">
-        <v>328</v>
-      </c>
-      <c r="G36" s="82"/>
-      <c r="H36" s="82"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="79" t="s">
-        <v>273</v>
-      </c>
-      <c r="C38" s="62" t="s">
-        <v>329</v>
-      </c>
-      <c r="D38" s="62"/>
-      <c r="E38" s="62"/>
-      <c r="F38" s="62"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="83" t="s">
-        <v>330</v>
-      </c>
-      <c r="C40" s="83"/>
-      <c r="D40" s="83"/>
-      <c r="E40" s="83"/>
-      <c r="F40" s="83"/>
-      <c r="G40" s="83"/>
-      <c r="H40" s="83"/>
+      <c r="C35" s="80"/>
+      <c r="D35" s="80"/>
+      <c r="E35" s="80"/>
+      <c r="F35" s="80"/>
+      <c r="G35" s="80"/>
+      <c r="H35" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -4597,48 +4467,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C20&lt;=0.55</formula>
+      <formula>C16&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C20&lt;=0.65</formula>
+      <formula>C16&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C20&gt;0.65</formula>
+      <formula>C16&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C21:G21">
+  <conditionalFormatting sqref="C17:G17">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C21&lt;=0.15</formula>
+      <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C21&lt;=0.22</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C21&gt;0.22</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22:G22">
+  <conditionalFormatting sqref="C18:G18">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C22&gt;=0.10</formula>
+      <formula>C18&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C22&gt;=0</formula>
+      <formula>C18&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C22&lt;0</formula>
+      <formula>C18&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C24:G24">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C24&gt;=1.25</formula>
+      <formula>C20&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1</formula>
+      <formula>C20&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1</formula>
+      <formula>C20&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6368,7 +6238,7 @@
         <v>135</v>
       </c>
       <c r="B14" s="22">
-        <v>257007</v>
+        <v>261905</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -6376,7 +6246,7 @@
         <v>136</v>
       </c>
       <c r="B15" s="22">
-        <v>26650</v>
+        <v>26895</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -6385,7 +6255,7 @@
       </c>
       <c r="B16" s="23">
         <f>SUM(B9:B15)</f>
-        <v>559657</v>
+        <v>564800</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -6394,7 +6264,7 @@
       </c>
       <c r="B18" s="24">
         <f>B6-B16</f>
-        <v>-59657</v>
+        <v>-64800</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
@@ -6692,34 +6562,34 @@
         <v>167</v>
       </c>
       <c r="B3" s="15">
-        <v>99704</v>
+        <v>102643</v>
       </c>
       <c r="C3" s="15">
-        <v>99704</v>
+        <v>102643</v>
       </c>
       <c r="D3" s="15">
-        <v>99704</v>
+        <v>102643</v>
       </c>
       <c r="E3" s="15">
-        <v>99704</v>
+        <v>102643</v>
       </c>
       <c r="F3" s="15">
-        <v>99704</v>
+        <v>102643</v>
       </c>
       <c r="G3" s="15">
-        <v>99704</v>
+        <v>102643</v>
       </c>
       <c r="H3" s="15">
-        <v>99704</v>
+        <v>102643</v>
       </c>
       <c r="I3" s="15">
-        <v>99704</v>
+        <v>102643</v>
       </c>
       <c r="J3" s="15">
-        <v>99704</v>
+        <v>102643</v>
       </c>
       <c r="K3" s="15">
-        <v>99704</v>
+        <v>102644</v>
       </c>
       <c r="L3" s="15">
         <v>0</v>
@@ -6729,7 +6599,7 @@
       </c>
       <c r="N3" s="15">
         <f>SUM(B3:M3)</f>
-        <v>997040</v>
+        <v>1026431</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -6828,43 +6698,43 @@
       </c>
       <c r="B6" s="23">
         <f>SUM(B3:B5)</f>
-        <v>167939</v>
+        <v>170878</v>
       </c>
       <c r="C6" s="23">
         <f>SUM(C3:C5)</f>
-        <v>167939</v>
+        <v>170878</v>
       </c>
       <c r="D6" s="23">
         <f>SUM(D3:D5)</f>
-        <v>167939</v>
+        <v>170878</v>
       </c>
       <c r="E6" s="23">
         <f>SUM(E3:E5)</f>
-        <v>167939</v>
+        <v>170878</v>
       </c>
       <c r="F6" s="23">
         <f>SUM(F3:F5)</f>
-        <v>167939</v>
+        <v>170878</v>
       </c>
       <c r="G6" s="23">
         <f>SUM(G3:G5)</f>
-        <v>167939</v>
+        <v>170878</v>
       </c>
       <c r="H6" s="23">
         <f>SUM(H3:H5)</f>
-        <v>167939</v>
+        <v>170878</v>
       </c>
       <c r="I6" s="23">
         <f>SUM(I3:I5)</f>
-        <v>167939</v>
+        <v>170878</v>
       </c>
       <c r="J6" s="23">
         <f>SUM(J3:J5)</f>
-        <v>167939</v>
+        <v>170878</v>
       </c>
       <c r="K6" s="23">
         <f>SUM(K3:K5)</f>
-        <v>167939</v>
+        <v>170879</v>
       </c>
       <c r="L6" s="23">
         <f>SUM(L3:L5)</f>
@@ -6876,7 +6746,7 @@
       </c>
       <c r="N6" s="23">
         <f>SUM(B6:M6)</f>
-        <v>1706865</v>
+        <v>1736256</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -6885,43 +6755,43 @@
       </c>
       <c r="B7" s="27">
         <f>B2-B6</f>
-        <v>-13339</v>
+        <v>-16278</v>
       </c>
       <c r="C7" s="27">
         <f>C2-C6</f>
-        <v>-13339</v>
+        <v>-16278</v>
       </c>
       <c r="D7" s="27">
         <f>D2-D6</f>
-        <v>-13339</v>
+        <v>-16278</v>
       </c>
       <c r="E7" s="27">
         <f>E2-E6</f>
-        <v>-13339</v>
+        <v>-16278</v>
       </c>
       <c r="F7" s="27">
         <f>F2-F6</f>
-        <v>-13339</v>
+        <v>-16278</v>
       </c>
       <c r="G7" s="27">
         <f>G2-G6</f>
-        <v>-13339</v>
+        <v>-16278</v>
       </c>
       <c r="H7" s="27">
         <f>H2-H6</f>
-        <v>-13339</v>
+        <v>-16278</v>
       </c>
       <c r="I7" s="27">
         <f>I2-I6</f>
-        <v>-13339</v>
+        <v>-16278</v>
       </c>
       <c r="J7" s="27">
         <f>J2-J6</f>
-        <v>-13339</v>
+        <v>-16278</v>
       </c>
       <c r="K7" s="27">
         <f>K2-K6</f>
-        <v>-271006</v>
+        <v>-273946</v>
       </c>
       <c r="L7" s="27">
         <f>L2-L6</f>
@@ -6933,7 +6803,7 @@
       </c>
       <c r="N7" s="27">
         <f>SUM(B7:M7)</f>
-        <v>-418532</v>
+        <v>-447923</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -6942,55 +6812,55 @@
       </c>
       <c r="B8" s="27">
         <f>500000+B7</f>
-        <v>486661</v>
+        <v>483722</v>
       </c>
       <c r="C8" s="27">
         <f>B8+C7</f>
-        <v>473322</v>
+        <v>467444</v>
       </c>
       <c r="D8" s="27">
         <f>C8+D7</f>
-        <v>459983</v>
+        <v>451166</v>
       </c>
       <c r="E8" s="27">
         <f>D8+E7</f>
-        <v>446644</v>
+        <v>434888</v>
       </c>
       <c r="F8" s="27">
         <f>E8+F7</f>
-        <v>433305</v>
+        <v>418610</v>
       </c>
       <c r="G8" s="27">
         <f>F8+G7</f>
-        <v>419966</v>
+        <v>402332</v>
       </c>
       <c r="H8" s="27">
         <f>G8+H7</f>
-        <v>406627</v>
+        <v>386054</v>
       </c>
       <c r="I8" s="27">
         <f>H8+I7</f>
-        <v>393288</v>
+        <v>369776</v>
       </c>
       <c r="J8" s="27">
         <f>I8+J7</f>
-        <v>379949</v>
+        <v>353498</v>
       </c>
       <c r="K8" s="27">
         <f>J8+K7</f>
-        <v>108943</v>
+        <v>79552</v>
       </c>
       <c r="L8" s="27">
         <f>K8+L7</f>
-        <v>95208</v>
+        <v>65817</v>
       </c>
       <c r="M8" s="27">
         <f>L8+M7</f>
-        <v>81468</v>
+        <v>52077</v>
       </c>
       <c r="N8" s="27">
         <f>M8</f>
-        <v>81468</v>
+        <v>52077</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -7025,7 +6895,7 @@
       </c>
       <c r="B12" s="18">
         <f>M8</f>
-        <v>81468</v>
+        <v>52077</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -7034,7 +6904,7 @@
       </c>
       <c r="B13" s="19">
         <f>MIN(B8:M8)</f>
-        <v>81468</v>
+        <v>52077</v>
       </c>
     </row>
   </sheetData>

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
@@ -50,7 +50,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'Underwriting Snapshot'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'Summary'!$A1:$F18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="13">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="15">'Financial Health'!$A1:$H35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'Financial Health'!$A1:$H40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="15">'Financial Health'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="331">
   <si>
     <t>SchoolStack - Assumptions &amp; Drivers</t>
   </si>
@@ -708,13 +708,13 @@
     <t>DSCR ≥ 1.20x (2026-27)</t>
   </si>
   <si>
-    <t>-5.68x</t>
+    <t>-5.09x</t>
   </si>
   <si>
     <t>Min 2 Months Cash Reserve (2026-27)</t>
   </si>
   <si>
-    <t>0.4 months</t>
+    <t>0.6 months</t>
   </si>
   <si>
     <t>Positive Net Income (2026-27)</t>
@@ -780,7 +780,7 @@
     <t>2026-27 Cash Reserve (Months)</t>
   </si>
   <si>
-    <t>0.4</t>
+    <t>0.6</t>
   </si>
   <si>
     <t>Break-Even Year</t>
@@ -915,6 +915,18 @@
     <t>≥ $10,000</t>
   </si>
   <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
+  </si>
+  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -951,6 +963,9 @@
     <t>≥ 24 months</t>
   </si>
   <si>
+    <t>≥ 90 days</t>
+  </si>
+  <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
   </si>
   <si>
@@ -990,7 +1005,7 @@
     <t>Staffing Burden</t>
   </si>
   <si>
-    <t>Staffing at 24% of revenue leaves room for facilities, programs, and reserves.</t>
+    <t>Staffing at 41% of revenue leaves room for facilities, programs, and reserves.</t>
   </si>
   <si>
     <t>As you add staff, ensure staffing stays below 60% of revenue.</t>
@@ -1008,7 +1023,7 @@
     <t>Debt Affordability</t>
   </si>
   <si>
-    <t>DSCR of 48.12x provides comfortable coverage of debt payments with room to spare.</t>
+    <t>DSCR of 30.43x provides comfortable coverage of debt payments with room to spare.</t>
   </si>
   <si>
     <t>Maintain this ratio as you take on any additional debt.</t>
@@ -1026,7 +1041,7 @@
     <t>Reserve Strength</t>
   </si>
   <si>
-    <t>25.3 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+    <t>11.3 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
   </si>
   <si>
     <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
@@ -1302,7 +1317,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1391,6 +1406,9 @@
     <xf numFmtId="165" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="165" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1398,7 +1416,16 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1414,9 +1441,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2232,23 +2256,23 @@
       </c>
       <c r="B3" s="15">
         <f>'Staffing Plan'!B28</f>
-        <v>1026431</v>
+        <v>997040</v>
       </c>
       <c r="C3" s="15">
         <f>'Staffing Plan'!C28</f>
-        <v>1231718</v>
+        <v>1478601</v>
       </c>
       <c r="D3" s="15">
         <f>'Staffing Plan'!D28</f>
-        <v>1231718</v>
+        <v>1796022</v>
       </c>
       <c r="E3" s="15">
         <f>'Staffing Plan'!E28</f>
-        <v>1231718</v>
+        <v>2042905</v>
       </c>
       <c r="F3" s="15">
         <f>'Staffing Plan'!F28</f>
-        <v>1231718</v>
+        <v>2113443</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2302,23 +2326,23 @@
       </c>
       <c r="B6" s="28">
         <f>SUM(B3:B5)</f>
-        <v>1736256</v>
+        <v>1706865</v>
       </c>
       <c r="C6" s="28">
         <f>SUM(C3:C5)</f>
-        <v>2209403</v>
+        <v>2456286</v>
       </c>
       <c r="D6" s="28">
         <f>SUM(D3:D5)</f>
-        <v>2512064</v>
+        <v>3076368</v>
       </c>
       <c r="E6" s="28">
         <f>SUM(E3:E5)</f>
-        <v>2745632</v>
+        <v>3556819</v>
       </c>
       <c r="F6" s="28">
         <f>SUM(F3:F5)</f>
-        <v>2856467</v>
+        <v>3738192</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2327,23 +2351,23 @@
       </c>
       <c r="B7" s="29">
         <f>B2-B6</f>
-        <v>-447923</v>
+        <v>-418532</v>
       </c>
       <c r="C7" s="30">
         <f>C2-C6</f>
-        <v>313398</v>
+        <v>66515</v>
       </c>
       <c r="D7" s="30">
         <f>D2-D6</f>
-        <v>1272536</v>
+        <v>708232</v>
       </c>
       <c r="E7" s="30">
         <f>E2-E6</f>
-        <v>2013494</v>
+        <v>1202307</v>
       </c>
       <c r="F7" s="30">
         <f>F2-F6</f>
-        <v>2327934</v>
+        <v>1446209</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2352,23 +2376,23 @@
       </c>
       <c r="B8" s="14">
         <f>IF(B2=0,0,B7/B2)</f>
-        <v>-0.35</v>
+        <v>-0.32</v>
       </c>
       <c r="C8" s="14">
         <f>IF(C2=0,0,C7/C2)</f>
-        <v>0.12</v>
+        <v>0.03</v>
       </c>
       <c r="D8" s="14">
         <f>IF(D2=0,0,D7/D2)</f>
-        <v>0.34</v>
+        <v>0.19</v>
       </c>
       <c r="E8" s="14">
         <f>IF(E2=0,0,E7/E2)</f>
-        <v>0.42</v>
+        <v>0.25</v>
       </c>
       <c r="F8" s="14">
         <f>IF(F2=0,0,F7/F2)</f>
-        <v>0.45</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2377,23 +2401,23 @@
       </c>
       <c r="B9" s="27">
         <f>B7</f>
-        <v>-447923</v>
+        <v>-418532</v>
       </c>
       <c r="C9" s="27">
         <f>B9+C7</f>
-        <v>-134525</v>
+        <v>-352017</v>
       </c>
       <c r="D9" s="27">
         <f>C9+D7</f>
-        <v>1138011</v>
+        <v>356215</v>
       </c>
       <c r="E9" s="27">
         <f>D9+E7</f>
-        <v>3151505</v>
+        <v>1558522</v>
       </c>
       <c r="F9" s="27">
         <f>E9+F7</f>
-        <v>5479439</v>
+        <v>3004731</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2473,19 +2497,19 @@
         <v>185</v>
       </c>
       <c r="B3" s="15">
-        <v>52077</v>
+        <v>81468</v>
       </c>
       <c r="C3" s="15">
-        <v>365475</v>
+        <v>147983</v>
       </c>
       <c r="D3" s="15">
-        <v>1638011</v>
+        <v>856215</v>
       </c>
       <c r="E3" s="15">
-        <v>3651505</v>
+        <v>2058522</v>
       </c>
       <c r="F3" s="15">
-        <v>5979439</v>
+        <v>3504731</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2514,23 +2538,23 @@
       </c>
       <c r="B5" s="16">
         <f>SUM(B3:B4)</f>
-        <v>52077</v>
+        <v>81468</v>
       </c>
       <c r="C5" s="16">
         <f>SUM(C3:C4)</f>
-        <v>365475</v>
+        <v>147983</v>
       </c>
       <c r="D5" s="16">
         <f>SUM(D3:D4)</f>
-        <v>1638011</v>
+        <v>856215</v>
       </c>
       <c r="E5" s="16">
         <f>SUM(E3:E4)</f>
-        <v>3651505</v>
+        <v>2058522</v>
       </c>
       <c r="F5" s="16">
         <f>SUM(F3:F4)</f>
-        <v>5979439</v>
+        <v>3504731</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2626,16 +2650,16 @@
         <v>0</v>
       </c>
       <c r="C13" s="15">
-        <v>-426848</v>
+        <v>-397457</v>
       </c>
       <c r="D13" s="15">
-        <v>-91164</v>
+        <v>-308656</v>
       </c>
       <c r="E13" s="15">
-        <v>1204940</v>
+        <v>423144</v>
       </c>
       <c r="F13" s="15">
-        <v>3243357</v>
+        <v>1650374</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2643,19 +2667,19 @@
         <v>194</v>
       </c>
       <c r="B14" s="15">
-        <v>-426848</v>
+        <v>-397457</v>
       </c>
       <c r="C14" s="15">
-        <v>335684</v>
+        <v>88801</v>
       </c>
       <c r="D14" s="15">
-        <v>1296104</v>
+        <v>731800</v>
       </c>
       <c r="E14" s="15">
-        <v>2038417</v>
+        <v>1227230</v>
       </c>
       <c r="F14" s="15">
-        <v>2354290</v>
+        <v>1472565</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2664,23 +2688,23 @@
       </c>
       <c r="B15" s="16">
         <f>B5-B10</f>
-        <v>-426848</v>
+        <v>-397457</v>
       </c>
       <c r="C15" s="16">
         <f>C5-C10</f>
-        <v>-91164</v>
+        <v>-308656</v>
       </c>
       <c r="D15" s="16">
         <f>D5-D10</f>
-        <v>1204940</v>
+        <v>423144</v>
       </c>
       <c r="E15" s="16">
         <f>E5-E10</f>
-        <v>3243357</v>
+        <v>1650374</v>
       </c>
       <c r="F15" s="16">
         <f>F5-F10</f>
-        <v>5597647</v>
+        <v>3122939</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -2765,19 +2789,19 @@
         <v>198</v>
       </c>
       <c r="B3" s="15">
-        <v>-283098</v>
+        <v>-253707</v>
       </c>
       <c r="C3" s="15">
-        <v>403222</v>
+        <v>156339</v>
       </c>
       <c r="D3" s="15">
-        <v>1362361</v>
+        <v>798057</v>
       </c>
       <c r="E3" s="15">
-        <v>2088318</v>
+        <v>1277131</v>
       </c>
       <c r="F3" s="15">
-        <v>2397758</v>
+        <v>1516033</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2806,23 +2830,23 @@
       </c>
       <c r="B5" s="33">
         <f>IF(B4=0,"N/A",B3/B4)</f>
-        <v>-5.68</v>
+        <v>-5.09</v>
       </c>
       <c r="C5" s="33">
         <f>IF(C4=0,"N/A",C3/C4)</f>
-        <v>8.09</v>
+        <v>3.14</v>
       </c>
       <c r="D5" s="33">
         <f>IF(D4=0,"N/A",D3/D4)</f>
-        <v>27.34</v>
+        <v>16.02</v>
       </c>
       <c r="E5" s="33">
         <f>IF(E4=0,"N/A",E3/E4)</f>
-        <v>41.91</v>
+        <v>25.63</v>
       </c>
       <c r="F5" s="33">
         <f>IF(F4=0,"N/A",F3/F4)</f>
-        <v>48.12</v>
+        <v>30.43</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2840,19 +2864,19 @@
         <v>201</v>
       </c>
       <c r="B8" s="15">
-        <v>52077</v>
+        <v>81468</v>
       </c>
       <c r="C8" s="15">
-        <v>365475</v>
+        <v>147983</v>
       </c>
       <c r="D8" s="15">
-        <v>1638011</v>
+        <v>856215</v>
       </c>
       <c r="E8" s="15">
-        <v>3651505</v>
+        <v>2058522</v>
       </c>
       <c r="F8" s="15">
-        <v>5979439</v>
+        <v>3504731</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2860,19 +2884,19 @@
         <v>202</v>
       </c>
       <c r="B9" s="15">
-        <v>130953</v>
+        <v>128503</v>
       </c>
       <c r="C9" s="15">
-        <v>176632</v>
+        <v>197205</v>
       </c>
       <c r="D9" s="15">
-        <v>201853</v>
+        <v>248879</v>
       </c>
       <c r="E9" s="15">
-        <v>222567</v>
+        <v>290166</v>
       </c>
       <c r="F9" s="15">
-        <v>232220</v>
+        <v>305697</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2881,23 +2905,23 @@
       </c>
       <c r="B10" s="34">
         <f>IF(B9=0,0,B8/B9)</f>
-        <v>0.4</v>
+        <v>0.63</v>
       </c>
       <c r="C10" s="34">
         <f>IF(C9=0,0,C8/C9)</f>
-        <v>2.07</v>
+        <v>0.75</v>
       </c>
       <c r="D10" s="34">
         <f>IF(D9=0,0,D8/D9)</f>
-        <v>8.11</v>
+        <v>3.44</v>
       </c>
       <c r="E10" s="34">
         <f>IF(E9=0,0,E8/E9)</f>
-        <v>16.41</v>
+        <v>7.09</v>
       </c>
       <c r="F10" s="34">
         <f>IF(F9=0,0,F8/F9)</f>
-        <v>25.75</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2905,19 +2929,19 @@
         <v>204</v>
       </c>
       <c r="B11" s="35">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C11" s="35">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="D11" s="35">
-        <v>247</v>
+        <v>105</v>
       </c>
       <c r="E11" s="35">
-        <v>499</v>
+        <v>216</v>
       </c>
       <c r="F11" s="35">
-        <v>783</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2963,9 +2987,9 @@
         <f>IF(B10&gt;=2,"PASS","FAIL")</f>
         <v>FAIL</v>
       </c>
-      <c r="C15" s="37" t="str">
+      <c r="C15" s="36" t="str">
         <f>IF(C10&gt;=2,"PASS","FAIL")</f>
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="D15" s="37" t="str">
         <f>IF(D10&gt;=2,"PASS","FAIL")</f>
@@ -3173,7 +3197,7 @@
         <v>233</v>
       </c>
       <c r="B18" s="18">
-        <v>1736256</v>
+        <v>1706865</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -3181,7 +3205,7 @@
         <v>234</v>
       </c>
       <c r="B19" s="18">
-        <v>-447923</v>
+        <v>-418532</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -3189,7 +3213,7 @@
         <v>235</v>
       </c>
       <c r="B20" s="41">
-        <v>-0.34767641595767557</v>
+        <v>-0.32486321471234536</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -3205,7 +3229,7 @@
         <v>236</v>
       </c>
       <c r="B22" s="18">
-        <v>52077</v>
+        <v>81468</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -3253,7 +3277,7 @@
         <v>243</v>
       </c>
       <c r="B28" s="18">
-        <v>14469</v>
+        <v>14224</v>
       </c>
     </row>
   </sheetData>
@@ -3398,23 +3422,23 @@
       </c>
       <c r="B9" s="15">
         <f>'5-Year P&amp;L'!B6</f>
-        <v>1736256</v>
+        <v>1706865</v>
       </c>
       <c r="C9" s="15">
         <f>'5-Year P&amp;L'!C6</f>
-        <v>2209403</v>
+        <v>2456286</v>
       </c>
       <c r="D9" s="15">
         <f>'5-Year P&amp;L'!D6</f>
-        <v>2512064</v>
+        <v>3076368</v>
       </c>
       <c r="E9" s="15">
         <f>'5-Year P&amp;L'!E6</f>
-        <v>2745632</v>
+        <v>3556819</v>
       </c>
       <c r="F9" s="15">
         <f>'5-Year P&amp;L'!F6</f>
-        <v>2856467</v>
+        <v>3738192</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3423,23 +3447,23 @@
       </c>
       <c r="B10" s="23">
         <f>'5-Year P&amp;L'!B7</f>
-        <v>-447923</v>
+        <v>-418532</v>
       </c>
       <c r="C10" s="23">
         <f>'5-Year P&amp;L'!C7</f>
-        <v>313398</v>
+        <v>66515</v>
       </c>
       <c r="D10" s="23">
         <f>'5-Year P&amp;L'!D7</f>
-        <v>1272536</v>
+        <v>708232</v>
       </c>
       <c r="E10" s="23">
         <f>'5-Year P&amp;L'!E7</f>
-        <v>2013494</v>
+        <v>1202307</v>
       </c>
       <c r="F10" s="23">
         <f>'5-Year P&amp;L'!F7</f>
-        <v>2327934</v>
+        <v>1446209</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -3448,23 +3472,23 @@
       </c>
       <c r="B11" s="14">
         <f>IF(B8=0,0,B10/B8)</f>
-        <v>-0.35</v>
+        <v>-0.32</v>
       </c>
       <c r="C11" s="14">
         <f>IF(C8=0,0,C10/C8)</f>
-        <v>0.12</v>
+        <v>0.03</v>
       </c>
       <c r="D11" s="14">
         <f>IF(D8=0,0,D10/D8)</f>
-        <v>0.34</v>
+        <v>0.19</v>
       </c>
       <c r="E11" s="14">
         <f>IF(E8=0,0,E10/E8)</f>
-        <v>0.42</v>
+        <v>0.25</v>
       </c>
       <c r="F11" s="14">
         <f>IF(F8=0,0,F10/F8)</f>
-        <v>0.45</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -3473,23 +3497,23 @@
       </c>
       <c r="B12" s="27">
         <f>B10</f>
-        <v>-447923</v>
+        <v>-418532</v>
       </c>
       <c r="C12" s="27">
         <f>B12+C10</f>
-        <v>-134525</v>
+        <v>-352017</v>
       </c>
       <c r="D12" s="27">
         <f>C12+D10</f>
-        <v>1138011</v>
+        <v>356215</v>
       </c>
       <c r="E12" s="27">
         <f>D12+E10</f>
-        <v>3151505</v>
+        <v>1558522</v>
       </c>
       <c r="F12" s="27">
         <f>E12+F10</f>
-        <v>5479439</v>
+        <v>3004731</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -3497,19 +3521,19 @@
         <v>247</v>
       </c>
       <c r="B13" s="27">
-        <v>52077</v>
+        <v>81468</v>
       </c>
       <c r="C13" s="27">
-        <v>365475</v>
+        <v>147983</v>
       </c>
       <c r="D13" s="27">
-        <v>1638011</v>
+        <v>856215</v>
       </c>
       <c r="E13" s="27">
-        <v>3651505</v>
+        <v>2058522</v>
       </c>
       <c r="F13" s="27">
-        <v>5979439</v>
+        <v>3504731</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -3537,19 +3561,19 @@
         <v>122</v>
       </c>
       <c r="B15" s="15">
-        <v>14469</v>
+        <v>14224</v>
       </c>
       <c r="C15" s="15">
-        <v>11047</v>
+        <v>12281</v>
       </c>
       <c r="D15" s="15">
-        <v>8374</v>
+        <v>10255</v>
       </c>
       <c r="E15" s="15">
-        <v>7322</v>
+        <v>9485</v>
       </c>
       <c r="F15" s="15">
-        <v>7141</v>
+        <v>9345</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -3557,19 +3581,19 @@
         <v>199</v>
       </c>
       <c r="B16" s="33">
-        <v>-5.68</v>
+        <v>-5.09</v>
       </c>
       <c r="C16" s="33">
-        <v>8.09</v>
+        <v>3.14</v>
       </c>
       <c r="D16" s="33">
-        <v>27.34</v>
+        <v>16.02</v>
       </c>
       <c r="E16" s="33">
-        <v>41.91</v>
+        <v>25.63</v>
       </c>
       <c r="F16" s="33">
-        <v>48.12</v>
+        <v>30.43</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -3676,7 +3700,7 @@
         <v>258</v>
       </c>
       <c r="C17" s="27">
-        <v>2327934</v>
+        <v>1446209</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
@@ -3684,7 +3708,7 @@
         <v>201</v>
       </c>
       <c r="C18" s="27">
-        <v>5479439</v>
+        <v>3004731</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
@@ -3827,7 +3851,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -3938,19 +3962,19 @@
         <v>167</v>
       </c>
       <c r="C9" s="61">
-        <v>1026431</v>
+        <v>997040</v>
       </c>
       <c r="D9" s="61">
-        <v>1231718</v>
+        <v>1478601</v>
       </c>
       <c r="E9" s="61">
-        <v>1231718</v>
+        <v>1796022</v>
       </c>
       <c r="F9" s="61">
-        <v>1231718</v>
+        <v>2042905</v>
       </c>
       <c r="G9" s="61">
-        <v>1231718</v>
+        <v>2113443</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -3998,19 +4022,19 @@
         <v>179</v>
       </c>
       <c r="C12" s="63">
-        <v>-447923</v>
+        <v>-418532</v>
       </c>
       <c r="D12" s="64">
-        <v>313398</v>
+        <v>66515</v>
       </c>
       <c r="E12" s="64">
-        <v>1272536</v>
+        <v>708232</v>
       </c>
       <c r="F12" s="64">
-        <v>2013494</v>
+        <v>1202307</v>
       </c>
       <c r="G12" s="64">
-        <v>2327934</v>
+        <v>1446209</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
@@ -4018,19 +4042,19 @@
         <v>282</v>
       </c>
       <c r="C13" s="64">
-        <v>52077</v>
+        <v>81468</v>
       </c>
       <c r="D13" s="64">
-        <v>365475</v>
+        <v>147983</v>
       </c>
       <c r="E13" s="64">
-        <v>1638011</v>
+        <v>856215</v>
       </c>
       <c r="F13" s="64">
-        <v>3651505</v>
+        <v>2058522</v>
       </c>
       <c r="G13" s="64">
-        <v>5979439</v>
+        <v>3504731</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
@@ -4038,390 +4062,496 @@
         <v>283</v>
       </c>
       <c r="C14" s="65">
-        <v>-0.34767641595767557</v>
+        <v>-0.32486321471234536</v>
       </c>
       <c r="D14" s="66">
-        <v>0.12422625654035199</v>
-      </c>
-      <c r="E14" s="66">
-        <v>0.3362405538233895</v>
-      </c>
-      <c r="F14" s="66">
-        <v>0.42308071336642766</v>
-      </c>
-      <c r="G14" s="66">
-        <v>0.44902669547102847</v>
+        <v>0.026365546218487395</v>
+      </c>
+      <c r="E14" s="67">
+        <v>0.1871352322570417</v>
+      </c>
+      <c r="F14" s="67">
+        <v>0.25263194389725</v>
+      </c>
+      <c r="G14" s="67">
+        <v>0.27895397731656507</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="62" t="s">
         <v>248</v>
       </c>
-      <c r="C15" s="67">
+      <c r="C15" s="68">
         <v>10736.108333333334</v>
       </c>
-      <c r="D15" s="67">
+      <c r="D15" s="68">
         <v>12614</v>
       </c>
-      <c r="E15" s="67">
+      <c r="E15" s="68">
         <v>12615.333333333334</v>
       </c>
-      <c r="F15" s="67">
+      <c r="F15" s="68">
         <v>12691</v>
       </c>
-      <c r="G15" s="67">
+      <c r="G15" s="68">
         <v>12961</v>
       </c>
-      <c r="H15" s="68" t="s">
+      <c r="H15" s="69" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="62" t="s">
+        <v>122</v>
+      </c>
+      <c r="C16" s="70">
+        <v>13265.541666666666</v>
+      </c>
+      <c r="D16" s="70">
+        <v>12081.43</v>
+      </c>
+      <c r="E16" s="70">
+        <v>10121.226666666667</v>
+      </c>
+      <c r="F16" s="70">
+        <v>9418.184</v>
+      </c>
+      <c r="G16" s="70">
+        <v>9295.48</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="13" t="s">
         <v>285</v>
       </c>
-      <c r="C16" s="65">
-        <v>0.7967124959152642</v>
-      </c>
-      <c r="D16" s="66">
-        <v>0.4882345013477089</v>
-      </c>
-      <c r="E16" s="66">
-        <v>0.3254552660783174</v>
-      </c>
-      <c r="F16" s="66">
-        <v>0.25881186142410634</v>
-      </c>
-      <c r="G16" s="66">
-        <v>0.23758159092662604</v>
-      </c>
-      <c r="H16" s="68" t="s">
+      <c r="C17" s="61">
+        <v>0</v>
+      </c>
+      <c r="D17" s="61">
+        <v>0</v>
+      </c>
+      <c r="E17" s="61">
+        <v>0</v>
+      </c>
+      <c r="F17" s="61">
+        <v>0</v>
+      </c>
+      <c r="G17" s="61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="13" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="62" t="s">
+      <c r="C18" s="71">
+        <v>2350</v>
+      </c>
+      <c r="D18" s="68">
+        <v>1452.3</v>
+      </c>
+      <c r="E18" s="68">
+        <v>997.2213333333334</v>
+      </c>
+      <c r="F18" s="68">
+        <v>821.7334186666667</v>
+      </c>
+      <c r="G18" s="68">
+        <v>793.4822574000001</v>
+      </c>
+      <c r="H18" s="69" t="s">
         <v>287</v>
       </c>
-      <c r="C17" s="69">
-        <v>0.21888750812095942</v>
-      </c>
-      <c r="D17" s="66">
-        <v>0.1151339781195497</v>
-      </c>
-      <c r="E17" s="66">
-        <v>0.07904835385509698</v>
-      </c>
-      <c r="F17" s="66">
-        <v>0.06474930412628371</v>
-      </c>
-      <c r="G17" s="66">
-        <v>0.06122075900007716</v>
-      </c>
-      <c r="H17" s="68" t="s">
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="62" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="62" t="s">
-        <v>289</v>
-      </c>
-      <c r="C18" s="65">
-        <v>-0.219739772248324</v>
-      </c>
-      <c r="D18" s="66">
-        <v>0.15983114000317108</v>
-      </c>
-      <c r="E18" s="66">
-        <v>0.3599748982719442</v>
-      </c>
-      <c r="F18" s="66">
-        <v>0.4388029312110945</v>
-      </c>
-      <c r="G18" s="66">
-        <v>0.46249479206851324</v>
-      </c>
-      <c r="H18" s="68" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="62" t="s">
-        <v>291</v>
-      </c>
-      <c r="C19" s="70">
-        <v>3</v>
-      </c>
-      <c r="D19" s="70">
-        <v>3</v>
-      </c>
-      <c r="E19" s="70">
-        <v>3</v>
-      </c>
-      <c r="F19" s="70">
-        <v>3</v>
-      </c>
-      <c r="G19" s="70">
-        <v>3</v>
-      </c>
-      <c r="H19" s="68" t="s">
-        <v>292</v>
+      <c r="C19" s="72">
+        <v>-3487.766666666667</v>
+      </c>
+      <c r="D19" s="73">
+        <v>332.575</v>
+      </c>
+      <c r="E19" s="73">
+        <v>2360.7733333333335</v>
+      </c>
+      <c r="F19" s="73">
+        <v>3206.152</v>
+      </c>
+      <c r="G19" s="73">
+        <v>3615.5225</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="62" t="s">
-        <v>199</v>
-      </c>
-      <c r="C20" s="71">
-        <v>-5.681846462619167</v>
-      </c>
-      <c r="D20" s="72">
-        <v>8.092764676367285</v>
-      </c>
-      <c r="E20" s="72">
-        <v>27.342920220772704</v>
-      </c>
-      <c r="F20" s="72">
-        <v>41.91305569493226</v>
-      </c>
-      <c r="G20" s="72">
-        <v>48.12359257400903</v>
-      </c>
-      <c r="H20" s="68" t="s">
-        <v>293</v>
+        <v>289</v>
+      </c>
+      <c r="C20" s="65">
+        <v>0.7738992946699339</v>
+      </c>
+      <c r="D20" s="66">
+        <v>0.5860952116695735</v>
+      </c>
+      <c r="E20" s="67">
+        <v>0.47456058764466524</v>
+      </c>
+      <c r="F20" s="67">
+        <v>0.429260630893284</v>
+      </c>
+      <c r="G20" s="67">
+        <v>0.4076543090810894</v>
+      </c>
+      <c r="H20" s="69" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="62" t="s">
+        <v>291</v>
+      </c>
+      <c r="C21" s="66">
+        <v>0.21888750812095942</v>
+      </c>
+      <c r="D21" s="67">
+        <v>0.1151339781195497</v>
+      </c>
+      <c r="E21" s="67">
+        <v>0.07904835385509698</v>
+      </c>
+      <c r="F21" s="67">
+        <v>0.06474930412628371</v>
+      </c>
+      <c r="G21" s="67">
+        <v>0.06122075900007716</v>
+      </c>
+      <c r="H21" s="69" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="62" t="s">
+        <v>293</v>
+      </c>
+      <c r="C22" s="65">
+        <v>-0.1969265710029938</v>
+      </c>
+      <c r="D22" s="66">
+        <v>0.061970429681306484</v>
+      </c>
+      <c r="E22" s="67">
+        <v>0.21086957670559636</v>
+      </c>
+      <c r="F22" s="67">
+        <v>0.26835416174191684</v>
+      </c>
+      <c r="G22" s="67">
+        <v>0.29242207391404984</v>
+      </c>
+      <c r="H22" s="69" t="s">
         <v>294</v>
       </c>
-      <c r="C21" s="73" t="str">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="62" t="s">
+        <v>295</v>
+      </c>
+      <c r="C23" s="74">
+        <v>3</v>
+      </c>
+      <c r="D23" s="74">
+        <v>3</v>
+      </c>
+      <c r="E23" s="74">
+        <v>3</v>
+      </c>
+      <c r="F23" s="74">
+        <v>3</v>
+      </c>
+      <c r="G23" s="74">
+        <v>3</v>
+      </c>
+      <c r="H23" s="69" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="62" t="s">
+        <v>199</v>
+      </c>
+      <c r="C24" s="75">
+        <v>-5.091961866532865</v>
+      </c>
+      <c r="D24" s="76">
+        <v>3.137762167586553</v>
+      </c>
+      <c r="E24" s="76">
+        <v>16.017200200702458</v>
+      </c>
+      <c r="F24" s="76">
+        <v>25.632333166081285</v>
+      </c>
+      <c r="G24" s="76">
+        <v>30.42715504264927</v>
+      </c>
+      <c r="H24" s="69" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="62" t="s">
+        <v>298</v>
+      </c>
+      <c r="C25" s="77" t="str">
         <f>IF('5-Year P&amp;L'!B9&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="73" t="str">
+      <c r="D25" s="77" t="str">
         <f>IF(AND('5-Year P&amp;L'!C9&gt;=0,'5-Year P&amp;L'!B9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="32" t="str">
+      <c r="E25" s="32" t="str">
         <f>IF(AND('5-Year P&amp;L'!D9&gt;=0,'5-Year P&amp;L'!C9&lt;0),"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="F21" s="73" t="str">
+      <c r="F25" s="77" t="str">
         <f>IF(AND('5-Year P&amp;L'!E9&gt;=0,'5-Year P&amp;L'!D9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="73" t="str">
+      <c r="G25" s="77" t="str">
         <f>IF(AND('5-Year P&amp;L'!F9&gt;=0,'5-Year P&amp;L'!E9&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="68" t="s">
+      <c r="H25" s="69" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="62" t="s">
-        <v>295</v>
-      </c>
-      <c r="C22" s="74">
-        <v>0</v>
-      </c>
-      <c r="D22" s="74">
-        <v>2</v>
-      </c>
-      <c r="E22" s="74">
-        <v>8</v>
-      </c>
-      <c r="F22" s="75">
-        <v>16</v>
-      </c>
-      <c r="G22" s="70">
-        <v>25</v>
-      </c>
-      <c r="H22" s="68" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="D24" s="5" t="s">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="62" t="s">
         <v>299</v>
       </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5" t="s">
+      <c r="C26" s="78">
+        <v>1</v>
+      </c>
+      <c r="D26" s="78">
+        <v>1</v>
+      </c>
+      <c r="E26" s="78">
+        <v>3</v>
+      </c>
+      <c r="F26" s="78">
+        <v>7</v>
+      </c>
+      <c r="G26" s="78">
+        <v>11</v>
+      </c>
+      <c r="H26" s="69" t="s">
         <v>300</v>
       </c>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="76" t="s">
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="62" t="s">
+        <v>204</v>
+      </c>
+      <c r="C27" s="78">
+        <v>19</v>
+      </c>
+      <c r="D27" s="78">
+        <v>22</v>
+      </c>
+      <c r="E27" s="74">
+        <v>103</v>
+      </c>
+      <c r="F27" s="74">
+        <v>213</v>
+      </c>
+      <c r="G27" s="74">
+        <v>344</v>
+      </c>
+      <c r="H27" s="69" t="s">
         <v>301</v>
       </c>
-      <c r="C25" s="77" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="D25" s="78" t="s">
+      <c r="C29" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="E25" s="78"/>
-      <c r="F25" s="79" t="s">
+      <c r="D29" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="G25" s="79"/>
-      <c r="H25" s="79"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="76" t="s">
+      <c r="E29" s="5"/>
+      <c r="F29" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="C26" s="32" t="s">
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="79" t="s">
         <v>306</v>
       </c>
-      <c r="D26" s="78" t="s">
+      <c r="C30" s="80" t="s">
         <v>307</v>
       </c>
-      <c r="E26" s="78"/>
-      <c r="F26" s="79" t="s">
+      <c r="D30" s="81" t="s">
         <v>308</v>
       </c>
-      <c r="G26" s="79"/>
-      <c r="H26" s="79"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="76" t="s">
+      <c r="E30" s="81"/>
+      <c r="F30" s="82" t="s">
         <v>309</v>
       </c>
-      <c r="C27" s="32" t="s">
-        <v>306</v>
-      </c>
-      <c r="D27" s="78" t="s">
+      <c r="G30" s="82"/>
+      <c r="H30" s="82"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="79" t="s">
         <v>310</v>
       </c>
-      <c r="E27" s="78"/>
-      <c r="F27" s="79" t="s">
+      <c r="C31" s="32" t="s">
         <v>311</v>
       </c>
-      <c r="G27" s="79"/>
-      <c r="H27" s="79"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="76" t="s">
+      <c r="D31" s="81" t="s">
         <v>312</v>
       </c>
-      <c r="C28" s="32" t="s">
-        <v>306</v>
-      </c>
-      <c r="D28" s="78" t="s">
+      <c r="E31" s="81"/>
+      <c r="F31" s="82" t="s">
         <v>313</v>
       </c>
-      <c r="E28" s="78"/>
-      <c r="F28" s="79" t="s">
+      <c r="G31" s="82"/>
+      <c r="H31" s="82"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="79" t="s">
         <v>314</v>
       </c>
-      <c r="G28" s="79"/>
-      <c r="H28" s="79"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="76" t="s">
+      <c r="C32" s="32" t="s">
+        <v>311</v>
+      </c>
+      <c r="D32" s="81" t="s">
         <v>315</v>
       </c>
-      <c r="C29" s="32" t="s">
-        <v>306</v>
-      </c>
-      <c r="D29" s="78" t="s">
+      <c r="E32" s="81"/>
+      <c r="F32" s="82" t="s">
         <v>316</v>
       </c>
-      <c r="E29" s="78"/>
-      <c r="F29" s="79" t="s">
+      <c r="G32" s="82"/>
+      <c r="H32" s="82"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="79" t="s">
         <v>317</v>
       </c>
-      <c r="G29" s="79"/>
-      <c r="H29" s="79"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="76" t="s">
+      <c r="C33" s="32" t="s">
+        <v>311</v>
+      </c>
+      <c r="D33" s="81" t="s">
         <v>318</v>
       </c>
-      <c r="C30" s="32" t="s">
-        <v>306</v>
-      </c>
-      <c r="D30" s="78" t="s">
+      <c r="E33" s="81"/>
+      <c r="F33" s="82" t="s">
         <v>319</v>
       </c>
-      <c r="E30" s="78"/>
-      <c r="F30" s="79" t="s">
+      <c r="G33" s="82"/>
+      <c r="H33" s="82"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="79" t="s">
         <v>320</v>
       </c>
-      <c r="G30" s="79"/>
-      <c r="H30" s="79"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="76" t="s">
+      <c r="C34" s="32" t="s">
+        <v>311</v>
+      </c>
+      <c r="D34" s="81" t="s">
         <v>321</v>
       </c>
-      <c r="C31" s="32" t="s">
-        <v>306</v>
-      </c>
-      <c r="D31" s="78" t="s">
+      <c r="E34" s="81"/>
+      <c r="F34" s="82" t="s">
         <v>322</v>
       </c>
-      <c r="E31" s="78"/>
-      <c r="F31" s="79" t="s">
+      <c r="G34" s="82"/>
+      <c r="H34" s="82"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="79" t="s">
         <v>323</v>
       </c>
-      <c r="G31" s="79"/>
-      <c r="H31" s="79"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="76" t="s">
+      <c r="C35" s="32" t="s">
+        <v>311</v>
+      </c>
+      <c r="D35" s="81" t="s">
+        <v>324</v>
+      </c>
+      <c r="E35" s="81"/>
+      <c r="F35" s="82" t="s">
+        <v>325</v>
+      </c>
+      <c r="G35" s="82"/>
+      <c r="H35" s="82"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="79" t="s">
+        <v>326</v>
+      </c>
+      <c r="C36" s="32" t="s">
+        <v>311</v>
+      </c>
+      <c r="D36" s="81" t="s">
+        <v>327</v>
+      </c>
+      <c r="E36" s="81"/>
+      <c r="F36" s="82" t="s">
+        <v>328</v>
+      </c>
+      <c r="G36" s="82"/>
+      <c r="H36" s="82"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="79" t="s">
         <v>273</v>
       </c>
-      <c r="C33" s="62" t="s">
-        <v>324</v>
-      </c>
-      <c r="D33" s="62"/>
-      <c r="E33" s="62"/>
-      <c r="F33" s="62"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="80" t="s">
-        <v>325</v>
-      </c>
-      <c r="C35" s="80"/>
-      <c r="D35" s="80"/>
-      <c r="E35" s="80"/>
-      <c r="F35" s="80"/>
-      <c r="G35" s="80"/>
-      <c r="H35" s="80"/>
+      <c r="C38" s="62" t="s">
+        <v>329</v>
+      </c>
+      <c r="D38" s="62"/>
+      <c r="E38" s="62"/>
+      <c r="F38" s="62"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="83" t="s">
+        <v>330</v>
+      </c>
+      <c r="C40" s="83"/>
+      <c r="D40" s="83"/>
+      <c r="E40" s="83"/>
+      <c r="F40" s="83"/>
+      <c r="G40" s="83"/>
+      <c r="H40" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -4467,48 +4597,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C24:G24">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C20&gt;=1.25</formula>
+      <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1</formula>
+      <formula>C24&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1</formula>
+      <formula>C24&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6238,7 +6368,7 @@
         <v>135</v>
       </c>
       <c r="B14" s="22">
-        <v>261905</v>
+        <v>257007</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -6246,7 +6376,7 @@
         <v>136</v>
       </c>
       <c r="B15" s="22">
-        <v>26895</v>
+        <v>26650</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -6255,7 +6385,7 @@
       </c>
       <c r="B16" s="23">
         <f>SUM(B9:B15)</f>
-        <v>564800</v>
+        <v>559657</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -6264,7 +6394,7 @@
       </c>
       <c r="B18" s="24">
         <f>B6-B16</f>
-        <v>-64800</v>
+        <v>-59657</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
@@ -6562,34 +6692,34 @@
         <v>167</v>
       </c>
       <c r="B3" s="15">
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="C3" s="15">
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="D3" s="15">
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="E3" s="15">
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="F3" s="15">
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="G3" s="15">
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="H3" s="15">
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="I3" s="15">
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="J3" s="15">
-        <v>102643</v>
+        <v>99704</v>
       </c>
       <c r="K3" s="15">
-        <v>102644</v>
+        <v>99704</v>
       </c>
       <c r="L3" s="15">
         <v>0</v>
@@ -6599,7 +6729,7 @@
       </c>
       <c r="N3" s="15">
         <f>SUM(B3:M3)</f>
-        <v>1026431</v>
+        <v>997040</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -6698,43 +6828,43 @@
       </c>
       <c r="B6" s="23">
         <f>SUM(B3:B5)</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="C6" s="23">
         <f>SUM(C3:C5)</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="D6" s="23">
         <f>SUM(D3:D5)</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="E6" s="23">
         <f>SUM(E3:E5)</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="F6" s="23">
         <f>SUM(F3:F5)</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="G6" s="23">
         <f>SUM(G3:G5)</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="H6" s="23">
         <f>SUM(H3:H5)</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="I6" s="23">
         <f>SUM(I3:I5)</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="J6" s="23">
         <f>SUM(J3:J5)</f>
-        <v>170878</v>
+        <v>167939</v>
       </c>
       <c r="K6" s="23">
         <f>SUM(K3:K5)</f>
-        <v>170879</v>
+        <v>167939</v>
       </c>
       <c r="L6" s="23">
         <f>SUM(L3:L5)</f>
@@ -6746,7 +6876,7 @@
       </c>
       <c r="N6" s="23">
         <f>SUM(B6:M6)</f>
-        <v>1736256</v>
+        <v>1706865</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -6755,43 +6885,43 @@
       </c>
       <c r="B7" s="27">
         <f>B2-B6</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="C7" s="27">
         <f>C2-C6</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="D7" s="27">
         <f>D2-D6</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="E7" s="27">
         <f>E2-E6</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="F7" s="27">
         <f>F2-F6</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="G7" s="27">
         <f>G2-G6</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="H7" s="27">
         <f>H2-H6</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="I7" s="27">
         <f>I2-I6</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="J7" s="27">
         <f>J2-J6</f>
-        <v>-16278</v>
+        <v>-13339</v>
       </c>
       <c r="K7" s="27">
         <f>K2-K6</f>
-        <v>-273946</v>
+        <v>-271006</v>
       </c>
       <c r="L7" s="27">
         <f>L2-L6</f>
@@ -6803,7 +6933,7 @@
       </c>
       <c r="N7" s="27">
         <f>SUM(B7:M7)</f>
-        <v>-447923</v>
+        <v>-418532</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -6812,55 +6942,55 @@
       </c>
       <c r="B8" s="27">
         <f>500000+B7</f>
-        <v>483722</v>
+        <v>486661</v>
       </c>
       <c r="C8" s="27">
         <f>B8+C7</f>
-        <v>467444</v>
+        <v>473322</v>
       </c>
       <c r="D8" s="27">
         <f>C8+D7</f>
-        <v>451166</v>
+        <v>459983</v>
       </c>
       <c r="E8" s="27">
         <f>D8+E7</f>
-        <v>434888</v>
+        <v>446644</v>
       </c>
       <c r="F8" s="27">
         <f>E8+F7</f>
-        <v>418610</v>
+        <v>433305</v>
       </c>
       <c r="G8" s="27">
         <f>F8+G7</f>
-        <v>402332</v>
+        <v>419966</v>
       </c>
       <c r="H8" s="27">
         <f>G8+H7</f>
-        <v>386054</v>
+        <v>406627</v>
       </c>
       <c r="I8" s="27">
         <f>H8+I7</f>
-        <v>369776</v>
+        <v>393288</v>
       </c>
       <c r="J8" s="27">
         <f>I8+J7</f>
-        <v>353498</v>
+        <v>379949</v>
       </c>
       <c r="K8" s="27">
         <f>J8+K7</f>
-        <v>79552</v>
+        <v>108943</v>
       </c>
       <c r="L8" s="27">
         <f>K8+L7</f>
-        <v>65817</v>
+        <v>95208</v>
       </c>
       <c r="M8" s="27">
         <f>L8+M7</f>
-        <v>52077</v>
+        <v>81468</v>
       </c>
       <c r="N8" s="27">
         <f>M8</f>
-        <v>52077</v>
+        <v>81468</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -6895,7 +7025,7 @@
       </c>
       <c r="B12" s="18">
         <f>M8</f>
-        <v>52077</v>
+        <v>81468</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -6904,7 +7034,7 @@
       </c>
       <c r="B13" s="19">
         <f>MIN(B8:M8)</f>
-        <v>52077</v>
+        <v>81468</v>
       </c>
     </row>
   </sheetData>

--- a/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V1_(14-tab)_Charter_Public_Funding.xlsx
@@ -678,7 +678,7 @@
     <t>COVENANT CHECKS</t>
   </si>
   <si>
-    <t>DSCR ≥ 1.20x</t>
+    <t>DSCR ≥ 1.25x</t>
   </si>
   <si>
     <t>Cash Reserve ≥ 2.0 Months</t>
@@ -705,7 +705,7 @@
     <t>POLICY FLAGS</t>
   </si>
   <si>
-    <t>DSCR ≥ 1.20x (2026-27)</t>
+    <t>DSCR ≥ 1.25x (2026-27)</t>
   </si>
   <si>
     <t>-5.09x</t>
@@ -798,7 +798,7 @@
     <t>Charter School  |  OH  |  Est. 2026</t>
   </si>
   <si>
-    <t>Prepared March 27, 2026</t>
+    <t>Prepared April 29, 2026</t>
   </si>
   <si>
     <t>Cash Balance</t>
@@ -825,7 +825,7 @@
     <t>Date Prepared</t>
   </si>
   <si>
-    <t>March 27, 2026</t>
+    <t>April 29, 2026</t>
   </si>
   <si>
     <t>UNDERWRITING HIGHLIGHTS</t>
@@ -885,7 +885,7 @@
     <t>Civic Scholars Charter — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated March 27, 2026</t>
+    <t>Generated April 29, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -2959,23 +2959,23 @@
         <v>206</v>
       </c>
       <c r="B14" s="36" t="str">
-        <f>IF(B5&gt;=1.2,"PASS","FAIL")</f>
+        <f>IF(B5&gt;=1.25,"PASS","FAIL")</f>
         <v>FAIL</v>
       </c>
       <c r="C14" s="37" t="str">
-        <f>IF(C5&gt;=1.2,"PASS","FAIL")</f>
+        <f>IF(C5&gt;=1.25,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="D14" s="37" t="str">
-        <f>IF(D5&gt;=1.2,"PASS","FAIL")</f>
+        <f>IF(D5&gt;=1.25,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="E14" s="37" t="str">
-        <f>IF(E5&gt;=1.2,"PASS","FAIL")</f>
+        <f>IF(E5&gt;=1.25,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="F14" s="37" t="str">
-        <f>IF(F5&gt;=1.2,"PASS","FAIL")</f>
+        <f>IF(F5&gt;=1.25,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
@@ -4635,10 +4635,10 @@
       <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1</formula>
+      <formula>C24&gt;=1.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1</formula>
+      <formula>C24&lt;1.15</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
